--- a/aisth/LTRYI-grammar-lesson-questions.xlsx
+++ b/aisth/LTRYI-grammar-lesson-questions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\Users\82109\Documents\My Lab\2_My Desk n Office\과외자료\루Ts추리영어영역\Ltryi_수업자료_Database\문법모음\henesith\aisth_prototypes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\82109\Documents\My Lab\4_My Factory\CodingNDeveloping\웹코딩\Ltryi_Frontend_moved\LTsRYI\aisth\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03AE3D05-9800-4F6A-9EE8-D46F255B39CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2FB65D8-8481-4DAF-84AA-790ED5301C2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40980" yWindow="9840" windowWidth="13335" windowHeight="18525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="40050" yWindow="5565" windowWidth="12150" windowHeight="21165" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5890" uniqueCount="2729">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5890" uniqueCount="2726">
   <si>
     <t>Lesson</t>
   </si>
@@ -5694,12 +5694,6 @@
     <t>She - goes **to** - school - every day</t>
   </si>
   <si>
-    <t>우리는 (S) / 기다렸다 (V) / ___ (T) / 문 앞에서 (D)</t>
-  </si>
-  <si>
-    <t>We - waited -  - **at the** room</t>
-  </si>
-  <si>
     <t>그는 (S) / 여행한다 (V) / ___ (T) / 자주 (D)</t>
   </si>
   <si>
@@ -5742,9 +5736,6 @@
     <t>She - gave - me - a book</t>
   </si>
   <si>
-    <t>그녀는 / 주었다 / 나에게 / 책 한권을</t>
-  </si>
-  <si>
     <t>그는 (S) / 보냈다 (V) / 친구에게 (T) / 엽서를 (D)</t>
   </si>
   <si>
@@ -5805,9 +5796,6 @@
     <t>We - made - her - happy</t>
   </si>
   <si>
-    <t>SVTD 후 자연스럽게 순서를 맞춰보세요.</t>
-  </si>
-  <si>
     <t>선생님은 (S) / 불렀다 (V) / 나를 (T) / 똑똑하다고 (D)</t>
   </si>
   <si>
@@ -5866,9 +5854,6 @@
   </si>
   <si>
     <t xml:space="preserve">She - is dancing -  - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">그녀는 춤추고있다 </t>
   </si>
   <si>
     <t>그들은 (S) / 자고 있다 (V) / ___ (T) / 지금 (D)</t>
@@ -8273,6 +8258,14 @@
   </si>
   <si>
     <t>I am cleaning the room \n(나는 방을 ___하고 있다)</t>
+  </si>
+  <si>
+    <t>우리는 (S) / 기다렸다 (V) / ___ (T) / 방 안에서 (D)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>We - waited -  - **in the** room</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -32744,13 +32737,13 @@
         <v>1862</v>
       </c>
       <c r="D1046" s="2" t="s">
-        <v>1870</v>
+        <v>2724</v>
       </c>
       <c r="E1046" s="2">
         <v>4</v>
       </c>
       <c r="F1046" s="2" t="s">
-        <v>1871</v>
+        <v>2725</v>
       </c>
       <c r="G1046" s="2" t="s">
         <v>1865</v>
@@ -32767,13 +32760,13 @@
         <v>1862</v>
       </c>
       <c r="D1047" s="2" t="s">
-        <v>1872</v>
+        <v>1870</v>
       </c>
       <c r="E1047" s="2">
         <v>5</v>
       </c>
       <c r="F1047" s="2" t="s">
-        <v>1873</v>
+        <v>1871</v>
       </c>
       <c r="G1047" s="2" t="s">
         <v>1865</v>
@@ -32790,13 +32783,13 @@
         <v>1862</v>
       </c>
       <c r="D1048" s="2" t="s">
-        <v>1874</v>
+        <v>1872</v>
       </c>
       <c r="E1048" s="2">
         <v>6</v>
       </c>
       <c r="F1048" s="2" t="s">
-        <v>1875</v>
+        <v>1873</v>
       </c>
       <c r="G1048" s="2" t="s">
         <v>1865</v>
@@ -32813,13 +32806,13 @@
         <v>1862</v>
       </c>
       <c r="D1049" s="2" t="s">
-        <v>1876</v>
+        <v>1874</v>
       </c>
       <c r="E1049" s="2">
         <v>7</v>
       </c>
       <c r="F1049" s="2" t="s">
-        <v>1877</v>
+        <v>1875</v>
       </c>
       <c r="G1049" s="2" t="s">
         <v>1865</v>
@@ -32836,13 +32829,13 @@
         <v>1862</v>
       </c>
       <c r="D1050" s="2" t="s">
-        <v>1878</v>
+        <v>1876</v>
       </c>
       <c r="E1050" s="2">
         <v>8</v>
       </c>
       <c r="F1050" s="2" t="s">
-        <v>1879</v>
+        <v>1877</v>
       </c>
       <c r="G1050" s="2" t="s">
         <v>1865</v>
@@ -32859,13 +32852,13 @@
         <v>1862</v>
       </c>
       <c r="D1051" s="2" t="s">
-        <v>1880</v>
+        <v>1878</v>
       </c>
       <c r="E1051" s="2">
         <v>9</v>
       </c>
       <c r="F1051" s="2" t="s">
-        <v>1881</v>
+        <v>1879</v>
       </c>
       <c r="G1051" s="2" t="s">
         <v>1865</v>
@@ -32882,13 +32875,13 @@
         <v>1862</v>
       </c>
       <c r="D1052" s="2" t="s">
-        <v>1882</v>
+        <v>1880</v>
       </c>
       <c r="E1052" s="2">
         <v>10</v>
       </c>
       <c r="F1052" s="2" t="s">
-        <v>1883</v>
+        <v>1881</v>
       </c>
       <c r="G1052" s="2" t="s">
         <v>1865</v>
@@ -32905,16 +32898,16 @@
         <v>1862</v>
       </c>
       <c r="D1053" s="2" t="s">
-        <v>1884</v>
+        <v>1882</v>
       </c>
       <c r="E1053" s="2">
         <v>11</v>
       </c>
       <c r="F1053" s="2" t="s">
-        <v>1885</v>
+        <v>1883</v>
       </c>
       <c r="G1053" s="2" t="s">
-        <v>1886</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="1054" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -32928,13 +32921,13 @@
         <v>1862</v>
       </c>
       <c r="D1054" s="2" t="s">
-        <v>1887</v>
+        <v>1884</v>
       </c>
       <c r="E1054" s="2">
         <v>12</v>
       </c>
       <c r="F1054" s="2" t="s">
-        <v>1888</v>
+        <v>1885</v>
       </c>
       <c r="G1054" s="2" t="s">
         <v>1865</v>
@@ -32951,13 +32944,13 @@
         <v>1862</v>
       </c>
       <c r="D1055" s="2" t="s">
-        <v>1889</v>
+        <v>1886</v>
       </c>
       <c r="E1055" s="2">
         <v>13</v>
       </c>
       <c r="F1055" s="2" t="s">
-        <v>1890</v>
+        <v>1887</v>
       </c>
       <c r="G1055" s="2" t="s">
         <v>1865</v>
@@ -32974,13 +32967,13 @@
         <v>1862</v>
       </c>
       <c r="D1056" s="2" t="s">
-        <v>1891</v>
+        <v>1888</v>
       </c>
       <c r="E1056" s="2">
         <v>14</v>
       </c>
       <c r="F1056" s="2" t="s">
-        <v>1892</v>
+        <v>1889</v>
       </c>
       <c r="G1056" s="2" t="s">
         <v>1865</v>
@@ -32997,13 +32990,13 @@
         <v>1862</v>
       </c>
       <c r="D1057" s="2" t="s">
-        <v>1893</v>
+        <v>1890</v>
       </c>
       <c r="E1057" s="2">
         <v>15</v>
       </c>
       <c r="F1057" s="2" t="s">
-        <v>1894</v>
+        <v>1891</v>
       </c>
       <c r="G1057" s="2" t="s">
         <v>1865</v>
@@ -33020,13 +33013,13 @@
         <v>1862</v>
       </c>
       <c r="D1058" s="2" t="s">
-        <v>1895</v>
+        <v>1892</v>
       </c>
       <c r="E1058" s="2">
         <v>16</v>
       </c>
       <c r="F1058" s="2" t="s">
-        <v>1896</v>
+        <v>1893</v>
       </c>
       <c r="G1058" s="2" t="s">
         <v>1865</v>
@@ -33043,13 +33036,13 @@
         <v>1862</v>
       </c>
       <c r="D1059" s="2" t="s">
-        <v>1897</v>
+        <v>1894</v>
       </c>
       <c r="E1059" s="2">
         <v>17</v>
       </c>
       <c r="F1059" s="2" t="s">
-        <v>1898</v>
+        <v>1895</v>
       </c>
       <c r="G1059" s="2" t="s">
         <v>1865</v>
@@ -33066,13 +33059,13 @@
         <v>1862</v>
       </c>
       <c r="D1060" s="2" t="s">
-        <v>1899</v>
+        <v>1896</v>
       </c>
       <c r="E1060" s="2">
         <v>18</v>
       </c>
       <c r="F1060" s="2" t="s">
-        <v>1900</v>
+        <v>1897</v>
       </c>
       <c r="G1060" s="2" t="s">
         <v>1865</v>
@@ -33089,13 +33082,13 @@
         <v>1862</v>
       </c>
       <c r="D1061" s="2" t="s">
-        <v>1901</v>
+        <v>1898</v>
       </c>
       <c r="E1061" s="2">
         <v>19</v>
       </c>
       <c r="F1061" s="2" t="s">
-        <v>1902</v>
+        <v>1899</v>
       </c>
       <c r="G1061" s="2" t="s">
         <v>1865</v>
@@ -33112,13 +33105,13 @@
         <v>1862</v>
       </c>
       <c r="D1062" s="2" t="s">
-        <v>1903</v>
+        <v>1900</v>
       </c>
       <c r="E1062" s="2">
         <v>20</v>
       </c>
       <c r="F1062" s="2" t="s">
-        <v>1904</v>
+        <v>1901</v>
       </c>
       <c r="G1062" s="2" t="s">
         <v>1865</v>
@@ -33135,16 +33128,16 @@
         <v>1862</v>
       </c>
       <c r="D1063" s="2" t="s">
-        <v>1905</v>
+        <v>1902</v>
       </c>
       <c r="E1063" s="2">
         <v>21</v>
       </c>
       <c r="F1063" s="2" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
       <c r="G1063" s="2" t="s">
-        <v>1907</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="1064" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -33158,16 +33151,16 @@
         <v>1862</v>
       </c>
       <c r="D1064" s="2" t="s">
-        <v>1908</v>
+        <v>1904</v>
       </c>
       <c r="E1064" s="2">
         <v>22</v>
       </c>
       <c r="F1064" s="2" t="s">
-        <v>1909</v>
+        <v>1905</v>
       </c>
       <c r="G1064" s="2" t="s">
-        <v>1907</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="1065" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -33181,16 +33174,16 @@
         <v>1862</v>
       </c>
       <c r="D1065" s="2" t="s">
-        <v>1910</v>
+        <v>1906</v>
       </c>
       <c r="E1065" s="2">
         <v>23</v>
       </c>
       <c r="F1065" s="2" t="s">
-        <v>1911</v>
+        <v>1907</v>
       </c>
       <c r="G1065" s="2" t="s">
-        <v>1907</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="1066" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -33204,16 +33197,16 @@
         <v>1862</v>
       </c>
       <c r="D1066" s="2" t="s">
-        <v>1912</v>
+        <v>1908</v>
       </c>
       <c r="E1066" s="2">
         <v>24</v>
       </c>
       <c r="F1066" s="2" t="s">
-        <v>1913</v>
+        <v>1909</v>
       </c>
       <c r="G1066" s="2" t="s">
-        <v>1907</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="1067" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -33227,16 +33220,16 @@
         <v>1862</v>
       </c>
       <c r="D1067" s="2" t="s">
-        <v>1914</v>
+        <v>1910</v>
       </c>
       <c r="E1067" s="2">
         <v>25</v>
       </c>
       <c r="F1067" s="2" t="s">
-        <v>1915</v>
+        <v>1911</v>
       </c>
       <c r="G1067" s="2" t="s">
-        <v>1907</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="1068" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -33250,16 +33243,16 @@
         <v>1862</v>
       </c>
       <c r="D1068" s="2" t="s">
-        <v>1916</v>
+        <v>1912</v>
       </c>
       <c r="E1068" s="2">
         <v>26</v>
       </c>
       <c r="F1068" s="2" t="s">
-        <v>1917</v>
+        <v>1913</v>
       </c>
       <c r="G1068" s="2" t="s">
-        <v>1907</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="1069" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -33273,16 +33266,16 @@
         <v>1862</v>
       </c>
       <c r="D1069" s="2" t="s">
-        <v>1918</v>
+        <v>1914</v>
       </c>
       <c r="E1069" s="2">
         <v>27</v>
       </c>
       <c r="F1069" s="2" t="s">
-        <v>1919</v>
+        <v>1915</v>
       </c>
       <c r="G1069" s="2" t="s">
-        <v>1907</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="1070" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -33296,16 +33289,16 @@
         <v>1862</v>
       </c>
       <c r="D1070" s="2" t="s">
-        <v>1920</v>
+        <v>1916</v>
       </c>
       <c r="E1070" s="2">
         <v>28</v>
       </c>
       <c r="F1070" s="2" t="s">
-        <v>1921</v>
+        <v>1917</v>
       </c>
       <c r="G1070" s="2" t="s">
-        <v>1907</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="1071" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -33319,16 +33312,16 @@
         <v>1862</v>
       </c>
       <c r="D1071" s="2" t="s">
-        <v>1922</v>
+        <v>1918</v>
       </c>
       <c r="E1071" s="2">
         <v>29</v>
       </c>
       <c r="F1071" s="2" t="s">
-        <v>1923</v>
+        <v>1919</v>
       </c>
       <c r="G1071" s="2" t="s">
-        <v>1907</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="1072" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -33342,16 +33335,16 @@
         <v>1862</v>
       </c>
       <c r="D1072" s="2" t="s">
-        <v>1924</v>
+        <v>1920</v>
       </c>
       <c r="E1072" s="2">
         <v>30</v>
       </c>
       <c r="F1072" s="2" t="s">
-        <v>1925</v>
+        <v>1921</v>
       </c>
       <c r="G1072" s="2" t="s">
-        <v>1907</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="1073" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -33365,16 +33358,16 @@
         <v>1862</v>
       </c>
       <c r="D1073" s="2" t="s">
-        <v>1926</v>
+        <v>1922</v>
       </c>
       <c r="E1073" s="2">
         <v>31</v>
       </c>
       <c r="F1073" s="2" t="s">
-        <v>1927</v>
+        <v>1923</v>
       </c>
       <c r="G1073" s="2" t="s">
-        <v>1928</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="1074" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -33388,16 +33381,16 @@
         <v>1862</v>
       </c>
       <c r="D1074" s="2" t="s">
-        <v>1929</v>
+        <v>1924</v>
       </c>
       <c r="E1074" s="2">
         <v>32</v>
       </c>
       <c r="F1074" s="2" t="s">
-        <v>1930</v>
+        <v>1925</v>
       </c>
       <c r="G1074" s="2" t="s">
-        <v>1907</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="1075" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -33411,16 +33404,16 @@
         <v>1862</v>
       </c>
       <c r="D1075" s="2" t="s">
-        <v>1931</v>
+        <v>1926</v>
       </c>
       <c r="E1075" s="2">
         <v>33</v>
       </c>
       <c r="F1075" s="2" t="s">
-        <v>1932</v>
+        <v>1927</v>
       </c>
       <c r="G1075" s="2" t="s">
-        <v>1907</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="1076" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -33434,16 +33427,16 @@
         <v>1862</v>
       </c>
       <c r="D1076" s="2" t="s">
-        <v>1933</v>
+        <v>1928</v>
       </c>
       <c r="E1076" s="2">
         <v>34</v>
       </c>
       <c r="F1076" s="2" t="s">
-        <v>1934</v>
+        <v>1929</v>
       </c>
       <c r="G1076" s="2" t="s">
-        <v>1907</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="1077" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -33457,16 +33450,16 @@
         <v>1862</v>
       </c>
       <c r="D1077" s="2" t="s">
-        <v>1935</v>
+        <v>1930</v>
       </c>
       <c r="E1077" s="2">
         <v>35</v>
       </c>
       <c r="F1077" s="2" t="s">
-        <v>1936</v>
+        <v>1931</v>
       </c>
       <c r="G1077" s="2" t="s">
-        <v>1907</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="1078" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -33480,16 +33473,16 @@
         <v>1862</v>
       </c>
       <c r="D1078" s="2" t="s">
-        <v>1937</v>
+        <v>1932</v>
       </c>
       <c r="E1078" s="2">
         <v>36</v>
       </c>
       <c r="F1078" s="2" t="s">
-        <v>1938</v>
+        <v>1933</v>
       </c>
       <c r="G1078" s="2" t="s">
-        <v>1907</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="1079" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -33503,16 +33496,16 @@
         <v>1862</v>
       </c>
       <c r="D1079" s="2" t="s">
-        <v>1939</v>
+        <v>1934</v>
       </c>
       <c r="E1079" s="2">
         <v>37</v>
       </c>
       <c r="F1079" s="2" t="s">
-        <v>1940</v>
+        <v>1935</v>
       </c>
       <c r="G1079" s="2" t="s">
-        <v>1907</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="1080" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -33526,16 +33519,16 @@
         <v>1862</v>
       </c>
       <c r="D1080" s="2" t="s">
-        <v>1941</v>
+        <v>1936</v>
       </c>
       <c r="E1080" s="2">
         <v>38</v>
       </c>
       <c r="F1080" s="2" t="s">
-        <v>1942</v>
+        <v>1937</v>
       </c>
       <c r="G1080" s="2" t="s">
-        <v>1907</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="1081" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -33549,16 +33542,16 @@
         <v>1862</v>
       </c>
       <c r="D1081" s="2" t="s">
-        <v>1943</v>
+        <v>1938</v>
       </c>
       <c r="E1081" s="2">
         <v>39</v>
       </c>
       <c r="F1081" s="2" t="s">
-        <v>1944</v>
+        <v>1939</v>
       </c>
       <c r="G1081" s="2" t="s">
-        <v>1907</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="1082" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -33572,16 +33565,16 @@
         <v>1862</v>
       </c>
       <c r="D1082" s="2" t="s">
-        <v>1945</v>
+        <v>1940</v>
       </c>
       <c r="E1082" s="2">
         <v>40</v>
       </c>
       <c r="F1082" s="2" t="s">
-        <v>1946</v>
+        <v>1941</v>
       </c>
       <c r="G1082" s="2" t="s">
-        <v>1907</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="1083" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -33595,16 +33588,16 @@
         <v>1862</v>
       </c>
       <c r="D1083" s="2" t="s">
-        <v>1947</v>
+        <v>1942</v>
       </c>
       <c r="E1083" s="3">
         <v>1</v>
       </c>
       <c r="F1083" s="2" t="s">
-        <v>1948</v>
+        <v>1943</v>
       </c>
       <c r="G1083" s="2" t="s">
-        <v>1949</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="1084" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -33618,16 +33611,16 @@
         <v>1862</v>
       </c>
       <c r="D1084" s="2" t="s">
-        <v>1950</v>
+        <v>1945</v>
       </c>
       <c r="E1084" s="3">
         <v>2</v>
       </c>
       <c r="F1084" s="2" t="s">
-        <v>1951</v>
+        <v>1946</v>
       </c>
       <c r="G1084" s="2" t="s">
-        <v>1952</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="1085" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -33641,16 +33634,16 @@
         <v>1862</v>
       </c>
       <c r="D1085" s="2" t="s">
-        <v>1953</v>
+        <v>1948</v>
       </c>
       <c r="E1085" s="3">
         <v>3</v>
       </c>
       <c r="F1085" s="2" t="s">
-        <v>1954</v>
+        <v>1949</v>
       </c>
       <c r="G1085" s="2" t="s">
-        <v>1952</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="1086" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -33664,16 +33657,16 @@
         <v>1862</v>
       </c>
       <c r="D1086" s="2" t="s">
-        <v>1955</v>
+        <v>1950</v>
       </c>
       <c r="E1086" s="3">
         <v>4</v>
       </c>
       <c r="F1086" s="2" t="s">
-        <v>1956</v>
+        <v>1951</v>
       </c>
       <c r="G1086" s="2" t="s">
-        <v>1952</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="1087" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -33687,16 +33680,16 @@
         <v>1862</v>
       </c>
       <c r="D1087" s="2" t="s">
-        <v>1957</v>
+        <v>1952</v>
       </c>
       <c r="E1087" s="3">
         <v>5</v>
       </c>
       <c r="F1087" s="2" t="s">
-        <v>1958</v>
+        <v>1953</v>
       </c>
       <c r="G1087" s="2" t="s">
-        <v>1952</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="1088" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -33710,16 +33703,16 @@
         <v>1862</v>
       </c>
       <c r="D1088" s="2" t="s">
-        <v>1959</v>
+        <v>1954</v>
       </c>
       <c r="E1088" s="3">
         <v>6</v>
       </c>
       <c r="F1088" s="2" t="s">
-        <v>1960</v>
+        <v>1955</v>
       </c>
       <c r="G1088" s="2" t="s">
-        <v>1952</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="1089" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -33733,16 +33726,16 @@
         <v>1862</v>
       </c>
       <c r="D1089" s="2" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
       <c r="E1089" s="3">
         <v>7</v>
       </c>
       <c r="F1089" s="2" t="s">
-        <v>1962</v>
+        <v>1957</v>
       </c>
       <c r="G1089" s="2" t="s">
-        <v>1952</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="1090" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -33756,16 +33749,16 @@
         <v>1862</v>
       </c>
       <c r="D1090" s="2" t="s">
-        <v>1963</v>
+        <v>1958</v>
       </c>
       <c r="E1090" s="3">
         <v>8</v>
       </c>
       <c r="F1090" s="2" t="s">
-        <v>1964</v>
+        <v>1959</v>
       </c>
       <c r="G1090" s="2" t="s">
-        <v>1952</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="1091" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -33779,16 +33772,16 @@
         <v>1862</v>
       </c>
       <c r="D1091" s="2" t="s">
-        <v>1965</v>
+        <v>1960</v>
       </c>
       <c r="E1091" s="3">
         <v>9</v>
       </c>
       <c r="F1091" s="2" t="s">
-        <v>1966</v>
+        <v>1961</v>
       </c>
       <c r="G1091" s="2" t="s">
-        <v>1952</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="1092" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -33802,16 +33795,16 @@
         <v>1862</v>
       </c>
       <c r="D1092" s="2" t="s">
-        <v>1967</v>
+        <v>1962</v>
       </c>
       <c r="E1092" s="3">
         <v>10</v>
       </c>
       <c r="F1092" s="2" t="s">
-        <v>1968</v>
+        <v>1963</v>
       </c>
       <c r="G1092" s="2" t="s">
-        <v>1952</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="1093" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -33822,19 +33815,19 @@
         <v>3</v>
       </c>
       <c r="C1093" t="s">
-        <v>1969</v>
+        <v>1964</v>
       </c>
       <c r="D1093" t="s">
-        <v>1970</v>
+        <v>1965</v>
       </c>
       <c r="E1093" s="2">
         <v>1</v>
       </c>
       <c r="F1093" s="2" t="s">
-        <v>1971</v>
+        <v>1966</v>
       </c>
       <c r="G1093" s="2" t="s">
-        <v>1972</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="1094" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -33845,19 +33838,19 @@
         <v>3</v>
       </c>
       <c r="C1094" t="s">
-        <v>1969</v>
+        <v>1964</v>
       </c>
       <c r="D1094" t="s">
-        <v>1973</v>
+        <v>1968</v>
       </c>
       <c r="E1094" s="2">
         <v>2</v>
       </c>
       <c r="F1094" s="2" t="s">
-        <v>1974</v>
+        <v>1969</v>
       </c>
       <c r="G1094" s="2" t="s">
-        <v>1972</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="1095" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -33868,19 +33861,19 @@
         <v>3</v>
       </c>
       <c r="C1095" t="s">
-        <v>1969</v>
+        <v>1964</v>
       </c>
       <c r="D1095" t="s">
-        <v>1975</v>
+        <v>1970</v>
       </c>
       <c r="E1095" s="2">
         <v>3</v>
       </c>
       <c r="F1095" s="2" t="s">
-        <v>1976</v>
+        <v>1971</v>
       </c>
       <c r="G1095" s="2" t="s">
-        <v>1972</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="1096" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -33891,19 +33884,19 @@
         <v>3</v>
       </c>
       <c r="C1096" t="s">
-        <v>1969</v>
+        <v>1964</v>
       </c>
       <c r="D1096" t="s">
-        <v>1977</v>
+        <v>1972</v>
       </c>
       <c r="E1096" s="2">
         <v>4</v>
       </c>
       <c r="F1096" s="2" t="s">
-        <v>1978</v>
+        <v>1973</v>
       </c>
       <c r="G1096" s="2" t="s">
-        <v>1972</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="1097" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -33914,19 +33907,19 @@
         <v>3</v>
       </c>
       <c r="C1097" t="s">
-        <v>1969</v>
+        <v>1964</v>
       </c>
       <c r="D1097" t="s">
-        <v>1979</v>
+        <v>1974</v>
       </c>
       <c r="E1097" s="2">
         <v>5</v>
       </c>
       <c r="F1097" s="2" t="s">
-        <v>1980</v>
+        <v>1975</v>
       </c>
       <c r="G1097" s="2" t="s">
-        <v>1972</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="1098" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -33937,19 +33930,19 @@
         <v>3</v>
       </c>
       <c r="C1098" t="s">
-        <v>1969</v>
+        <v>1964</v>
       </c>
       <c r="D1098" t="s">
-        <v>1981</v>
+        <v>1976</v>
       </c>
       <c r="E1098" s="2">
         <v>6</v>
       </c>
       <c r="F1098" s="2" t="s">
-        <v>1982</v>
+        <v>1977</v>
       </c>
       <c r="G1098" s="2" t="s">
-        <v>1972</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="1099" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -33960,19 +33953,19 @@
         <v>3</v>
       </c>
       <c r="C1099" t="s">
-        <v>1969</v>
+        <v>1964</v>
       </c>
       <c r="D1099" t="s">
-        <v>1983</v>
+        <v>1978</v>
       </c>
       <c r="E1099" s="2">
         <v>7</v>
       </c>
       <c r="F1099" s="2" t="s">
-        <v>1984</v>
+        <v>1979</v>
       </c>
       <c r="G1099" s="2" t="s">
-        <v>1972</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="1100" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -33983,19 +33976,19 @@
         <v>3</v>
       </c>
       <c r="C1100" t="s">
-        <v>1969</v>
+        <v>1964</v>
       </c>
       <c r="D1100" t="s">
-        <v>1985</v>
+        <v>1980</v>
       </c>
       <c r="E1100" s="2">
         <v>8</v>
       </c>
       <c r="F1100" s="2" t="s">
-        <v>1986</v>
+        <v>1981</v>
       </c>
       <c r="G1100" s="2" t="s">
-        <v>1972</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="1101" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -34006,19 +33999,19 @@
         <v>3</v>
       </c>
       <c r="C1101" t="s">
-        <v>1969</v>
+        <v>1964</v>
       </c>
       <c r="D1101" t="s">
-        <v>1987</v>
+        <v>1982</v>
       </c>
       <c r="E1101" s="2">
         <v>9</v>
       </c>
       <c r="F1101" s="2" t="s">
-        <v>1988</v>
+        <v>1983</v>
       </c>
       <c r="G1101" s="2" t="s">
-        <v>1972</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="1102" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -34029,19 +34022,19 @@
         <v>3</v>
       </c>
       <c r="C1102" t="s">
-        <v>1969</v>
+        <v>1964</v>
       </c>
       <c r="D1102" t="s">
-        <v>1989</v>
+        <v>1984</v>
       </c>
       <c r="E1102" s="2">
         <v>10</v>
       </c>
       <c r="F1102" s="2" t="s">
-        <v>1990</v>
+        <v>1985</v>
       </c>
       <c r="G1102" s="2" t="s">
-        <v>1972</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="1103" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -34052,19 +34045,19 @@
         <v>3</v>
       </c>
       <c r="C1103" t="s">
-        <v>1969</v>
+        <v>1964</v>
       </c>
       <c r="D1103" t="s">
-        <v>1991</v>
+        <v>1986</v>
       </c>
       <c r="E1103" s="2">
         <v>11</v>
       </c>
       <c r="F1103" s="2" t="s">
-        <v>1992</v>
+        <v>1987</v>
       </c>
       <c r="G1103" s="2" t="s">
-        <v>1992</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="1104" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -34075,19 +34068,19 @@
         <v>3</v>
       </c>
       <c r="C1104" t="s">
-        <v>1969</v>
+        <v>1964</v>
       </c>
       <c r="D1104" t="s">
-        <v>1993</v>
+        <v>1988</v>
       </c>
       <c r="E1104" s="2">
         <v>12</v>
       </c>
       <c r="F1104" s="2" t="s">
-        <v>1994</v>
+        <v>1989</v>
       </c>
       <c r="G1104" s="2" t="s">
-        <v>1972</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="1105" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -34098,19 +34091,19 @@
         <v>3</v>
       </c>
       <c r="C1105" t="s">
-        <v>1969</v>
+        <v>1964</v>
       </c>
       <c r="D1105" t="s">
-        <v>1995</v>
+        <v>1990</v>
       </c>
       <c r="E1105" s="2">
         <v>13</v>
       </c>
       <c r="F1105" s="2" t="s">
-        <v>1996</v>
+        <v>1991</v>
       </c>
       <c r="G1105" s="2" t="s">
-        <v>1972</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="1106" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -34121,19 +34114,19 @@
         <v>3</v>
       </c>
       <c r="C1106" t="s">
-        <v>1969</v>
+        <v>1964</v>
       </c>
       <c r="D1106" t="s">
-        <v>1997</v>
+        <v>1992</v>
       </c>
       <c r="E1106" s="2">
         <v>14</v>
       </c>
       <c r="F1106" s="2" t="s">
-        <v>1998</v>
+        <v>1993</v>
       </c>
       <c r="G1106" s="2" t="s">
-        <v>1972</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="1107" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -34144,19 +34137,19 @@
         <v>3</v>
       </c>
       <c r="C1107" t="s">
-        <v>1969</v>
+        <v>1964</v>
       </c>
       <c r="D1107" t="s">
-        <v>1999</v>
+        <v>1994</v>
       </c>
       <c r="E1107" s="2">
         <v>15</v>
       </c>
       <c r="F1107" s="2" t="s">
-        <v>2000</v>
+        <v>1995</v>
       </c>
       <c r="G1107" s="2" t="s">
-        <v>1972</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="1108" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -34167,19 +34160,19 @@
         <v>3</v>
       </c>
       <c r="C1108" t="s">
-        <v>1969</v>
+        <v>1964</v>
       </c>
       <c r="D1108" t="s">
-        <v>2001</v>
+        <v>1996</v>
       </c>
       <c r="E1108" s="2">
         <v>16</v>
       </c>
       <c r="F1108" s="2" t="s">
-        <v>2002</v>
+        <v>1997</v>
       </c>
       <c r="G1108" s="2" t="s">
-        <v>1972</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="1109" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -34190,19 +34183,19 @@
         <v>3</v>
       </c>
       <c r="C1109" t="s">
-        <v>1969</v>
+        <v>1964</v>
       </c>
       <c r="D1109" t="s">
-        <v>2003</v>
+        <v>1998</v>
       </c>
       <c r="E1109" s="2">
         <v>17</v>
       </c>
       <c r="F1109" s="2" t="s">
-        <v>2004</v>
+        <v>1999</v>
       </c>
       <c r="G1109" s="2" t="s">
-        <v>1972</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="1110" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -34213,19 +34206,19 @@
         <v>3</v>
       </c>
       <c r="C1110" t="s">
-        <v>1969</v>
+        <v>1964</v>
       </c>
       <c r="D1110" t="s">
-        <v>2005</v>
+        <v>2000</v>
       </c>
       <c r="E1110" s="2">
         <v>18</v>
       </c>
       <c r="F1110" s="2" t="s">
-        <v>2006</v>
+        <v>2001</v>
       </c>
       <c r="G1110" s="2" t="s">
-        <v>1972</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="1111" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -34236,19 +34229,19 @@
         <v>3</v>
       </c>
       <c r="C1111" t="s">
-        <v>1969</v>
+        <v>1964</v>
       </c>
       <c r="D1111" t="s">
-        <v>2007</v>
+        <v>2002</v>
       </c>
       <c r="E1111" s="2">
         <v>19</v>
       </c>
       <c r="F1111" s="2" t="s">
-        <v>2008</v>
+        <v>2003</v>
       </c>
       <c r="G1111" s="2" t="s">
-        <v>1972</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="1112" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -34259,19 +34252,19 @@
         <v>3</v>
       </c>
       <c r="C1112" t="s">
-        <v>1969</v>
+        <v>1964</v>
       </c>
       <c r="D1112" t="s">
-        <v>2009</v>
+        <v>2004</v>
       </c>
       <c r="E1112" s="2">
         <v>20</v>
       </c>
       <c r="F1112" s="2" t="s">
-        <v>2010</v>
+        <v>2005</v>
       </c>
       <c r="G1112" s="2" t="s">
-        <v>1972</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="1113" spans="1:7" x14ac:dyDescent="0.45">
@@ -34282,19 +34275,19 @@
         <v>4</v>
       </c>
       <c r="C1113" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1113" s="2" t="s">
-        <v>2012</v>
+        <v>2007</v>
       </c>
       <c r="E1113" s="2">
         <v>1</v>
       </c>
       <c r="F1113" s="2" t="s">
-        <v>2013</v>
+        <v>2008</v>
       </c>
       <c r="G1113" s="2" t="s">
-        <v>2014</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="1114" spans="1:7" x14ac:dyDescent="0.45">
@@ -34305,19 +34298,19 @@
         <v>4</v>
       </c>
       <c r="C1114" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1114" s="2" t="s">
-        <v>2015</v>
+        <v>2010</v>
       </c>
       <c r="E1114" s="2">
         <v>2</v>
       </c>
       <c r="F1114" s="2" t="s">
-        <v>2013</v>
+        <v>2008</v>
       </c>
       <c r="G1114" s="2" t="s">
-        <v>2014</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="1115" spans="1:7" x14ac:dyDescent="0.45">
@@ -34328,19 +34321,19 @@
         <v>4</v>
       </c>
       <c r="C1115" t="s">
+        <v>2006</v>
+      </c>
+      <c r="D1115" s="2" t="s">
         <v>2011</v>
-      </c>
-      <c r="D1115" s="2" t="s">
-        <v>2016</v>
       </c>
       <c r="E1115" s="2">
         <v>3</v>
       </c>
       <c r="F1115" s="2" t="s">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="G1115" s="2" t="s">
-        <v>2014</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="1116" spans="1:7" x14ac:dyDescent="0.45">
@@ -34351,19 +34344,19 @@
         <v>4</v>
       </c>
       <c r="C1116" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1116" s="2" t="s">
-        <v>2018</v>
+        <v>2013</v>
       </c>
       <c r="E1116" s="2">
         <v>4</v>
       </c>
       <c r="F1116" s="2" t="s">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="G1116" s="2" t="s">
-        <v>2014</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="1117" spans="1:7" x14ac:dyDescent="0.45">
@@ -34374,19 +34367,19 @@
         <v>4</v>
       </c>
       <c r="C1117" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1117" s="2" t="s">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="E1117" s="2">
         <v>5</v>
       </c>
       <c r="F1117" s="2" t="s">
-        <v>2013</v>
+        <v>2008</v>
       </c>
       <c r="G1117" s="2" t="s">
-        <v>2014</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="1118" spans="1:7" x14ac:dyDescent="0.45">
@@ -34397,19 +34390,19 @@
         <v>4</v>
       </c>
       <c r="C1118" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1118" s="2" t="s">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="E1118" s="2">
         <v>6</v>
       </c>
       <c r="F1118" s="2" t="s">
-        <v>2013</v>
+        <v>2008</v>
       </c>
       <c r="G1118" s="2" t="s">
-        <v>2014</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="1119" spans="1:7" x14ac:dyDescent="0.45">
@@ -34420,19 +34413,19 @@
         <v>4</v>
       </c>
       <c r="C1119" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1119" s="2" t="s">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="E1119" s="2">
         <v>7</v>
       </c>
       <c r="F1119" s="2" t="s">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="G1119" s="2" t="s">
-        <v>2014</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="1120" spans="1:7" x14ac:dyDescent="0.45">
@@ -34443,19 +34436,19 @@
         <v>4</v>
       </c>
       <c r="C1120" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1120" s="2" t="s">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="E1120" s="2">
         <v>8</v>
       </c>
       <c r="F1120" s="2" t="s">
-        <v>2013</v>
+        <v>2008</v>
       </c>
       <c r="G1120" s="2" t="s">
-        <v>2014</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="1121" spans="1:7" x14ac:dyDescent="0.45">
@@ -34466,19 +34459,19 @@
         <v>4</v>
       </c>
       <c r="C1121" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1121" s="2" t="s">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="E1121" s="2">
         <v>9</v>
       </c>
       <c r="F1121" s="2" t="s">
-        <v>2013</v>
+        <v>2008</v>
       </c>
       <c r="G1121" s="2" t="s">
-        <v>2014</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="1122" spans="1:7" x14ac:dyDescent="0.45">
@@ -34489,19 +34482,19 @@
         <v>4</v>
       </c>
       <c r="C1122" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1122" s="2" t="s">
-        <v>2025</v>
+        <v>2020</v>
       </c>
       <c r="E1122" s="2">
         <v>10</v>
       </c>
       <c r="F1122" s="2" t="s">
-        <v>2013</v>
+        <v>2008</v>
       </c>
       <c r="G1122" s="2" t="s">
-        <v>2014</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="1123" spans="1:7" x14ac:dyDescent="0.45">
@@ -34512,19 +34505,19 @@
         <v>4</v>
       </c>
       <c r="C1123" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1123" s="2" t="s">
-        <v>2026</v>
+        <v>2021</v>
       </c>
       <c r="E1123" s="2">
         <v>11</v>
       </c>
       <c r="F1123" s="2" t="s">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="G1123" s="2" t="s">
-        <v>2017</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="1124" spans="1:7" x14ac:dyDescent="0.45">
@@ -34535,19 +34528,19 @@
         <v>4</v>
       </c>
       <c r="C1124" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1124" s="2" t="s">
-        <v>2027</v>
+        <v>2022</v>
       </c>
       <c r="E1124" s="2">
         <v>12</v>
       </c>
       <c r="F1124" s="2" t="s">
-        <v>2013</v>
+        <v>2008</v>
       </c>
       <c r="G1124" s="2" t="s">
-        <v>2014</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="1125" spans="1:7" x14ac:dyDescent="0.45">
@@ -34558,19 +34551,19 @@
         <v>4</v>
       </c>
       <c r="C1125" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1125" s="2" t="s">
-        <v>2028</v>
+        <v>2023</v>
       </c>
       <c r="E1125" s="2">
         <v>13</v>
       </c>
       <c r="F1125" s="2" t="s">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="G1125" s="2" t="s">
-        <v>2014</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="1126" spans="1:7" x14ac:dyDescent="0.45">
@@ -34581,19 +34574,19 @@
         <v>4</v>
       </c>
       <c r="C1126" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1126" s="2" t="s">
-        <v>2029</v>
+        <v>2024</v>
       </c>
       <c r="E1126" s="2">
         <v>14</v>
       </c>
       <c r="F1126" s="2" t="s">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="G1126" s="2" t="s">
-        <v>2014</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="1127" spans="1:7" x14ac:dyDescent="0.45">
@@ -34604,19 +34597,19 @@
         <v>4</v>
       </c>
       <c r="C1127" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1127" s="2" t="s">
-        <v>2030</v>
+        <v>2025</v>
       </c>
       <c r="E1127" s="2">
         <v>15</v>
       </c>
       <c r="F1127" s="2" t="s">
-        <v>2013</v>
+        <v>2008</v>
       </c>
       <c r="G1127" s="2" t="s">
-        <v>2014</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="1128" spans="1:7" x14ac:dyDescent="0.45">
@@ -34627,19 +34620,19 @@
         <v>4</v>
       </c>
       <c r="C1128" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1128" s="2" t="s">
-        <v>2031</v>
+        <v>2026</v>
       </c>
       <c r="E1128" s="2">
         <v>16</v>
       </c>
       <c r="F1128" s="2" t="s">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="G1128" s="2" t="s">
-        <v>2014</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="1129" spans="1:7" x14ac:dyDescent="0.45">
@@ -34650,19 +34643,19 @@
         <v>4</v>
       </c>
       <c r="C1129" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1129" s="2" t="s">
-        <v>2032</v>
+        <v>2027</v>
       </c>
       <c r="E1129" s="2">
         <v>17</v>
       </c>
       <c r="F1129" s="2" t="s">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="G1129" s="2" t="s">
-        <v>2014</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="1130" spans="1:7" x14ac:dyDescent="0.45">
@@ -34673,19 +34666,19 @@
         <v>4</v>
       </c>
       <c r="C1130" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1130" s="2" t="s">
-        <v>2033</v>
+        <v>2028</v>
       </c>
       <c r="E1130" s="2">
         <v>18</v>
       </c>
       <c r="F1130" s="2" t="s">
-        <v>2013</v>
+        <v>2008</v>
       </c>
       <c r="G1130" s="2" t="s">
-        <v>2014</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="1131" spans="1:7" x14ac:dyDescent="0.45">
@@ -34696,19 +34689,19 @@
         <v>4</v>
       </c>
       <c r="C1131" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1131" s="2" t="s">
-        <v>2034</v>
+        <v>2029</v>
       </c>
       <c r="E1131" s="2">
         <v>19</v>
       </c>
       <c r="F1131" s="2" t="s">
-        <v>2035</v>
+        <v>2030</v>
       </c>
       <c r="G1131" s="2" t="s">
-        <v>2014</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="1132" spans="1:7" x14ac:dyDescent="0.45">
@@ -34719,19 +34712,19 @@
         <v>4</v>
       </c>
       <c r="C1132" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1132" s="2" t="s">
-        <v>2036</v>
+        <v>2031</v>
       </c>
       <c r="E1132" s="2">
         <v>20</v>
       </c>
       <c r="F1132" s="2" t="s">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="G1132" s="2" t="s">
-        <v>2014</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="1133" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -34742,19 +34735,19 @@
         <v>4</v>
       </c>
       <c r="C1133" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1133" s="2" t="s">
-        <v>2037</v>
+        <v>2032</v>
       </c>
       <c r="E1133" s="2">
         <v>21</v>
       </c>
       <c r="F1133" s="2" t="s">
-        <v>2038</v>
+        <v>2033</v>
       </c>
       <c r="G1133" s="2" t="s">
-        <v>2038</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="1134" spans="1:7" x14ac:dyDescent="0.45">
@@ -34765,19 +34758,19 @@
         <v>4</v>
       </c>
       <c r="C1134" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1134" s="2" t="s">
-        <v>2039</v>
+        <v>2034</v>
       </c>
       <c r="E1134" s="2">
         <v>22</v>
       </c>
       <c r="F1134" s="2" t="s">
-        <v>2040</v>
+        <v>2035</v>
       </c>
       <c r="G1134" s="2" t="s">
-        <v>2041</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="1135" spans="1:7" x14ac:dyDescent="0.45">
@@ -34788,19 +34781,19 @@
         <v>4</v>
       </c>
       <c r="C1135" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1135" s="2" t="s">
-        <v>2042</v>
+        <v>2037</v>
       </c>
       <c r="E1135" s="2">
         <v>23</v>
       </c>
       <c r="F1135" s="2" t="s">
-        <v>2043</v>
+        <v>2038</v>
       </c>
       <c r="G1135" s="2" t="s">
-        <v>2041</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="1136" spans="1:7" x14ac:dyDescent="0.45">
@@ -34811,19 +34804,19 @@
         <v>4</v>
       </c>
       <c r="C1136" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1136" s="2" t="s">
-        <v>2044</v>
+        <v>2039</v>
       </c>
       <c r="E1136" s="2">
         <v>24</v>
       </c>
       <c r="F1136" s="2" t="s">
-        <v>2045</v>
+        <v>2040</v>
       </c>
       <c r="G1136" s="2" t="s">
-        <v>2041</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="1137" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -34834,19 +34827,19 @@
         <v>4</v>
       </c>
       <c r="C1137" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1137" s="2" t="s">
-        <v>2046</v>
+        <v>2041</v>
       </c>
       <c r="E1137" s="2">
         <v>25</v>
       </c>
       <c r="F1137" s="2" t="s">
-        <v>2047</v>
+        <v>2042</v>
       </c>
       <c r="G1137" s="2" t="s">
-        <v>2041</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="1138" spans="1:7" x14ac:dyDescent="0.45">
@@ -34857,19 +34850,19 @@
         <v>4</v>
       </c>
       <c r="C1138" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1138" s="2" t="s">
-        <v>2048</v>
+        <v>2043</v>
       </c>
       <c r="E1138" s="2">
         <v>26</v>
       </c>
       <c r="F1138" s="2" t="s">
-        <v>2049</v>
+        <v>2044</v>
       </c>
       <c r="G1138" s="2" t="s">
-        <v>2041</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="1139" spans="1:7" x14ac:dyDescent="0.45">
@@ -34880,19 +34873,19 @@
         <v>4</v>
       </c>
       <c r="C1139" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1139" s="2" t="s">
-        <v>2050</v>
+        <v>2045</v>
       </c>
       <c r="E1139" s="2">
         <v>27</v>
       </c>
       <c r="F1139" s="2" t="s">
-        <v>2051</v>
+        <v>2046</v>
       </c>
       <c r="G1139" s="2" t="s">
-        <v>2041</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="1140" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -34903,19 +34896,19 @@
         <v>4</v>
       </c>
       <c r="C1140" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1140" s="2" t="s">
-        <v>2052</v>
+        <v>2047</v>
       </c>
       <c r="E1140" s="2">
         <v>28</v>
       </c>
       <c r="F1140" s="2" t="s">
-        <v>2053</v>
+        <v>2048</v>
       </c>
       <c r="G1140" s="2" t="s">
-        <v>2041</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="1141" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -34926,19 +34919,19 @@
         <v>4</v>
       </c>
       <c r="C1141" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1141" s="2" t="s">
-        <v>2054</v>
+        <v>2049</v>
       </c>
       <c r="E1141" s="2">
         <v>29</v>
       </c>
       <c r="F1141" s="2" t="s">
-        <v>2055</v>
+        <v>2050</v>
       </c>
       <c r="G1141" s="2" t="s">
-        <v>2041</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="1142" spans="1:7" x14ac:dyDescent="0.45">
@@ -34949,19 +34942,19 @@
         <v>4</v>
       </c>
       <c r="C1142" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1142" s="2" t="s">
-        <v>2056</v>
+        <v>2051</v>
       </c>
       <c r="E1142" s="2">
         <v>30</v>
       </c>
       <c r="F1142" s="2" t="s">
-        <v>2057</v>
+        <v>2052</v>
       </c>
       <c r="G1142" s="2" t="s">
-        <v>2041</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="1143" spans="1:7" x14ac:dyDescent="0.45">
@@ -34972,19 +34965,19 @@
         <v>5</v>
       </c>
       <c r="C1143" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1143" s="2" t="s">
-        <v>2058</v>
+        <v>2053</v>
       </c>
       <c r="E1143" s="2">
         <v>31</v>
       </c>
       <c r="F1143" s="2" t="s">
-        <v>2059</v>
+        <v>2054</v>
       </c>
       <c r="G1143" s="2" t="s">
-        <v>2041</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="1144" spans="1:7" x14ac:dyDescent="0.45">
@@ -34995,19 +34988,19 @@
         <v>5</v>
       </c>
       <c r="C1144" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1144" s="2" t="s">
-        <v>2060</v>
+        <v>2055</v>
       </c>
       <c r="E1144" s="2">
         <v>32</v>
       </c>
       <c r="F1144" s="2" t="s">
-        <v>2061</v>
+        <v>2056</v>
       </c>
       <c r="G1144" s="2" t="s">
-        <v>2041</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="1145" spans="1:7" x14ac:dyDescent="0.45">
@@ -35018,19 +35011,19 @@
         <v>5</v>
       </c>
       <c r="C1145" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1145" s="2" t="s">
-        <v>2062</v>
+        <v>2057</v>
       </c>
       <c r="E1145" s="2">
         <v>33</v>
       </c>
       <c r="F1145" s="2" t="s">
-        <v>2063</v>
+        <v>2058</v>
       </c>
       <c r="G1145" s="2" t="s">
-        <v>2041</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="1146" spans="1:7" x14ac:dyDescent="0.45">
@@ -35041,19 +35034,19 @@
         <v>5</v>
       </c>
       <c r="C1146" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1146" s="2" t="s">
-        <v>2064</v>
+        <v>2059</v>
       </c>
       <c r="E1146" s="2">
         <v>34</v>
       </c>
       <c r="F1146" s="2" t="s">
-        <v>2065</v>
+        <v>2060</v>
       </c>
       <c r="G1146" s="2" t="s">
-        <v>2041</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="1147" spans="1:7" x14ac:dyDescent="0.45">
@@ -35064,19 +35057,19 @@
         <v>5</v>
       </c>
       <c r="C1147" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1147" s="2" t="s">
-        <v>2066</v>
+        <v>2061</v>
       </c>
       <c r="E1147" s="2">
         <v>35</v>
       </c>
       <c r="F1147" s="2" t="s">
-        <v>2067</v>
+        <v>2062</v>
       </c>
       <c r="G1147" s="2" t="s">
-        <v>2041</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="1148" spans="1:7" x14ac:dyDescent="0.45">
@@ -35087,19 +35080,19 @@
         <v>5</v>
       </c>
       <c r="C1148" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1148" s="2" t="s">
-        <v>2068</v>
+        <v>2063</v>
       </c>
       <c r="E1148" s="2">
         <v>36</v>
       </c>
       <c r="F1148" s="2" t="s">
-        <v>2069</v>
+        <v>2064</v>
       </c>
       <c r="G1148" s="2" t="s">
-        <v>2041</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="1149" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -35110,19 +35103,19 @@
         <v>5</v>
       </c>
       <c r="C1149" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1149" s="2" t="s">
-        <v>2070</v>
+        <v>2065</v>
       </c>
       <c r="E1149" s="2">
         <v>37</v>
       </c>
       <c r="F1149" s="2" t="s">
-        <v>2071</v>
+        <v>2066</v>
       </c>
       <c r="G1149" s="2" t="s">
-        <v>2041</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="1150" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -35133,19 +35126,19 @@
         <v>5</v>
       </c>
       <c r="C1150" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1150" s="2" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
       <c r="E1150" s="2">
         <v>38</v>
       </c>
       <c r="F1150" s="2" t="s">
-        <v>2073</v>
+        <v>2068</v>
       </c>
       <c r="G1150" s="2" t="s">
-        <v>2041</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="1151" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -35156,19 +35149,19 @@
         <v>5</v>
       </c>
       <c r="C1151" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1151" s="2" t="s">
-        <v>2074</v>
+        <v>2069</v>
       </c>
       <c r="E1151" s="2">
         <v>39</v>
       </c>
       <c r="F1151" s="2" t="s">
-        <v>2075</v>
+        <v>2070</v>
       </c>
       <c r="G1151" s="2" t="s">
-        <v>2041</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="1152" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -35179,19 +35172,19 @@
         <v>5</v>
       </c>
       <c r="C1152" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1152" s="2" t="s">
-        <v>2076</v>
+        <v>2071</v>
       </c>
       <c r="E1152" s="2">
         <v>40</v>
       </c>
       <c r="F1152" s="2" t="s">
-        <v>2077</v>
+        <v>2072</v>
       </c>
       <c r="G1152" s="2" t="s">
-        <v>2041</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="1153" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -35202,19 +35195,19 @@
         <v>5</v>
       </c>
       <c r="C1153" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1153" s="2" t="s">
-        <v>2078</v>
+        <v>2073</v>
       </c>
       <c r="E1153" s="2">
         <v>41</v>
       </c>
       <c r="F1153" s="2" t="s">
-        <v>2079</v>
+        <v>2074</v>
       </c>
       <c r="G1153" s="2" t="s">
-        <v>2079</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="1154" spans="1:7" x14ac:dyDescent="0.45">
@@ -35225,19 +35218,19 @@
         <v>5</v>
       </c>
       <c r="C1154" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1154" s="2" t="s">
-        <v>2080</v>
+        <v>2075</v>
       </c>
       <c r="E1154" s="2">
         <v>42</v>
       </c>
       <c r="F1154" s="2" t="s">
-        <v>2081</v>
+        <v>2076</v>
       </c>
       <c r="G1154" s="2" t="s">
-        <v>2041</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="1155" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -35248,19 +35241,19 @@
         <v>5</v>
       </c>
       <c r="C1155" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1155" s="2" t="s">
-        <v>2082</v>
+        <v>2077</v>
       </c>
       <c r="E1155" s="2">
         <v>43</v>
       </c>
       <c r="F1155" s="2" t="s">
-        <v>2083</v>
+        <v>2078</v>
       </c>
       <c r="G1155" s="2" t="s">
-        <v>2041</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="1156" spans="1:7" x14ac:dyDescent="0.45">
@@ -35271,19 +35264,19 @@
         <v>5</v>
       </c>
       <c r="C1156" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1156" s="2" t="s">
-        <v>2084</v>
+        <v>2079</v>
       </c>
       <c r="E1156" s="2">
         <v>44</v>
       </c>
       <c r="F1156" s="2" t="s">
-        <v>2085</v>
+        <v>2080</v>
       </c>
       <c r="G1156" s="2" t="s">
-        <v>2041</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="1157" spans="1:7" x14ac:dyDescent="0.45">
@@ -35294,19 +35287,19 @@
         <v>5</v>
       </c>
       <c r="C1157" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1157" s="2" t="s">
-        <v>2086</v>
+        <v>2081</v>
       </c>
       <c r="E1157" s="2">
         <v>45</v>
       </c>
       <c r="F1157" s="2" t="s">
-        <v>2087</v>
+        <v>2082</v>
       </c>
       <c r="G1157" s="2" t="s">
-        <v>2041</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="1158" spans="1:7" x14ac:dyDescent="0.45">
@@ -35317,19 +35310,19 @@
         <v>5</v>
       </c>
       <c r="C1158" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1158" s="2" t="s">
-        <v>2088</v>
+        <v>2083</v>
       </c>
       <c r="E1158" s="2">
         <v>46</v>
       </c>
       <c r="F1158" s="2" t="s">
-        <v>2089</v>
+        <v>2084</v>
       </c>
       <c r="G1158" s="2" t="s">
-        <v>2041</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="1159" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -35340,19 +35333,19 @@
         <v>5</v>
       </c>
       <c r="C1159" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1159" s="2" t="s">
-        <v>2090</v>
+        <v>2085</v>
       </c>
       <c r="E1159" s="2">
         <v>47</v>
       </c>
       <c r="F1159" s="2" t="s">
-        <v>2091</v>
+        <v>2086</v>
       </c>
       <c r="G1159" s="2" t="s">
-        <v>2041</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="1160" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -35363,19 +35356,19 @@
         <v>5</v>
       </c>
       <c r="C1160" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1160" s="2" t="s">
-        <v>2092</v>
+        <v>2087</v>
       </c>
       <c r="E1160" s="2">
         <v>48</v>
       </c>
       <c r="F1160" s="2" t="s">
-        <v>2093</v>
+        <v>2088</v>
       </c>
       <c r="G1160" s="2" t="s">
-        <v>2041</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="1161" spans="1:7" x14ac:dyDescent="0.45">
@@ -35386,19 +35379,19 @@
         <v>5</v>
       </c>
       <c r="C1161" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1161" s="2" t="s">
-        <v>2094</v>
+        <v>2089</v>
       </c>
       <c r="E1161" s="2">
         <v>49</v>
       </c>
       <c r="F1161" s="2" t="s">
-        <v>2095</v>
+        <v>2090</v>
       </c>
       <c r="G1161" s="2" t="s">
-        <v>2041</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="1162" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -35409,19 +35402,19 @@
         <v>5</v>
       </c>
       <c r="C1162" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1162" s="2" t="s">
-        <v>2096</v>
+        <v>2091</v>
       </c>
       <c r="E1162" s="2">
         <v>50</v>
       </c>
       <c r="F1162" s="2" t="s">
-        <v>2097</v>
+        <v>2092</v>
       </c>
       <c r="G1162" s="2" t="s">
-        <v>2041</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="1163" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -35432,19 +35425,19 @@
         <v>5</v>
       </c>
       <c r="C1163" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1163" s="2" t="s">
-        <v>2098</v>
+        <v>2093</v>
       </c>
       <c r="E1163" s="2">
         <v>51</v>
       </c>
       <c r="F1163" s="2" t="s">
-        <v>2099</v>
+        <v>2094</v>
       </c>
       <c r="G1163" s="2" t="s">
-        <v>2099</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="1164" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -35455,19 +35448,19 @@
         <v>5</v>
       </c>
       <c r="C1164" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1164" s="2" t="s">
-        <v>2100</v>
+        <v>2095</v>
       </c>
       <c r="E1164" s="2">
         <v>52</v>
       </c>
       <c r="F1164" s="2" t="s">
-        <v>2101</v>
+        <v>2096</v>
       </c>
       <c r="G1164" s="2" t="s">
-        <v>2041</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="1165" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -35478,19 +35471,19 @@
         <v>5</v>
       </c>
       <c r="C1165" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1165" s="2" t="s">
-        <v>2102</v>
+        <v>2097</v>
       </c>
       <c r="E1165" s="2">
         <v>53</v>
       </c>
       <c r="F1165" s="2" t="s">
-        <v>2103</v>
+        <v>2098</v>
       </c>
       <c r="G1165" s="2" t="s">
-        <v>2041</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="1166" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -35501,19 +35494,19 @@
         <v>5</v>
       </c>
       <c r="C1166" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1166" s="2" t="s">
-        <v>2104</v>
+        <v>2099</v>
       </c>
       <c r="E1166" s="2">
         <v>54</v>
       </c>
       <c r="F1166" s="2" t="s">
-        <v>2105</v>
+        <v>2100</v>
       </c>
       <c r="G1166" s="2" t="s">
-        <v>2041</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="1167" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -35524,19 +35517,19 @@
         <v>5</v>
       </c>
       <c r="C1167" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1167" s="2" t="s">
-        <v>2106</v>
+        <v>2101</v>
       </c>
       <c r="E1167" s="2">
         <v>55</v>
       </c>
       <c r="F1167" s="2" t="s">
-        <v>2107</v>
+        <v>2102</v>
       </c>
       <c r="G1167" s="2" t="s">
-        <v>2041</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="1168" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -35547,19 +35540,19 @@
         <v>5</v>
       </c>
       <c r="C1168" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1168" s="2" t="s">
-        <v>2108</v>
+        <v>2103</v>
       </c>
       <c r="E1168" s="2">
         <v>56</v>
       </c>
       <c r="F1168" s="2" t="s">
-        <v>2109</v>
+        <v>2104</v>
       </c>
       <c r="G1168" s="2" t="s">
-        <v>2041</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="1169" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -35570,19 +35563,19 @@
         <v>5</v>
       </c>
       <c r="C1169" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1169" s="2" t="s">
-        <v>2110</v>
+        <v>2105</v>
       </c>
       <c r="E1169" s="2">
         <v>57</v>
       </c>
       <c r="F1169" s="2" t="s">
-        <v>2111</v>
+        <v>2106</v>
       </c>
       <c r="G1169" s="2" t="s">
-        <v>2041</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="1170" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -35593,19 +35586,19 @@
         <v>5</v>
       </c>
       <c r="C1170" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1170" s="2" t="s">
-        <v>2112</v>
+        <v>2107</v>
       </c>
       <c r="E1170" s="2">
         <v>58</v>
       </c>
       <c r="F1170" s="2" t="s">
-        <v>2113</v>
+        <v>2108</v>
       </c>
       <c r="G1170" s="2" t="s">
-        <v>2041</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="1171" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -35616,19 +35609,19 @@
         <v>5</v>
       </c>
       <c r="C1171" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1171" s="2" t="s">
-        <v>2114</v>
+        <v>2109</v>
       </c>
       <c r="E1171" s="2">
         <v>59</v>
       </c>
       <c r="F1171" s="2" t="s">
-        <v>2115</v>
+        <v>2110</v>
       </c>
       <c r="G1171" s="2" t="s">
-        <v>2041</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="1172" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -35639,19 +35632,19 @@
         <v>5</v>
       </c>
       <c r="C1172" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="D1172" s="2" t="s">
-        <v>2116</v>
+        <v>2111</v>
       </c>
       <c r="E1172" s="2">
         <v>60</v>
       </c>
       <c r="F1172" s="2" t="s">
-        <v>2117</v>
+        <v>2112</v>
       </c>
       <c r="G1172" s="2" t="s">
-        <v>2041</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="1173" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -35662,19 +35655,19 @@
         <v>6</v>
       </c>
       <c r="C1173" t="s">
-        <v>2118</v>
+        <v>2113</v>
       </c>
       <c r="D1173" s="2" t="s">
-        <v>2119</v>
+        <v>2114</v>
       </c>
       <c r="E1173" s="2">
         <v>1</v>
       </c>
       <c r="F1173" s="2" t="s">
-        <v>2120</v>
+        <v>2115</v>
       </c>
       <c r="G1173" s="2" t="s">
-        <v>1952</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="1174" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -35685,19 +35678,19 @@
         <v>6</v>
       </c>
       <c r="C1174" t="s">
-        <v>2118</v>
+        <v>2113</v>
       </c>
       <c r="D1174" s="2" t="s">
-        <v>2121</v>
+        <v>2116</v>
       </c>
       <c r="E1174" s="2">
         <v>2</v>
       </c>
       <c r="F1174" s="2" t="s">
-        <v>2122</v>
+        <v>2117</v>
       </c>
       <c r="G1174" s="2" t="s">
-        <v>1952</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="1175" spans="1:7" x14ac:dyDescent="0.45">
@@ -35708,19 +35701,19 @@
         <v>6</v>
       </c>
       <c r="C1175" t="s">
+        <v>2113</v>
+      </c>
+      <c r="D1175" s="2" t="s">
         <v>2118</v>
-      </c>
-      <c r="D1175" s="2" t="s">
-        <v>2123</v>
       </c>
       <c r="E1175" s="2">
         <v>3</v>
       </c>
       <c r="F1175" s="2" t="s">
-        <v>2013</v>
+        <v>2008</v>
       </c>
       <c r="G1175" s="2" t="s">
-        <v>2124</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="1176" spans="1:7" x14ac:dyDescent="0.45">
@@ -35731,19 +35724,19 @@
         <v>6</v>
       </c>
       <c r="C1176" t="s">
-        <v>2118</v>
+        <v>2113</v>
       </c>
       <c r="D1176" s="2" t="s">
-        <v>2125</v>
+        <v>2120</v>
       </c>
       <c r="E1176" s="2">
         <v>4</v>
       </c>
       <c r="F1176" s="2" t="s">
-        <v>2126</v>
+        <v>2121</v>
       </c>
       <c r="G1176" s="2" t="s">
-        <v>2124</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="1177" spans="1:7" x14ac:dyDescent="0.45">
@@ -35754,19 +35747,19 @@
         <v>6</v>
       </c>
       <c r="C1177" t="s">
-        <v>2118</v>
+        <v>2113</v>
       </c>
       <c r="D1177" s="2" t="s">
-        <v>2127</v>
+        <v>2122</v>
       </c>
       <c r="E1177" s="2">
         <v>5</v>
       </c>
       <c r="F1177" s="2" t="s">
-        <v>2128</v>
+        <v>2123</v>
       </c>
       <c r="G1177" s="2" t="s">
-        <v>2129</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="1178" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -35777,19 +35770,19 @@
         <v>6</v>
       </c>
       <c r="C1178" t="s">
-        <v>2118</v>
+        <v>2113</v>
       </c>
       <c r="D1178" s="2" t="s">
-        <v>2130</v>
+        <v>2125</v>
       </c>
       <c r="E1178" s="2">
         <v>6</v>
       </c>
       <c r="F1178" s="2" t="s">
-        <v>2131</v>
+        <v>2126</v>
       </c>
       <c r="G1178" s="2" t="s">
-        <v>2132</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="1179" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -35800,19 +35793,19 @@
         <v>6</v>
       </c>
       <c r="C1179" t="s">
-        <v>2118</v>
+        <v>2113</v>
       </c>
       <c r="D1179" s="2" t="s">
-        <v>2133</v>
+        <v>2128</v>
       </c>
       <c r="E1179" s="2">
         <v>7</v>
       </c>
       <c r="F1179" s="2" t="s">
-        <v>2134</v>
+        <v>2129</v>
       </c>
       <c r="G1179" s="2" t="s">
-        <v>1952</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="1180" spans="1:7" x14ac:dyDescent="0.45">
@@ -35823,19 +35816,19 @@
         <v>6</v>
       </c>
       <c r="C1180" t="s">
-        <v>2118</v>
+        <v>2113</v>
       </c>
       <c r="D1180" s="2" t="s">
-        <v>2135</v>
+        <v>2130</v>
       </c>
       <c r="E1180" s="2">
         <v>8</v>
       </c>
       <c r="F1180" s="2" t="s">
-        <v>2136</v>
+        <v>2131</v>
       </c>
       <c r="G1180" s="2" t="s">
-        <v>1952</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="1181" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -35846,19 +35839,19 @@
         <v>6</v>
       </c>
       <c r="C1181" t="s">
-        <v>2118</v>
+        <v>2113</v>
       </c>
       <c r="D1181" s="2" t="s">
-        <v>2137</v>
+        <v>2132</v>
       </c>
       <c r="E1181" s="2">
         <v>9</v>
       </c>
       <c r="F1181" s="2" t="s">
-        <v>2138</v>
+        <v>2133</v>
       </c>
       <c r="G1181" s="2" t="s">
-        <v>1952</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="1182" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -35869,19 +35862,19 @@
         <v>6</v>
       </c>
       <c r="C1182" t="s">
-        <v>2118</v>
+        <v>2113</v>
       </c>
       <c r="D1182" s="2" t="s">
-        <v>2139</v>
+        <v>2134</v>
       </c>
       <c r="E1182" s="2">
         <v>10</v>
       </c>
       <c r="F1182" s="2" t="s">
-        <v>2140</v>
+        <v>2135</v>
       </c>
       <c r="G1182" s="2" t="s">
-        <v>2141</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="1183" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -35892,19 +35885,19 @@
         <v>6</v>
       </c>
       <c r="C1183" t="s">
-        <v>2118</v>
+        <v>2113</v>
       </c>
       <c r="D1183" s="2" t="s">
-        <v>2142</v>
+        <v>2137</v>
       </c>
       <c r="E1183" s="2">
         <v>11</v>
       </c>
       <c r="F1183" s="2" t="s">
-        <v>2143</v>
+        <v>2138</v>
       </c>
       <c r="G1183" s="2" t="s">
-        <v>2144</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="1184" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -35915,19 +35908,19 @@
         <v>6</v>
       </c>
       <c r="C1184" t="s">
-        <v>2118</v>
+        <v>2113</v>
       </c>
       <c r="D1184" s="2" t="s">
-        <v>2145</v>
+        <v>2140</v>
       </c>
       <c r="E1184" s="2">
         <v>12</v>
       </c>
       <c r="F1184" s="2" t="s">
-        <v>2146</v>
+        <v>2141</v>
       </c>
       <c r="G1184" s="2" t="s">
-        <v>1952</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="1185" spans="1:7" x14ac:dyDescent="0.45">
@@ -35938,19 +35931,19 @@
         <v>6</v>
       </c>
       <c r="C1185" t="s">
-        <v>2118</v>
+        <v>2113</v>
       </c>
       <c r="D1185" s="2" t="s">
-        <v>2147</v>
+        <v>2142</v>
       </c>
       <c r="E1185" s="2">
         <v>13</v>
       </c>
       <c r="F1185" s="2" t="s">
-        <v>2148</v>
+        <v>2143</v>
       </c>
       <c r="G1185" s="2" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="1186" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -35961,19 +35954,19 @@
         <v>6</v>
       </c>
       <c r="C1186" t="s">
-        <v>2118</v>
+        <v>2113</v>
       </c>
       <c r="D1186" s="2" t="s">
-        <v>2150</v>
+        <v>2145</v>
       </c>
       <c r="E1186" s="2">
         <v>14</v>
       </c>
       <c r="F1186" s="2" t="s">
-        <v>2151</v>
+        <v>2146</v>
       </c>
       <c r="G1186" s="2" t="s">
-        <v>2152</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="1187" spans="1:7" x14ac:dyDescent="0.45">
@@ -35984,19 +35977,19 @@
         <v>6</v>
       </c>
       <c r="C1187" t="s">
-        <v>2118</v>
+        <v>2113</v>
       </c>
       <c r="D1187" s="2" t="s">
-        <v>2153</v>
+        <v>2148</v>
       </c>
       <c r="E1187" s="2">
         <v>15</v>
       </c>
       <c r="F1187" s="2" t="s">
-        <v>2154</v>
+        <v>2149</v>
       </c>
       <c r="G1187" s="2" t="s">
-        <v>2155</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="1188" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -36007,19 +36000,19 @@
         <v>6</v>
       </c>
       <c r="C1188" t="s">
-        <v>2118</v>
+        <v>2113</v>
       </c>
       <c r="D1188" s="2" t="s">
-        <v>2156</v>
+        <v>2151</v>
       </c>
       <c r="E1188" s="2">
         <v>16</v>
       </c>
       <c r="F1188" s="2" t="s">
-        <v>2157</v>
+        <v>2152</v>
       </c>
       <c r="G1188" s="2" t="s">
-        <v>2158</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="1189" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -36030,19 +36023,19 @@
         <v>6</v>
       </c>
       <c r="C1189" t="s">
-        <v>2118</v>
+        <v>2113</v>
       </c>
       <c r="D1189" s="2" t="s">
-        <v>2159</v>
+        <v>2154</v>
       </c>
       <c r="E1189" s="2">
         <v>17</v>
       </c>
       <c r="F1189" s="2" t="s">
-        <v>2160</v>
+        <v>2155</v>
       </c>
       <c r="G1189" s="2" t="s">
-        <v>1952</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="1190" spans="1:7" x14ac:dyDescent="0.45">
@@ -36053,19 +36046,19 @@
         <v>6</v>
       </c>
       <c r="C1190" t="s">
-        <v>2118</v>
+        <v>2113</v>
       </c>
       <c r="D1190" s="2" t="s">
-        <v>2161</v>
+        <v>2156</v>
       </c>
       <c r="E1190" s="2">
         <v>18</v>
       </c>
       <c r="F1190" s="2" t="s">
-        <v>2162</v>
+        <v>2157</v>
       </c>
       <c r="G1190" s="2" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="1191" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -36076,19 +36069,19 @@
         <v>6</v>
       </c>
       <c r="C1191" t="s">
-        <v>2118</v>
+        <v>2113</v>
       </c>
       <c r="D1191" s="2" t="s">
-        <v>2163</v>
+        <v>2158</v>
       </c>
       <c r="E1191" s="2">
         <v>19</v>
       </c>
       <c r="F1191" s="2" t="s">
-        <v>2164</v>
+        <v>2159</v>
       </c>
       <c r="G1191" s="2" t="s">
-        <v>2165</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="1192" spans="1:7" x14ac:dyDescent="0.45">
@@ -36099,19 +36092,19 @@
         <v>6</v>
       </c>
       <c r="C1192" t="s">
-        <v>2118</v>
+        <v>2113</v>
       </c>
       <c r="D1192" s="2" t="s">
-        <v>2166</v>
+        <v>2161</v>
       </c>
       <c r="E1192" s="2">
         <v>20</v>
       </c>
       <c r="F1192" s="2" t="s">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="G1192" s="2" t="s">
-        <v>2167</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="1193" spans="1:7" x14ac:dyDescent="0.45">
@@ -36122,19 +36115,19 @@
         <v>6</v>
       </c>
       <c r="C1193" t="s">
-        <v>2118</v>
+        <v>2113</v>
       </c>
       <c r="D1193" s="2" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
       <c r="E1193" s="2">
         <v>21</v>
       </c>
       <c r="F1193" s="2" t="s">
-        <v>2169</v>
+        <v>2164</v>
       </c>
       <c r="G1193" s="2" t="s">
-        <v>2170</v>
+        <v>2165</v>
       </c>
     </row>
     <row r="1194" spans="1:7" x14ac:dyDescent="0.45">
@@ -36145,19 +36138,19 @@
         <v>6</v>
       </c>
       <c r="C1194" t="s">
-        <v>2118</v>
+        <v>2113</v>
       </c>
       <c r="D1194" s="2" t="s">
-        <v>2171</v>
+        <v>2166</v>
       </c>
       <c r="E1194" s="2">
         <v>22</v>
       </c>
       <c r="F1194" s="2" t="s">
-        <v>2172</v>
+        <v>2167</v>
       </c>
       <c r="G1194" s="2" t="s">
-        <v>2173</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1195" spans="1:7" x14ac:dyDescent="0.45">
@@ -36168,19 +36161,19 @@
         <v>6</v>
       </c>
       <c r="C1195" t="s">
-        <v>2118</v>
+        <v>2113</v>
       </c>
       <c r="D1195" s="2" t="s">
-        <v>2174</v>
+        <v>2169</v>
       </c>
       <c r="E1195" s="2">
         <v>23</v>
       </c>
       <c r="F1195" s="2" t="s">
-        <v>2175</v>
+        <v>2170</v>
       </c>
       <c r="G1195" s="2" t="s">
-        <v>2167</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="1196" spans="1:7" x14ac:dyDescent="0.45">
@@ -36191,19 +36184,19 @@
         <v>6</v>
       </c>
       <c r="C1196" t="s">
-        <v>2118</v>
+        <v>2113</v>
       </c>
       <c r="D1196" s="2" t="s">
-        <v>2176</v>
+        <v>2171</v>
       </c>
       <c r="E1196" s="2">
         <v>24</v>
       </c>
       <c r="F1196" s="2" t="s">
-        <v>2177</v>
+        <v>2172</v>
       </c>
       <c r="G1196" s="2" t="s">
-        <v>2178</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="1197" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -36214,19 +36207,19 @@
         <v>6</v>
       </c>
       <c r="C1197" t="s">
-        <v>2118</v>
+        <v>2113</v>
       </c>
       <c r="D1197" s="2" t="s">
-        <v>2179</v>
+        <v>2174</v>
       </c>
       <c r="E1197" s="2">
         <v>25</v>
       </c>
       <c r="F1197" s="2" t="s">
-        <v>2180</v>
+        <v>2175</v>
       </c>
       <c r="G1197" s="2" t="s">
-        <v>2181</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="1198" spans="1:7" x14ac:dyDescent="0.45">
@@ -36237,19 +36230,19 @@
         <v>6</v>
       </c>
       <c r="C1198" t="s">
-        <v>2118</v>
+        <v>2113</v>
       </c>
       <c r="D1198" s="2" t="s">
-        <v>2182</v>
+        <v>2177</v>
       </c>
       <c r="E1198" s="2">
         <v>26</v>
       </c>
       <c r="F1198" s="2" t="s">
-        <v>2183</v>
+        <v>2178</v>
       </c>
       <c r="G1198" s="2" t="s">
-        <v>2184</v>
+        <v>2179</v>
       </c>
     </row>
     <row r="1199" spans="1:7" x14ac:dyDescent="0.45">
@@ -36260,19 +36253,19 @@
         <v>6</v>
       </c>
       <c r="C1199" t="s">
-        <v>2118</v>
+        <v>2113</v>
       </c>
       <c r="D1199" s="2" t="s">
-        <v>2185</v>
+        <v>2180</v>
       </c>
       <c r="E1199" s="2">
         <v>27</v>
       </c>
       <c r="F1199" s="2" t="s">
-        <v>2186</v>
+        <v>2181</v>
       </c>
       <c r="G1199" s="2" t="s">
-        <v>2187</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="1200" spans="1:7" x14ac:dyDescent="0.45">
@@ -36283,19 +36276,19 @@
         <v>6</v>
       </c>
       <c r="C1200" t="s">
-        <v>2118</v>
+        <v>2113</v>
       </c>
       <c r="D1200" s="2" t="s">
-        <v>2188</v>
+        <v>2183</v>
       </c>
       <c r="E1200" s="2">
         <v>28</v>
       </c>
       <c r="F1200" s="2" t="s">
-        <v>2189</v>
+        <v>2184</v>
       </c>
       <c r="G1200" s="2" t="s">
-        <v>2190</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="1201" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -36306,19 +36299,19 @@
         <v>6</v>
       </c>
       <c r="C1201" t="s">
-        <v>2118</v>
+        <v>2113</v>
       </c>
       <c r="D1201" s="2" t="s">
-        <v>2191</v>
+        <v>2186</v>
       </c>
       <c r="E1201" s="2">
         <v>29</v>
       </c>
       <c r="F1201" s="2" t="s">
-        <v>2192</v>
+        <v>2187</v>
       </c>
       <c r="G1201" s="2" t="s">
-        <v>2190</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="1202" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -36329,19 +36322,19 @@
         <v>6</v>
       </c>
       <c r="C1202" t="s">
-        <v>2118</v>
+        <v>2113</v>
       </c>
       <c r="D1202" s="2" t="s">
-        <v>2193</v>
+        <v>2188</v>
       </c>
       <c r="E1202" s="2">
         <v>30</v>
       </c>
       <c r="F1202" s="2" t="s">
-        <v>2194</v>
+        <v>2189</v>
       </c>
       <c r="G1202" s="2" t="s">
-        <v>2195</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="1203" spans="1:7" x14ac:dyDescent="0.45">
@@ -36352,19 +36345,19 @@
         <v>6</v>
       </c>
       <c r="C1203" t="s">
-        <v>2118</v>
+        <v>2113</v>
       </c>
       <c r="D1203" s="2" t="s">
-        <v>2196</v>
+        <v>2191</v>
       </c>
       <c r="E1203" s="2">
         <v>31</v>
       </c>
       <c r="F1203" s="2" t="s">
-        <v>2197</v>
+        <v>2192</v>
       </c>
       <c r="G1203" s="2" t="s">
-        <v>2198</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="1204" spans="1:7" ht="68" customHeight="1" x14ac:dyDescent="0.45">
@@ -36375,19 +36368,19 @@
         <v>6</v>
       </c>
       <c r="C1204" t="s">
-        <v>2118</v>
+        <v>2113</v>
       </c>
       <c r="D1204" s="2" t="s">
-        <v>2199</v>
+        <v>2194</v>
       </c>
       <c r="E1204" s="2">
         <v>32</v>
       </c>
       <c r="F1204" s="2" t="s">
-        <v>2200</v>
+        <v>2195</v>
       </c>
       <c r="G1204" s="2" t="s">
-        <v>2201</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="1205" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -36398,19 +36391,19 @@
         <v>6</v>
       </c>
       <c r="C1205" t="s">
-        <v>2118</v>
+        <v>2113</v>
       </c>
       <c r="D1205" s="2" t="s">
-        <v>2202</v>
+        <v>2197</v>
       </c>
       <c r="E1205" s="2">
         <v>33</v>
       </c>
       <c r="F1205" s="2" t="s">
-        <v>2203</v>
+        <v>2198</v>
       </c>
       <c r="G1205" s="2" t="s">
-        <v>1952</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="1206" spans="1:7" x14ac:dyDescent="0.45">
@@ -36421,19 +36414,19 @@
         <v>6</v>
       </c>
       <c r="C1206" t="s">
-        <v>2118</v>
+        <v>2113</v>
       </c>
       <c r="D1206" s="2" t="s">
-        <v>2204</v>
+        <v>2199</v>
       </c>
       <c r="E1206" s="2">
         <v>34</v>
       </c>
       <c r="F1206" s="2" t="s">
-        <v>2013</v>
+        <v>2008</v>
       </c>
       <c r="G1206" s="2" t="s">
-        <v>2167</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="1207" spans="1:7" x14ac:dyDescent="0.45">
@@ -36444,19 +36437,19 @@
         <v>6</v>
       </c>
       <c r="C1207" t="s">
-        <v>2118</v>
+        <v>2113</v>
       </c>
       <c r="D1207" s="2" t="s">
-        <v>2205</v>
+        <v>2200</v>
       </c>
       <c r="E1207" s="2">
         <v>35</v>
       </c>
       <c r="F1207" s="2" t="s">
-        <v>2206</v>
+        <v>2201</v>
       </c>
       <c r="G1207" s="2" t="s">
-        <v>1952</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="1208" spans="1:7" x14ac:dyDescent="0.45">
@@ -36467,19 +36460,19 @@
         <v>6</v>
       </c>
       <c r="C1208" t="s">
-        <v>2118</v>
+        <v>2113</v>
       </c>
       <c r="D1208" s="2" t="s">
-        <v>2207</v>
+        <v>2202</v>
       </c>
       <c r="E1208" s="2">
         <v>36</v>
       </c>
       <c r="F1208" s="2" t="s">
-        <v>2208</v>
+        <v>2203</v>
       </c>
       <c r="G1208" s="2" t="s">
-        <v>1952</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="1209" spans="1:7" x14ac:dyDescent="0.45">
@@ -36490,19 +36483,19 @@
         <v>6</v>
       </c>
       <c r="C1209" t="s">
-        <v>2118</v>
+        <v>2113</v>
       </c>
       <c r="D1209" s="2" t="s">
-        <v>2209</v>
+        <v>2204</v>
       </c>
       <c r="E1209" s="2">
         <v>37</v>
       </c>
       <c r="F1209" s="2" t="s">
-        <v>2210</v>
+        <v>2205</v>
       </c>
       <c r="G1209" s="2" t="s">
-        <v>2211</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="1210" spans="1:7" x14ac:dyDescent="0.45">
@@ -36513,19 +36506,19 @@
         <v>6</v>
       </c>
       <c r="C1210" t="s">
-        <v>2118</v>
+        <v>2113</v>
       </c>
       <c r="D1210" s="2" t="s">
-        <v>2212</v>
+        <v>2207</v>
       </c>
       <c r="E1210" s="2">
         <v>38</v>
       </c>
       <c r="F1210" s="2" t="s">
-        <v>2213</v>
+        <v>2208</v>
       </c>
       <c r="G1210" s="2" t="s">
-        <v>2152</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="1211" spans="1:7" x14ac:dyDescent="0.45">
@@ -36536,19 +36529,19 @@
         <v>6</v>
       </c>
       <c r="C1211" t="s">
-        <v>2118</v>
+        <v>2113</v>
       </c>
       <c r="D1211" s="2" t="s">
-        <v>2214</v>
+        <v>2209</v>
       </c>
       <c r="E1211" s="2">
         <v>39</v>
       </c>
       <c r="F1211" s="7" t="s">
-        <v>2215</v>
+        <v>2210</v>
       </c>
       <c r="G1211" s="2" t="s">
-        <v>2216</v>
+        <v>2211</v>
       </c>
     </row>
     <row r="1212" spans="1:7" x14ac:dyDescent="0.45">
@@ -36559,7 +36552,7 @@
         <v>6</v>
       </c>
       <c r="C1212" t="s">
-        <v>2118</v>
+        <v>2113</v>
       </c>
       <c r="D1212" s="11" t="s">
         <v>1217</v>
@@ -36582,19 +36575,19 @@
         <v>1</v>
       </c>
       <c r="C1213" t="s">
-        <v>2217</v>
+        <v>2212</v>
       </c>
       <c r="D1213" s="2" t="s">
-        <v>2218</v>
+        <v>2213</v>
       </c>
       <c r="E1213" s="2">
         <v>1</v>
       </c>
       <c r="F1213" s="2" t="s">
-        <v>2219</v>
+        <v>2214</v>
       </c>
       <c r="G1213" s="2" t="s">
-        <v>2220</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="1214" spans="1:7" x14ac:dyDescent="0.45">
@@ -36605,19 +36598,19 @@
         <v>1</v>
       </c>
       <c r="C1214" t="s">
-        <v>2217</v>
+        <v>2212</v>
       </c>
       <c r="D1214" s="2" t="s">
-        <v>2221</v>
+        <v>2216</v>
       </c>
       <c r="E1214" s="2">
         <v>2</v>
       </c>
       <c r="F1214" s="2" t="s">
-        <v>2222</v>
+        <v>2217</v>
       </c>
       <c r="G1214" s="2" t="s">
-        <v>2220</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="1215" spans="1:7" x14ac:dyDescent="0.45">
@@ -36628,19 +36621,19 @@
         <v>1</v>
       </c>
       <c r="C1215" t="s">
-        <v>2217</v>
+        <v>2212</v>
       </c>
       <c r="D1215" s="2" t="s">
-        <v>2223</v>
+        <v>2218</v>
       </c>
       <c r="E1215" s="2">
         <v>3</v>
       </c>
       <c r="F1215" s="2" t="s">
-        <v>2224</v>
+        <v>2219</v>
       </c>
       <c r="G1215" s="2" t="s">
-        <v>2220</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="1216" spans="1:7" x14ac:dyDescent="0.45">
@@ -36651,19 +36644,19 @@
         <v>1</v>
       </c>
       <c r="C1216" t="s">
-        <v>2217</v>
+        <v>2212</v>
       </c>
       <c r="D1216" s="2" t="s">
-        <v>2225</v>
+        <v>2220</v>
       </c>
       <c r="E1216" s="2">
         <v>4</v>
       </c>
       <c r="F1216" s="2" t="s">
-        <v>2226</v>
+        <v>2221</v>
       </c>
       <c r="G1216" s="2" t="s">
-        <v>2220</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="1217" spans="1:7" x14ac:dyDescent="0.45">
@@ -36674,19 +36667,19 @@
         <v>1</v>
       </c>
       <c r="C1217" t="s">
-        <v>2217</v>
+        <v>2212</v>
       </c>
       <c r="D1217" s="2" t="s">
-        <v>2227</v>
+        <v>2222</v>
       </c>
       <c r="E1217" s="2">
         <v>5</v>
       </c>
       <c r="F1217" s="2" t="s">
-        <v>2228</v>
+        <v>2223</v>
       </c>
       <c r="G1217" s="2" t="s">
-        <v>2220</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="1218" spans="1:7" x14ac:dyDescent="0.45">
@@ -36697,19 +36690,19 @@
         <v>1</v>
       </c>
       <c r="C1218" t="s">
-        <v>2217</v>
+        <v>2212</v>
       </c>
       <c r="D1218" s="2" t="s">
-        <v>2229</v>
+        <v>2224</v>
       </c>
       <c r="E1218" s="2">
         <v>6</v>
       </c>
       <c r="F1218" s="2" t="s">
-        <v>2230</v>
+        <v>2225</v>
       </c>
       <c r="G1218" s="2" t="s">
-        <v>2220</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="1219" spans="1:7" x14ac:dyDescent="0.45">
@@ -36720,19 +36713,19 @@
         <v>1</v>
       </c>
       <c r="C1219" t="s">
-        <v>2217</v>
+        <v>2212</v>
       </c>
       <c r="D1219" s="2" t="s">
-        <v>2231</v>
+        <v>2226</v>
       </c>
       <c r="E1219" s="2">
         <v>7</v>
       </c>
       <c r="F1219" s="2" t="s">
-        <v>2232</v>
+        <v>2227</v>
       </c>
       <c r="G1219" s="2" t="s">
-        <v>2220</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="1220" spans="1:7" x14ac:dyDescent="0.45">
@@ -36743,19 +36736,19 @@
         <v>1</v>
       </c>
       <c r="C1220" t="s">
-        <v>2217</v>
+        <v>2212</v>
       </c>
       <c r="D1220" s="2" t="s">
-        <v>2233</v>
+        <v>2228</v>
       </c>
       <c r="E1220" s="2">
         <v>8</v>
       </c>
       <c r="F1220" s="2" t="s">
-        <v>2234</v>
+        <v>2229</v>
       </c>
       <c r="G1220" s="2" t="s">
-        <v>2220</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="1221" spans="1:7" x14ac:dyDescent="0.45">
@@ -36766,19 +36759,19 @@
         <v>1</v>
       </c>
       <c r="C1221" t="s">
-        <v>2217</v>
+        <v>2212</v>
       </c>
       <c r="D1221" s="2" t="s">
-        <v>2235</v>
+        <v>2230</v>
       </c>
       <c r="E1221" s="2">
         <v>9</v>
       </c>
       <c r="F1221" s="2" t="s">
-        <v>2236</v>
+        <v>2231</v>
       </c>
       <c r="G1221" s="2" t="s">
-        <v>2220</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="1222" spans="1:7" x14ac:dyDescent="0.45">
@@ -36789,19 +36782,19 @@
         <v>1</v>
       </c>
       <c r="C1222" t="s">
-        <v>2217</v>
+        <v>2212</v>
       </c>
       <c r="D1222" s="2" t="s">
-        <v>2237</v>
+        <v>2232</v>
       </c>
       <c r="E1222" s="2">
         <v>10</v>
       </c>
       <c r="F1222" s="2" t="s">
-        <v>2224</v>
+        <v>2219</v>
       </c>
       <c r="G1222" s="2" t="s">
-        <v>2220</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="1223" spans="1:7" x14ac:dyDescent="0.45">
@@ -36812,19 +36805,19 @@
         <v>1</v>
       </c>
       <c r="C1223" t="s">
-        <v>2217</v>
+        <v>2212</v>
       </c>
       <c r="D1223" s="2" t="s">
-        <v>2238</v>
+        <v>2233</v>
       </c>
       <c r="E1223" s="2">
         <v>11</v>
       </c>
       <c r="F1223" s="2" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="G1223" s="2" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="1224" spans="1:7" x14ac:dyDescent="0.45">
@@ -36835,19 +36828,19 @@
         <v>1</v>
       </c>
       <c r="C1224" t="s">
-        <v>2217</v>
+        <v>2212</v>
       </c>
       <c r="D1224" s="2" t="s">
-        <v>2240</v>
+        <v>2235</v>
       </c>
       <c r="E1224" s="2">
         <v>12</v>
       </c>
       <c r="F1224" s="2" t="s">
-        <v>2241</v>
+        <v>2236</v>
       </c>
       <c r="G1224" s="2" t="s">
-        <v>2220</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="1225" spans="1:7" x14ac:dyDescent="0.45">
@@ -36858,19 +36851,19 @@
         <v>1</v>
       </c>
       <c r="C1225" t="s">
-        <v>2217</v>
+        <v>2212</v>
       </c>
       <c r="D1225" s="2" t="s">
-        <v>2242</v>
+        <v>2237</v>
       </c>
       <c r="E1225" s="2">
         <v>13</v>
       </c>
       <c r="F1225" s="2" t="s">
-        <v>2243</v>
+        <v>2238</v>
       </c>
       <c r="G1225" s="2" t="s">
-        <v>2220</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="1226" spans="1:7" x14ac:dyDescent="0.45">
@@ -36881,19 +36874,19 @@
         <v>1</v>
       </c>
       <c r="C1226" t="s">
-        <v>2217</v>
+        <v>2212</v>
       </c>
       <c r="D1226" s="2" t="s">
-        <v>2244</v>
+        <v>2239</v>
       </c>
       <c r="E1226" s="2">
         <v>14</v>
       </c>
       <c r="F1226" s="2" t="s">
-        <v>2226</v>
+        <v>2221</v>
       </c>
       <c r="G1226" s="2" t="s">
-        <v>2220</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="1227" spans="1:7" x14ac:dyDescent="0.45">
@@ -36904,19 +36897,19 @@
         <v>1</v>
       </c>
       <c r="C1227" t="s">
-        <v>2217</v>
+        <v>2212</v>
       </c>
       <c r="D1227" s="2" t="s">
-        <v>2245</v>
+        <v>2240</v>
       </c>
       <c r="E1227" s="2">
         <v>15</v>
       </c>
       <c r="F1227" s="2" t="s">
-        <v>2246</v>
+        <v>2241</v>
       </c>
       <c r="G1227" s="2" t="s">
-        <v>2220</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="1228" spans="1:7" x14ac:dyDescent="0.45">
@@ -36927,19 +36920,19 @@
         <v>1</v>
       </c>
       <c r="C1228" t="s">
-        <v>2217</v>
+        <v>2212</v>
       </c>
       <c r="D1228" s="2" t="s">
-        <v>2247</v>
+        <v>2242</v>
       </c>
       <c r="E1228" s="2">
         <v>16</v>
       </c>
       <c r="F1228" s="2" t="s">
-        <v>2239</v>
+        <v>2234</v>
       </c>
       <c r="G1228" s="2" t="s">
-        <v>2220</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="1229" spans="1:7" x14ac:dyDescent="0.45">
@@ -36950,19 +36943,19 @@
         <v>1</v>
       </c>
       <c r="C1229" t="s">
-        <v>2217</v>
+        <v>2212</v>
       </c>
       <c r="D1229" s="2" t="s">
-        <v>2248</v>
+        <v>2243</v>
       </c>
       <c r="E1229" s="2">
         <v>17</v>
       </c>
       <c r="F1229" s="2" t="s">
-        <v>2249</v>
+        <v>2244</v>
       </c>
       <c r="G1229" s="2" t="s">
-        <v>2220</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="1230" spans="1:7" x14ac:dyDescent="0.45">
@@ -36973,19 +36966,19 @@
         <v>1</v>
       </c>
       <c r="C1230" t="s">
-        <v>2217</v>
+        <v>2212</v>
       </c>
       <c r="D1230" s="2" t="s">
-        <v>2250</v>
+        <v>2245</v>
       </c>
       <c r="E1230" s="2">
         <v>18</v>
       </c>
       <c r="F1230" s="2" t="s">
-        <v>2251</v>
+        <v>2246</v>
       </c>
       <c r="G1230" s="2" t="s">
-        <v>2220</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="1231" spans="1:7" x14ac:dyDescent="0.45">
@@ -36996,19 +36989,19 @@
         <v>1</v>
       </c>
       <c r="C1231" t="s">
-        <v>2217</v>
+        <v>2212</v>
       </c>
       <c r="D1231" s="2" t="s">
-        <v>2252</v>
+        <v>2247</v>
       </c>
       <c r="E1231" s="2">
         <v>19</v>
       </c>
       <c r="F1231" s="2" t="s">
-        <v>2253</v>
+        <v>2248</v>
       </c>
       <c r="G1231" s="2" t="s">
-        <v>2220</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="1232" spans="1:7" x14ac:dyDescent="0.45">
@@ -37019,19 +37012,19 @@
         <v>1</v>
       </c>
       <c r="C1232" t="s">
-        <v>2217</v>
+        <v>2212</v>
       </c>
       <c r="D1232" s="2" t="s">
-        <v>2254</v>
+        <v>2249</v>
       </c>
       <c r="E1232" s="2">
         <v>20</v>
       </c>
       <c r="F1232" s="2" t="s">
-        <v>2219</v>
+        <v>2214</v>
       </c>
       <c r="G1232" s="2" t="s">
-        <v>2220</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="1233" spans="1:7" x14ac:dyDescent="0.45">
@@ -37042,10 +37035,10 @@
         <v>2</v>
       </c>
       <c r="C1233" t="s">
-        <v>2255</v>
+        <v>2250</v>
       </c>
       <c r="D1233" s="2" t="s">
-        <v>2256</v>
+        <v>2251</v>
       </c>
       <c r="E1233" s="2">
         <v>1</v>
@@ -37054,7 +37047,7 @@
         <v>14</v>
       </c>
       <c r="G1233" s="2" t="s">
-        <v>2257</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="1234" spans="1:7" x14ac:dyDescent="0.45">
@@ -37065,10 +37058,10 @@
         <v>2</v>
       </c>
       <c r="C1234" t="s">
-        <v>2255</v>
+        <v>2250</v>
       </c>
       <c r="D1234" s="2" t="s">
-        <v>2258</v>
+        <v>2253</v>
       </c>
       <c r="E1234" s="2">
         <v>2</v>
@@ -37077,7 +37070,7 @@
         <v>1177</v>
       </c>
       <c r="G1234" s="2" t="s">
-        <v>2257</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="1235" spans="1:7" x14ac:dyDescent="0.45">
@@ -37088,10 +37081,10 @@
         <v>2</v>
       </c>
       <c r="C1235" t="s">
-        <v>2255</v>
+        <v>2250</v>
       </c>
       <c r="D1235" s="2" t="s">
-        <v>2259</v>
+        <v>2254</v>
       </c>
       <c r="E1235" s="2">
         <v>3</v>
@@ -37100,7 +37093,7 @@
         <v>530</v>
       </c>
       <c r="G1235" s="2" t="s">
-        <v>2257</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="1236" spans="1:7" x14ac:dyDescent="0.45">
@@ -37111,10 +37104,10 @@
         <v>2</v>
       </c>
       <c r="C1236" t="s">
+        <v>2250</v>
+      </c>
+      <c r="D1236" s="2" t="s">
         <v>2255</v>
-      </c>
-      <c r="D1236" s="2" t="s">
-        <v>2260</v>
       </c>
       <c r="E1236" s="2">
         <v>4</v>
@@ -37123,7 +37116,7 @@
         <v>888</v>
       </c>
       <c r="G1236" s="2" t="s">
-        <v>2257</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="1237" spans="1:7" x14ac:dyDescent="0.45">
@@ -37134,10 +37127,10 @@
         <v>2</v>
       </c>
       <c r="C1237" t="s">
-        <v>2255</v>
+        <v>2250</v>
       </c>
       <c r="D1237" s="2" t="s">
-        <v>2261</v>
+        <v>2256</v>
       </c>
       <c r="E1237" s="2">
         <v>5</v>
@@ -37146,7 +37139,7 @@
         <v>390</v>
       </c>
       <c r="G1237" s="2" t="s">
-        <v>2257</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="1238" spans="1:7" x14ac:dyDescent="0.45">
@@ -37157,10 +37150,10 @@
         <v>2</v>
       </c>
       <c r="C1238" t="s">
-        <v>2255</v>
+        <v>2250</v>
       </c>
       <c r="D1238" s="2" t="s">
-        <v>2262</v>
+        <v>2257</v>
       </c>
       <c r="E1238" s="2">
         <v>6</v>
@@ -37169,7 +37162,7 @@
         <v>888</v>
       </c>
       <c r="G1238" s="2" t="s">
-        <v>2257</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="1239" spans="1:7" x14ac:dyDescent="0.45">
@@ -37180,10 +37173,10 @@
         <v>2</v>
       </c>
       <c r="C1239" t="s">
-        <v>2255</v>
+        <v>2250</v>
       </c>
       <c r="D1239" s="2" t="s">
-        <v>2263</v>
+        <v>2258</v>
       </c>
       <c r="E1239" s="2">
         <v>7</v>
@@ -37192,7 +37185,7 @@
         <v>888</v>
       </c>
       <c r="G1239" s="2" t="s">
-        <v>2257</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="1240" spans="1:7" x14ac:dyDescent="0.45">
@@ -37203,10 +37196,10 @@
         <v>2</v>
       </c>
       <c r="C1240" t="s">
-        <v>2255</v>
+        <v>2250</v>
       </c>
       <c r="D1240" s="2" t="s">
-        <v>2264</v>
+        <v>2259</v>
       </c>
       <c r="E1240" s="2">
         <v>8</v>
@@ -37215,7 +37208,7 @@
         <v>1470</v>
       </c>
       <c r="G1240" s="2" t="s">
-        <v>2257</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="1241" spans="1:7" x14ac:dyDescent="0.45">
@@ -37226,10 +37219,10 @@
         <v>2</v>
       </c>
       <c r="C1241" t="s">
-        <v>2255</v>
+        <v>2250</v>
       </c>
       <c r="D1241" s="2" t="s">
-        <v>2265</v>
+        <v>2260</v>
       </c>
       <c r="E1241" s="2">
         <v>9</v>
@@ -37238,7 +37231,7 @@
         <v>128</v>
       </c>
       <c r="G1241" s="2" t="s">
-        <v>2257</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="1242" spans="1:7" x14ac:dyDescent="0.45">
@@ -37249,10 +37242,10 @@
         <v>2</v>
       </c>
       <c r="C1242" t="s">
-        <v>2255</v>
+        <v>2250</v>
       </c>
       <c r="D1242" s="2" t="s">
-        <v>2266</v>
+        <v>2261</v>
       </c>
       <c r="E1242" s="2">
         <v>10</v>
@@ -37261,7 +37254,7 @@
         <v>1177</v>
       </c>
       <c r="G1242" s="2" t="s">
-        <v>2257</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="1243" spans="1:7" x14ac:dyDescent="0.45">
@@ -37272,19 +37265,19 @@
         <v>2</v>
       </c>
       <c r="C1243" t="s">
-        <v>2255</v>
+        <v>2250</v>
       </c>
       <c r="D1243" s="2" t="s">
-        <v>2267</v>
+        <v>2262</v>
       </c>
       <c r="E1243" s="2">
         <v>11</v>
       </c>
       <c r="F1243" s="2" t="s">
-        <v>2013</v>
+        <v>2008</v>
       </c>
       <c r="G1243" s="2" t="s">
-        <v>2013</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="1244" spans="1:7" x14ac:dyDescent="0.45">
@@ -37295,19 +37288,19 @@
         <v>2</v>
       </c>
       <c r="C1244" t="s">
-        <v>2255</v>
+        <v>2250</v>
       </c>
       <c r="D1244" s="2" t="s">
-        <v>2268</v>
+        <v>2263</v>
       </c>
       <c r="E1244" s="2">
         <v>12</v>
       </c>
       <c r="F1244" s="2" t="s">
-        <v>2175</v>
+        <v>2170</v>
       </c>
       <c r="G1244" s="2" t="s">
-        <v>2257</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="1245" spans="1:7" x14ac:dyDescent="0.45">
@@ -37318,19 +37311,19 @@
         <v>2</v>
       </c>
       <c r="C1245" t="s">
-        <v>2255</v>
+        <v>2250</v>
       </c>
       <c r="D1245" s="2" t="s">
-        <v>2269</v>
+        <v>2264</v>
       </c>
       <c r="E1245" s="2">
         <v>13</v>
       </c>
       <c r="F1245" s="2" t="s">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="G1245" s="2" t="s">
-        <v>2257</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="1246" spans="1:7" x14ac:dyDescent="0.45">
@@ -37341,19 +37334,19 @@
         <v>2</v>
       </c>
       <c r="C1246" t="s">
-        <v>2255</v>
+        <v>2250</v>
       </c>
       <c r="D1246" s="2" t="s">
-        <v>2270</v>
+        <v>2265</v>
       </c>
       <c r="E1246" s="2">
         <v>14</v>
       </c>
       <c r="F1246" s="2" t="s">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="G1246" s="2" t="s">
-        <v>2257</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="1247" spans="1:7" x14ac:dyDescent="0.45">
@@ -37364,19 +37357,19 @@
         <v>2</v>
       </c>
       <c r="C1247" t="s">
-        <v>2255</v>
+        <v>2250</v>
       </c>
       <c r="D1247" s="2" t="s">
-        <v>2271</v>
+        <v>2266</v>
       </c>
       <c r="E1247" s="2">
         <v>15</v>
       </c>
       <c r="F1247" s="2" t="s">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="G1247" s="2" t="s">
-        <v>2257</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="1248" spans="1:7" x14ac:dyDescent="0.45">
@@ -37387,19 +37380,19 @@
         <v>2</v>
       </c>
       <c r="C1248" t="s">
-        <v>2255</v>
+        <v>2250</v>
       </c>
       <c r="D1248" s="2" t="s">
-        <v>2272</v>
+        <v>2267</v>
       </c>
       <c r="E1248" s="2">
         <v>16</v>
       </c>
       <c r="F1248" s="2" t="s">
-        <v>2013</v>
+        <v>2008</v>
       </c>
       <c r="G1248" s="2" t="s">
-        <v>2257</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="1249" spans="1:7" x14ac:dyDescent="0.45">
@@ -37410,19 +37403,19 @@
         <v>2</v>
       </c>
       <c r="C1249" t="s">
-        <v>2255</v>
+        <v>2250</v>
       </c>
       <c r="D1249" s="2" t="s">
-        <v>2273</v>
+        <v>2268</v>
       </c>
       <c r="E1249" s="2">
         <v>17</v>
       </c>
       <c r="F1249" s="2" t="s">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="G1249" s="2" t="s">
-        <v>2257</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="1250" spans="1:7" x14ac:dyDescent="0.45">
@@ -37433,19 +37426,19 @@
         <v>2</v>
       </c>
       <c r="C1250" t="s">
-        <v>2255</v>
+        <v>2250</v>
       </c>
       <c r="D1250" s="2" t="s">
-        <v>2274</v>
+        <v>2269</v>
       </c>
       <c r="E1250" s="2">
         <v>18</v>
       </c>
       <c r="F1250" s="2" t="s">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="G1250" s="2" t="s">
-        <v>2257</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="1251" spans="1:7" x14ac:dyDescent="0.45">
@@ -37456,19 +37449,19 @@
         <v>2</v>
       </c>
       <c r="C1251" t="s">
-        <v>2255</v>
+        <v>2250</v>
       </c>
       <c r="D1251" s="2" t="s">
-        <v>2275</v>
+        <v>2270</v>
       </c>
       <c r="E1251" s="2">
         <v>19</v>
       </c>
       <c r="F1251" s="2" t="s">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="G1251" s="2" t="s">
-        <v>2257</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="1252" spans="1:7" x14ac:dyDescent="0.45">
@@ -37479,19 +37472,19 @@
         <v>2</v>
       </c>
       <c r="C1252" t="s">
-        <v>2255</v>
+        <v>2250</v>
       </c>
       <c r="D1252" s="2" t="s">
-        <v>2276</v>
+        <v>2271</v>
       </c>
       <c r="E1252" s="2">
         <v>20</v>
       </c>
       <c r="F1252" s="2" t="s">
-        <v>2013</v>
+        <v>2008</v>
       </c>
       <c r="G1252" s="2" t="s">
-        <v>2257</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="1253" spans="1:7" x14ac:dyDescent="0.45">
@@ -37502,19 +37495,19 @@
         <v>2</v>
       </c>
       <c r="C1253" t="s">
-        <v>2255</v>
+        <v>2250</v>
       </c>
       <c r="D1253" s="2" t="s">
-        <v>2277</v>
+        <v>2272</v>
       </c>
       <c r="E1253" s="2">
         <v>21</v>
       </c>
       <c r="F1253" s="2" t="s">
-        <v>2278</v>
+        <v>2273</v>
       </c>
       <c r="G1253" s="2" t="s">
-        <v>2278</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="1254" spans="1:7" x14ac:dyDescent="0.45">
@@ -37525,19 +37518,19 @@
         <v>2</v>
       </c>
       <c r="C1254" t="s">
-        <v>2255</v>
+        <v>2250</v>
       </c>
       <c r="D1254" s="2" t="s">
-        <v>2279</v>
+        <v>2274</v>
       </c>
       <c r="E1254" s="2">
         <v>22</v>
       </c>
       <c r="F1254" s="2" t="s">
-        <v>2280</v>
+        <v>2275</v>
       </c>
       <c r="G1254" s="2" t="s">
-        <v>2281</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="1255" spans="1:7" x14ac:dyDescent="0.45">
@@ -37548,19 +37541,19 @@
         <v>2</v>
       </c>
       <c r="C1255" t="s">
-        <v>2255</v>
+        <v>2250</v>
       </c>
       <c r="D1255" s="2" t="s">
-        <v>2282</v>
+        <v>2277</v>
       </c>
       <c r="E1255" s="2">
         <v>23</v>
       </c>
       <c r="F1255" s="2" t="s">
-        <v>2283</v>
+        <v>2278</v>
       </c>
       <c r="G1255" s="2" t="s">
-        <v>2281</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="1256" spans="1:7" x14ac:dyDescent="0.45">
@@ -37571,19 +37564,19 @@
         <v>2</v>
       </c>
       <c r="C1256" t="s">
-        <v>2255</v>
+        <v>2250</v>
       </c>
       <c r="D1256" s="2" t="s">
-        <v>2284</v>
+        <v>2279</v>
       </c>
       <c r="E1256" s="2">
         <v>24</v>
       </c>
       <c r="F1256" s="2" t="s">
-        <v>2285</v>
+        <v>2280</v>
       </c>
       <c r="G1256" s="2" t="s">
-        <v>2281</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="1257" spans="1:7" x14ac:dyDescent="0.45">
@@ -37594,19 +37587,19 @@
         <v>2</v>
       </c>
       <c r="C1257" t="s">
-        <v>2255</v>
+        <v>2250</v>
       </c>
       <c r="D1257" s="2" t="s">
-        <v>2286</v>
+        <v>2281</v>
       </c>
       <c r="E1257" s="2">
         <v>25</v>
       </c>
       <c r="F1257" s="2" t="s">
-        <v>2280</v>
+        <v>2275</v>
       </c>
       <c r="G1257" s="2" t="s">
-        <v>2281</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="1258" spans="1:7" x14ac:dyDescent="0.45">
@@ -37617,19 +37610,19 @@
         <v>2</v>
       </c>
       <c r="C1258" t="s">
-        <v>2255</v>
+        <v>2250</v>
       </c>
       <c r="D1258" s="2" t="s">
-        <v>2287</v>
+        <v>2282</v>
       </c>
       <c r="E1258" s="2">
         <v>26</v>
       </c>
       <c r="F1258" s="2" t="s">
-        <v>2288</v>
+        <v>2283</v>
       </c>
       <c r="G1258" s="2" t="s">
-        <v>2281</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="1259" spans="1:7" x14ac:dyDescent="0.45">
@@ -37640,19 +37633,19 @@
         <v>2</v>
       </c>
       <c r="C1259" t="s">
-        <v>2255</v>
+        <v>2250</v>
       </c>
       <c r="D1259" s="2" t="s">
-        <v>2289</v>
+        <v>2284</v>
       </c>
       <c r="E1259" s="2">
         <v>27</v>
       </c>
       <c r="F1259" s="2" t="s">
-        <v>2290</v>
+        <v>2285</v>
       </c>
       <c r="G1259" s="2" t="s">
-        <v>2281</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="1260" spans="1:7" x14ac:dyDescent="0.45">
@@ -37663,19 +37656,19 @@
         <v>2</v>
       </c>
       <c r="C1260" t="s">
-        <v>2255</v>
+        <v>2250</v>
       </c>
       <c r="D1260" s="2" t="s">
-        <v>2291</v>
+        <v>2286</v>
       </c>
       <c r="E1260" s="2">
         <v>28</v>
       </c>
       <c r="F1260" s="2" t="s">
-        <v>2292</v>
+        <v>2287</v>
       </c>
       <c r="G1260" s="2" t="s">
-        <v>2281</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="1261" spans="1:7" x14ac:dyDescent="0.45">
@@ -37686,19 +37679,19 @@
         <v>2</v>
       </c>
       <c r="C1261" t="s">
-        <v>2255</v>
+        <v>2250</v>
       </c>
       <c r="D1261" s="2" t="s">
-        <v>2293</v>
+        <v>2288</v>
       </c>
       <c r="E1261" s="2">
         <v>29</v>
       </c>
       <c r="F1261" s="2" t="s">
-        <v>2294</v>
+        <v>2289</v>
       </c>
       <c r="G1261" s="2" t="s">
-        <v>2281</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="1262" spans="1:7" x14ac:dyDescent="0.45">
@@ -37709,19 +37702,19 @@
         <v>2</v>
       </c>
       <c r="C1262" t="s">
-        <v>2255</v>
+        <v>2250</v>
       </c>
       <c r="D1262" s="2" t="s">
-        <v>2295</v>
+        <v>2290</v>
       </c>
       <c r="E1262" s="2">
         <v>30</v>
       </c>
       <c r="F1262" s="2" t="s">
-        <v>2296</v>
+        <v>2291</v>
       </c>
       <c r="G1262" s="2" t="s">
-        <v>2281</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="1263" spans="1:7" x14ac:dyDescent="0.45">
@@ -37732,19 +37725,19 @@
         <v>2</v>
       </c>
       <c r="C1263" t="s">
-        <v>2255</v>
+        <v>2250</v>
       </c>
       <c r="D1263" s="2" t="s">
-        <v>2297</v>
+        <v>2292</v>
       </c>
       <c r="E1263" s="2">
         <v>31</v>
       </c>
       <c r="F1263" s="2" t="s">
-        <v>2298</v>
+        <v>2293</v>
       </c>
       <c r="G1263" s="2" t="s">
-        <v>2298</v>
+        <v>2293</v>
       </c>
     </row>
     <row r="1264" spans="1:7" x14ac:dyDescent="0.45">
@@ -37755,19 +37748,19 @@
         <v>2</v>
       </c>
       <c r="C1264" t="s">
-        <v>2255</v>
+        <v>2250</v>
       </c>
       <c r="D1264" s="2" t="s">
-        <v>2299</v>
+        <v>2294</v>
       </c>
       <c r="E1264" s="2">
         <v>32</v>
       </c>
       <c r="F1264" s="2" t="s">
-        <v>2298</v>
+        <v>2293</v>
       </c>
       <c r="G1264" s="2" t="s">
-        <v>2257</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="1265" spans="1:7" x14ac:dyDescent="0.45">
@@ -37778,10 +37771,10 @@
         <v>2</v>
       </c>
       <c r="C1265" t="s">
-        <v>2255</v>
+        <v>2250</v>
       </c>
       <c r="D1265" s="2" t="s">
-        <v>2300</v>
+        <v>2295</v>
       </c>
       <c r="E1265" s="2">
         <v>33</v>
@@ -37790,7 +37783,7 @@
         <v>888</v>
       </c>
       <c r="G1265" s="2" t="s">
-        <v>2257</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="1266" spans="1:7" x14ac:dyDescent="0.45">
@@ -37801,10 +37794,10 @@
         <v>2</v>
       </c>
       <c r="C1266" t="s">
-        <v>2255</v>
+        <v>2250</v>
       </c>
       <c r="D1266" s="2" t="s">
-        <v>2301</v>
+        <v>2296</v>
       </c>
       <c r="E1266" s="2">
         <v>34</v>
@@ -37813,7 +37806,7 @@
         <v>390</v>
       </c>
       <c r="G1266" s="2" t="s">
-        <v>2257</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="1267" spans="1:7" x14ac:dyDescent="0.45">
@@ -37824,10 +37817,10 @@
         <v>2</v>
       </c>
       <c r="C1267" t="s">
-        <v>2255</v>
+        <v>2250</v>
       </c>
       <c r="D1267" s="2" t="s">
-        <v>2302</v>
+        <v>2297</v>
       </c>
       <c r="E1267" s="2">
         <v>35</v>
@@ -37836,7 +37829,7 @@
         <v>888</v>
       </c>
       <c r="G1267" s="2" t="s">
-        <v>2257</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="1268" spans="1:7" x14ac:dyDescent="0.45">
@@ -37847,19 +37840,19 @@
         <v>2</v>
       </c>
       <c r="C1268" t="s">
-        <v>2255</v>
+        <v>2250</v>
       </c>
       <c r="D1268" s="2" t="s">
-        <v>2303</v>
+        <v>2298</v>
       </c>
       <c r="E1268" s="2">
         <v>36</v>
       </c>
       <c r="F1268" s="2" t="s">
-        <v>2298</v>
+        <v>2293</v>
       </c>
       <c r="G1268" s="2" t="s">
-        <v>2257</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="1269" spans="1:7" x14ac:dyDescent="0.45">
@@ -37870,10 +37863,10 @@
         <v>2</v>
       </c>
       <c r="C1269" t="s">
-        <v>2255</v>
+        <v>2250</v>
       </c>
       <c r="D1269" s="2" t="s">
-        <v>2304</v>
+        <v>2299</v>
       </c>
       <c r="E1269" s="2">
         <v>37</v>
@@ -37882,7 +37875,7 @@
         <v>471</v>
       </c>
       <c r="G1269" s="2" t="s">
-        <v>2257</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="1270" spans="1:7" x14ac:dyDescent="0.45">
@@ -37893,19 +37886,19 @@
         <v>2</v>
       </c>
       <c r="C1270" t="s">
-        <v>2255</v>
+        <v>2250</v>
       </c>
       <c r="D1270" s="2" t="s">
-        <v>2305</v>
+        <v>2300</v>
       </c>
       <c r="E1270" s="2">
         <v>38</v>
       </c>
       <c r="F1270" s="2" t="s">
-        <v>2298</v>
+        <v>2293</v>
       </c>
       <c r="G1270" s="2" t="s">
-        <v>2257</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="1271" spans="1:7" x14ac:dyDescent="0.45">
@@ -37916,10 +37909,10 @@
         <v>2</v>
       </c>
       <c r="C1271" t="s">
-        <v>2255</v>
+        <v>2250</v>
       </c>
       <c r="D1271" s="2" t="s">
-        <v>2306</v>
+        <v>2301</v>
       </c>
       <c r="E1271" s="2">
         <v>39</v>
@@ -37928,7 +37921,7 @@
         <v>473</v>
       </c>
       <c r="G1271" s="2" t="s">
-        <v>2257</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="1272" spans="1:7" x14ac:dyDescent="0.45">
@@ -37939,10 +37932,10 @@
         <v>2</v>
       </c>
       <c r="C1272" t="s">
-        <v>2255</v>
+        <v>2250</v>
       </c>
       <c r="D1272" s="2" t="s">
-        <v>2307</v>
+        <v>2302</v>
       </c>
       <c r="E1272" s="2">
         <v>40</v>
@@ -37951,7 +37944,7 @@
         <v>888</v>
       </c>
       <c r="G1272" s="2" t="s">
-        <v>2257</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="1273" spans="1:7" x14ac:dyDescent="0.45">
@@ -37962,19 +37955,19 @@
         <v>3</v>
       </c>
       <c r="C1273" t="s">
-        <v>2308</v>
+        <v>2303</v>
       </c>
       <c r="D1273" s="2" t="s">
-        <v>2309</v>
+        <v>2304</v>
       </c>
       <c r="E1273" s="3">
         <v>1</v>
       </c>
       <c r="F1273" s="2" t="s">
-        <v>2310</v>
+        <v>2305</v>
       </c>
       <c r="G1273" s="2" t="s">
-        <v>2311</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="1274" spans="1:7" x14ac:dyDescent="0.45">
@@ -37985,19 +37978,19 @@
         <v>3</v>
       </c>
       <c r="C1274" t="s">
-        <v>2308</v>
+        <v>2303</v>
       </c>
       <c r="D1274" s="2" t="s">
-        <v>2312</v>
+        <v>2307</v>
       </c>
       <c r="E1274" s="3">
         <v>2</v>
       </c>
       <c r="F1274" s="2" t="s">
-        <v>2310</v>
+        <v>2305</v>
       </c>
       <c r="G1274" s="2" t="s">
-        <v>2311</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="1275" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -38008,19 +38001,19 @@
         <v>3</v>
       </c>
       <c r="C1275" t="s">
+        <v>2303</v>
+      </c>
+      <c r="D1275" s="2" t="s">
         <v>2308</v>
-      </c>
-      <c r="D1275" s="2" t="s">
-        <v>2313</v>
       </c>
       <c r="E1275" s="3">
         <v>3</v>
       </c>
       <c r="F1275" s="2" t="s">
-        <v>2310</v>
+        <v>2305</v>
       </c>
       <c r="G1275" s="2" t="s">
-        <v>2311</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="1276" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -38031,19 +38024,19 @@
         <v>3</v>
       </c>
       <c r="C1276" t="s">
-        <v>2308</v>
+        <v>2303</v>
       </c>
       <c r="D1276" s="2" t="s">
-        <v>2314</v>
+        <v>2309</v>
       </c>
       <c r="E1276" s="3">
         <v>4</v>
       </c>
       <c r="F1276" s="2" t="s">
-        <v>2310</v>
+        <v>2305</v>
       </c>
       <c r="G1276" s="2" t="s">
-        <v>2311</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="1277" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -38054,10 +38047,10 @@
         <v>3</v>
       </c>
       <c r="C1277" t="s">
-        <v>2308</v>
+        <v>2303</v>
       </c>
       <c r="D1277" s="2" t="s">
-        <v>2315</v>
+        <v>2310</v>
       </c>
       <c r="E1277" s="3">
         <v>5</v>
@@ -38066,7 +38059,7 @@
         <v>922</v>
       </c>
       <c r="G1277" s="2" t="s">
-        <v>2311</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="1278" spans="1:7" x14ac:dyDescent="0.45">
@@ -38077,10 +38070,10 @@
         <v>3</v>
       </c>
       <c r="C1278" t="s">
-        <v>2308</v>
+        <v>2303</v>
       </c>
       <c r="D1278" s="2" t="s">
-        <v>2316</v>
+        <v>2311</v>
       </c>
       <c r="E1278" s="3">
         <v>6</v>
@@ -38089,7 +38082,7 @@
         <v>959</v>
       </c>
       <c r="G1278" s="2" t="s">
-        <v>2311</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="1279" spans="1:7" x14ac:dyDescent="0.45">
@@ -38100,19 +38093,19 @@
         <v>3</v>
       </c>
       <c r="C1279" t="s">
-        <v>2308</v>
+        <v>2303</v>
       </c>
       <c r="D1279" s="2" t="s">
-        <v>2317</v>
+        <v>2312</v>
       </c>
       <c r="E1279" s="3">
         <v>7</v>
       </c>
       <c r="F1279" s="2" t="s">
-        <v>2318</v>
+        <v>2313</v>
       </c>
       <c r="G1279" s="2" t="s">
-        <v>2311</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="1280" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -38123,19 +38116,19 @@
         <v>3</v>
       </c>
       <c r="C1280" t="s">
-        <v>2308</v>
+        <v>2303</v>
       </c>
       <c r="D1280" s="2" t="s">
-        <v>2319</v>
+        <v>2314</v>
       </c>
       <c r="E1280" s="3">
         <v>8</v>
       </c>
       <c r="F1280" s="2" t="s">
-        <v>2320</v>
+        <v>2315</v>
       </c>
       <c r="G1280" s="2" t="s">
-        <v>2311</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="1281" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -38146,19 +38139,19 @@
         <v>3</v>
       </c>
       <c r="C1281" t="s">
-        <v>2308</v>
+        <v>2303</v>
       </c>
       <c r="D1281" s="2" t="s">
-        <v>2321</v>
+        <v>2316</v>
       </c>
       <c r="E1281" s="3">
         <v>9</v>
       </c>
       <c r="F1281" s="2" t="s">
-        <v>2322</v>
+        <v>2317</v>
       </c>
       <c r="G1281" s="2" t="s">
-        <v>2311</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="1282" spans="1:7" x14ac:dyDescent="0.45">
@@ -38169,19 +38162,19 @@
         <v>3</v>
       </c>
       <c r="C1282" t="s">
-        <v>2308</v>
+        <v>2303</v>
       </c>
       <c r="D1282" s="2" t="s">
-        <v>2323</v>
+        <v>2318</v>
       </c>
       <c r="E1282" s="3">
         <v>10</v>
       </c>
       <c r="F1282" s="2" t="s">
-        <v>2318</v>
+        <v>2313</v>
       </c>
       <c r="G1282" s="2" t="s">
-        <v>2311</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="1283" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -38192,19 +38185,19 @@
         <v>3</v>
       </c>
       <c r="C1283" t="s">
-        <v>2308</v>
+        <v>2303</v>
       </c>
       <c r="D1283" s="2" t="s">
-        <v>2324</v>
+        <v>2319</v>
       </c>
       <c r="E1283" s="3">
         <v>11</v>
       </c>
       <c r="F1283" s="2" t="s">
-        <v>2325</v>
+        <v>2320</v>
       </c>
       <c r="G1283" s="2" t="s">
-        <v>2325</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="1284" spans="1:7" x14ac:dyDescent="0.45">
@@ -38215,10 +38208,10 @@
         <v>3</v>
       </c>
       <c r="C1284" t="s">
-        <v>2308</v>
+        <v>2303</v>
       </c>
       <c r="D1284" s="2" t="s">
-        <v>2326</v>
+        <v>2321</v>
       </c>
       <c r="E1284" s="3">
         <v>12</v>
@@ -38227,7 +38220,7 @@
         <v>910</v>
       </c>
       <c r="G1284" s="2" t="s">
-        <v>2311</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="1285" spans="1:7" x14ac:dyDescent="0.45">
@@ -38238,19 +38231,19 @@
         <v>3</v>
       </c>
       <c r="C1285" t="s">
-        <v>2308</v>
+        <v>2303</v>
       </c>
       <c r="D1285" s="2" t="s">
-        <v>2327</v>
+        <v>2322</v>
       </c>
       <c r="E1285" s="3">
         <v>13</v>
       </c>
       <c r="F1285" s="2" t="s">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="G1285" s="2" t="s">
-        <v>2311</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="1286" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -38261,19 +38254,19 @@
         <v>3</v>
       </c>
       <c r="C1286" t="s">
-        <v>2308</v>
+        <v>2303</v>
       </c>
       <c r="D1286" s="2" t="s">
-        <v>2328</v>
+        <v>2323</v>
       </c>
       <c r="E1286" s="3">
         <v>14</v>
       </c>
       <c r="F1286" s="2" t="s">
-        <v>2320</v>
+        <v>2315</v>
       </c>
       <c r="G1286" s="2" t="s">
-        <v>2311</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="1287" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -38284,19 +38277,19 @@
         <v>3</v>
       </c>
       <c r="C1287" t="s">
-        <v>2308</v>
+        <v>2303</v>
       </c>
       <c r="D1287" s="2" t="s">
-        <v>2329</v>
+        <v>2324</v>
       </c>
       <c r="E1287" s="3">
         <v>15</v>
       </c>
       <c r="F1287" s="2" t="s">
-        <v>2320</v>
+        <v>2315</v>
       </c>
       <c r="G1287" s="2" t="s">
-        <v>2311</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="1288" spans="1:7" x14ac:dyDescent="0.45">
@@ -38307,10 +38300,10 @@
         <v>3</v>
       </c>
       <c r="C1288" t="s">
-        <v>2308</v>
+        <v>2303</v>
       </c>
       <c r="D1288" s="2" t="s">
-        <v>2330</v>
+        <v>2325</v>
       </c>
       <c r="E1288" s="3">
         <v>16</v>
@@ -38319,7 +38312,7 @@
         <v>910</v>
       </c>
       <c r="G1288" s="2" t="s">
-        <v>2311</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="1289" spans="1:7" x14ac:dyDescent="0.45">
@@ -38330,10 +38323,10 @@
         <v>3</v>
       </c>
       <c r="C1289" t="s">
-        <v>2308</v>
+        <v>2303</v>
       </c>
       <c r="D1289" s="2" t="s">
-        <v>2331</v>
+        <v>2326</v>
       </c>
       <c r="E1289" s="3">
         <v>17</v>
@@ -38342,7 +38335,7 @@
         <v>959</v>
       </c>
       <c r="G1289" s="2" t="s">
-        <v>2311</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="1290" spans="1:7" x14ac:dyDescent="0.45">
@@ -38353,10 +38346,10 @@
         <v>3</v>
       </c>
       <c r="C1290" t="s">
-        <v>2308</v>
+        <v>2303</v>
       </c>
       <c r="D1290" s="2" t="s">
-        <v>2332</v>
+        <v>2327</v>
       </c>
       <c r="E1290" s="3">
         <v>18</v>
@@ -38365,7 +38358,7 @@
         <v>959</v>
       </c>
       <c r="G1290" s="2" t="s">
-        <v>2311</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="1291" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -38376,19 +38369,19 @@
         <v>3</v>
       </c>
       <c r="C1291" t="s">
-        <v>2308</v>
+        <v>2303</v>
       </c>
       <c r="D1291" s="2" t="s">
-        <v>2333</v>
+        <v>2328</v>
       </c>
       <c r="E1291" s="3">
         <v>19</v>
       </c>
       <c r="F1291" s="2" t="s">
-        <v>2322</v>
+        <v>2317</v>
       </c>
       <c r="G1291" s="2" t="s">
-        <v>2311</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="1292" spans="1:7" x14ac:dyDescent="0.45">
@@ -38399,19 +38392,19 @@
         <v>3</v>
       </c>
       <c r="C1292" t="s">
-        <v>2308</v>
+        <v>2303</v>
       </c>
       <c r="D1292" s="2" t="s">
-        <v>2334</v>
+        <v>2329</v>
       </c>
       <c r="E1292" s="3">
         <v>20</v>
       </c>
       <c r="F1292" s="2" t="s">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="G1292" s="2" t="s">
-        <v>2311</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="1293" spans="1:7" x14ac:dyDescent="0.45">
@@ -38422,10 +38415,10 @@
         <v>3</v>
       </c>
       <c r="C1293" t="s">
-        <v>2308</v>
+        <v>2303</v>
       </c>
       <c r="D1293" s="2" t="s">
-        <v>2335</v>
+        <v>2330</v>
       </c>
       <c r="E1293" s="3">
         <v>21</v>
@@ -38445,10 +38438,10 @@
         <v>3</v>
       </c>
       <c r="C1294" t="s">
-        <v>2308</v>
+        <v>2303</v>
       </c>
       <c r="D1294" s="2" t="s">
-        <v>2336</v>
+        <v>2331</v>
       </c>
       <c r="E1294" s="3">
         <v>22</v>
@@ -38457,7 +38450,7 @@
         <v>910</v>
       </c>
       <c r="G1294" s="2" t="s">
-        <v>2311</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="1295" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -38468,19 +38461,19 @@
         <v>3</v>
       </c>
       <c r="C1295" t="s">
-        <v>2308</v>
+        <v>2303</v>
       </c>
       <c r="D1295" s="2" t="s">
-        <v>2337</v>
+        <v>2332</v>
       </c>
       <c r="E1295" s="3">
         <v>23</v>
       </c>
       <c r="F1295" s="2" t="s">
-        <v>2325</v>
+        <v>2320</v>
       </c>
       <c r="G1295" s="2" t="s">
-        <v>2311</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="1296" spans="1:7" x14ac:dyDescent="0.45">
@@ -38491,19 +38484,19 @@
         <v>3</v>
       </c>
       <c r="C1296" t="s">
-        <v>2308</v>
+        <v>2303</v>
       </c>
       <c r="D1296" s="2" t="s">
-        <v>2338</v>
+        <v>2333</v>
       </c>
       <c r="E1296" s="3">
         <v>24</v>
       </c>
       <c r="F1296" s="2" t="s">
-        <v>2339</v>
+        <v>2334</v>
       </c>
       <c r="G1296" s="2" t="s">
-        <v>2311</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="1297" spans="1:9" x14ac:dyDescent="0.45">
@@ -38514,10 +38507,10 @@
         <v>3</v>
       </c>
       <c r="C1297" t="s">
-        <v>2308</v>
+        <v>2303</v>
       </c>
       <c r="D1297" s="2" t="s">
-        <v>2340</v>
+        <v>2335</v>
       </c>
       <c r="E1297" s="3">
         <v>25</v>
@@ -38526,7 +38519,7 @@
         <v>959</v>
       </c>
       <c r="G1297" s="2" t="s">
-        <v>2311</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="1298" spans="1:9" x14ac:dyDescent="0.45">
@@ -38537,10 +38530,10 @@
         <v>3</v>
       </c>
       <c r="C1298" t="s">
-        <v>2308</v>
+        <v>2303</v>
       </c>
       <c r="D1298" s="2" t="s">
-        <v>2341</v>
+        <v>2336</v>
       </c>
       <c r="E1298" s="3">
         <v>26</v>
@@ -38549,7 +38542,7 @@
         <v>959</v>
       </c>
       <c r="G1298" s="2" t="s">
-        <v>2311</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="1299" spans="1:9" x14ac:dyDescent="0.45">
@@ -38560,10 +38553,10 @@
         <v>3</v>
       </c>
       <c r="C1299" t="s">
-        <v>2308</v>
+        <v>2303</v>
       </c>
       <c r="D1299" s="2" t="s">
-        <v>2342</v>
+        <v>2337</v>
       </c>
       <c r="E1299" s="3">
         <v>27</v>
@@ -38572,7 +38565,7 @@
         <v>959</v>
       </c>
       <c r="G1299" s="2" t="s">
-        <v>2311</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="1300" spans="1:9" x14ac:dyDescent="0.45">
@@ -38583,10 +38576,10 @@
         <v>3</v>
       </c>
       <c r="C1300" t="s">
-        <v>2308</v>
+        <v>2303</v>
       </c>
       <c r="D1300" s="2" t="s">
-        <v>2343</v>
+        <v>2338</v>
       </c>
       <c r="E1300" s="3">
         <v>28</v>
@@ -38595,7 +38588,7 @@
         <v>910</v>
       </c>
       <c r="G1300" s="2" t="s">
-        <v>2311</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="1301" spans="1:9" x14ac:dyDescent="0.45">
@@ -38606,10 +38599,10 @@
         <v>3</v>
       </c>
       <c r="C1301" t="s">
-        <v>2308</v>
+        <v>2303</v>
       </c>
       <c r="D1301" s="2" t="s">
-        <v>2344</v>
+        <v>2339</v>
       </c>
       <c r="E1301" s="3">
         <v>29</v>
@@ -38618,7 +38611,7 @@
         <v>968</v>
       </c>
       <c r="G1301" s="2" t="s">
-        <v>2311</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="1302" spans="1:9" x14ac:dyDescent="0.45">
@@ -38629,19 +38622,19 @@
         <v>3</v>
       </c>
       <c r="C1302" t="s">
-        <v>2308</v>
+        <v>2303</v>
       </c>
       <c r="D1302" s="2" t="s">
-        <v>2345</v>
+        <v>2340</v>
       </c>
       <c r="E1302" s="3">
         <v>30</v>
       </c>
       <c r="F1302" s="2" t="s">
-        <v>2346</v>
+        <v>2341</v>
       </c>
       <c r="G1302" s="2" t="s">
-        <v>2311</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="1303" spans="1:9" x14ac:dyDescent="0.45">
@@ -38652,25 +38645,25 @@
         <v>4</v>
       </c>
       <c r="C1303" t="s">
+        <v>2342</v>
+      </c>
+      <c r="D1303" s="2" t="s">
+        <v>2343</v>
+      </c>
+      <c r="E1303" s="2">
+        <v>1</v>
+      </c>
+      <c r="F1303" s="2" t="s">
+        <v>2344</v>
+      </c>
+      <c r="G1303" s="2" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H1303" t="s">
+        <v>2346</v>
+      </c>
+      <c r="I1303" t="s">
         <v>2347</v>
-      </c>
-      <c r="D1303" s="2" t="s">
-        <v>2348</v>
-      </c>
-      <c r="E1303" s="2">
-        <v>1</v>
-      </c>
-      <c r="F1303" s="2" t="s">
-        <v>2349</v>
-      </c>
-      <c r="G1303" s="2" t="s">
-        <v>2350</v>
-      </c>
-      <c r="H1303" t="s">
-        <v>2351</v>
-      </c>
-      <c r="I1303" t="s">
-        <v>2352</v>
       </c>
     </row>
     <row r="1304" spans="1:9" x14ac:dyDescent="0.45">
@@ -38681,25 +38674,25 @@
         <v>4</v>
       </c>
       <c r="C1304" t="s">
-        <v>2347</v>
+        <v>2342</v>
       </c>
       <c r="D1304" s="2" t="s">
-        <v>2353</v>
+        <v>2348</v>
       </c>
       <c r="E1304" s="2">
         <v>2</v>
       </c>
       <c r="F1304" s="2" t="s">
-        <v>2354</v>
+        <v>2349</v>
       </c>
       <c r="G1304" s="2" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H1304" t="s">
         <v>2350</v>
       </c>
-      <c r="H1304" t="s">
-        <v>2355</v>
-      </c>
       <c r="I1304" t="s">
-        <v>2356</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="1305" spans="1:9" x14ac:dyDescent="0.45">
@@ -38710,25 +38703,25 @@
         <v>4</v>
       </c>
       <c r="C1305" t="s">
-        <v>2347</v>
+        <v>2342</v>
       </c>
       <c r="D1305" s="2" t="s">
-        <v>2357</v>
+        <v>2352</v>
       </c>
       <c r="E1305" s="2">
         <v>3</v>
       </c>
       <c r="F1305" s="2" t="s">
-        <v>2358</v>
+        <v>2353</v>
       </c>
       <c r="G1305" s="2" t="s">
-        <v>2350</v>
+        <v>2345</v>
       </c>
       <c r="H1305" t="s">
-        <v>2359</v>
+        <v>2354</v>
       </c>
       <c r="I1305" t="s">
-        <v>2360</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="1306" spans="1:9" x14ac:dyDescent="0.45">
@@ -38739,25 +38732,25 @@
         <v>4</v>
       </c>
       <c r="C1306" t="s">
-        <v>2347</v>
+        <v>2342</v>
       </c>
       <c r="D1306" s="2" t="s">
-        <v>2361</v>
+        <v>2356</v>
       </c>
       <c r="E1306" s="2">
         <v>4</v>
       </c>
       <c r="F1306" s="2" t="s">
-        <v>2362</v>
+        <v>2357</v>
       </c>
       <c r="G1306" s="2" t="s">
-        <v>2350</v>
+        <v>2345</v>
       </c>
       <c r="H1306" t="s">
-        <v>2363</v>
+        <v>2358</v>
       </c>
       <c r="I1306" t="s">
-        <v>2364</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="1307" spans="1:9" x14ac:dyDescent="0.45">
@@ -38768,25 +38761,25 @@
         <v>4</v>
       </c>
       <c r="C1307" t="s">
-        <v>2347</v>
+        <v>2342</v>
       </c>
       <c r="D1307" s="2" t="s">
-        <v>2365</v>
+        <v>2360</v>
       </c>
       <c r="E1307" s="2">
         <v>5</v>
       </c>
       <c r="F1307" s="2" t="s">
-        <v>2366</v>
+        <v>2361</v>
       </c>
       <c r="G1307" s="2" t="s">
-        <v>2350</v>
+        <v>2345</v>
       </c>
       <c r="H1307" t="s">
-        <v>2367</v>
+        <v>2362</v>
       </c>
       <c r="I1307" t="s">
-        <v>2368</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="1308" spans="1:9" x14ac:dyDescent="0.45">
@@ -38797,25 +38790,25 @@
         <v>4</v>
       </c>
       <c r="C1308" t="s">
-        <v>2347</v>
+        <v>2342</v>
       </c>
       <c r="D1308" s="2" t="s">
-        <v>2369</v>
+        <v>2364</v>
       </c>
       <c r="E1308" s="2">
         <v>6</v>
       </c>
       <c r="F1308" s="2" t="s">
-        <v>2370</v>
+        <v>2365</v>
       </c>
       <c r="G1308" s="2" t="s">
-        <v>2350</v>
+        <v>2345</v>
       </c>
       <c r="H1308" t="s">
-        <v>2371</v>
+        <v>2366</v>
       </c>
       <c r="I1308" t="s">
-        <v>2372</v>
+        <v>2367</v>
       </c>
     </row>
     <row r="1309" spans="1:9" x14ac:dyDescent="0.45">
@@ -38826,25 +38819,25 @@
         <v>4</v>
       </c>
       <c r="C1309" t="s">
-        <v>2347</v>
+        <v>2342</v>
       </c>
       <c r="D1309" s="2" t="s">
-        <v>2373</v>
+        <v>2368</v>
       </c>
       <c r="E1309" s="2">
         <v>7</v>
       </c>
       <c r="F1309" s="2" t="s">
-        <v>2374</v>
+        <v>2369</v>
       </c>
       <c r="G1309" s="2" t="s">
-        <v>2350</v>
+        <v>2345</v>
       </c>
       <c r="H1309" t="s">
-        <v>2375</v>
+        <v>2370</v>
       </c>
       <c r="I1309" t="s">
-        <v>2376</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="1310" spans="1:9" x14ac:dyDescent="0.45">
@@ -38855,25 +38848,25 @@
         <v>4</v>
       </c>
       <c r="C1310" t="s">
-        <v>2347</v>
+        <v>2342</v>
       </c>
       <c r="D1310" s="2" t="s">
-        <v>2377</v>
+        <v>2372</v>
       </c>
       <c r="E1310" s="2">
         <v>8</v>
       </c>
       <c r="F1310" s="2" t="s">
-        <v>2378</v>
+        <v>2373</v>
       </c>
       <c r="G1310" s="2" t="s">
-        <v>2350</v>
+        <v>2345</v>
       </c>
       <c r="H1310" t="s">
-        <v>2379</v>
+        <v>2374</v>
       </c>
       <c r="I1310" t="s">
-        <v>2380</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="1311" spans="1:9" x14ac:dyDescent="0.45">
@@ -38884,25 +38877,25 @@
         <v>4</v>
       </c>
       <c r="C1311" t="s">
-        <v>2347</v>
+        <v>2342</v>
       </c>
       <c r="D1311" s="2" t="s">
-        <v>2381</v>
+        <v>2376</v>
       </c>
       <c r="E1311" s="2">
         <v>9</v>
       </c>
       <c r="F1311" s="2" t="s">
-        <v>2382</v>
+        <v>2377</v>
       </c>
       <c r="G1311" s="2" t="s">
-        <v>2350</v>
+        <v>2345</v>
       </c>
       <c r="H1311" t="s">
-        <v>2383</v>
+        <v>2378</v>
       </c>
       <c r="I1311" t="s">
-        <v>2384</v>
+        <v>2379</v>
       </c>
     </row>
     <row r="1312" spans="1:9" x14ac:dyDescent="0.45">
@@ -38913,25 +38906,25 @@
         <v>4</v>
       </c>
       <c r="C1312" t="s">
-        <v>2347</v>
+        <v>2342</v>
       </c>
       <c r="D1312" s="2" t="s">
-        <v>2385</v>
+        <v>2380</v>
       </c>
       <c r="E1312" s="2">
         <v>10</v>
       </c>
       <c r="F1312" s="2" t="s">
-        <v>2386</v>
+        <v>2381</v>
       </c>
       <c r="G1312" s="2" t="s">
-        <v>2350</v>
+        <v>2345</v>
       </c>
       <c r="H1312" t="s">
-        <v>2387</v>
+        <v>2382</v>
       </c>
       <c r="I1312" t="s">
-        <v>2388</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="1313" spans="1:9" x14ac:dyDescent="0.45">
@@ -38942,25 +38935,25 @@
         <v>4</v>
       </c>
       <c r="C1313" t="s">
-        <v>2347</v>
+        <v>2342</v>
       </c>
       <c r="D1313" s="2" t="s">
-        <v>2389</v>
+        <v>2384</v>
       </c>
       <c r="E1313" s="2">
         <v>11</v>
       </c>
       <c r="F1313" s="2" t="s">
-        <v>2390</v>
+        <v>2385</v>
       </c>
       <c r="G1313" s="2" t="s">
-        <v>2391</v>
+        <v>2386</v>
       </c>
       <c r="H1313" t="s">
-        <v>2392</v>
+        <v>2387</v>
       </c>
       <c r="I1313" t="s">
-        <v>2393</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="1314" spans="1:9" x14ac:dyDescent="0.45">
@@ -38971,25 +38964,25 @@
         <v>4</v>
       </c>
       <c r="C1314" t="s">
-        <v>2347</v>
+        <v>2342</v>
       </c>
       <c r="D1314" s="2" t="s">
-        <v>2394</v>
+        <v>2389</v>
       </c>
       <c r="E1314" s="2">
         <v>12</v>
       </c>
       <c r="F1314" s="2" t="s">
-        <v>2395</v>
+        <v>2390</v>
       </c>
       <c r="G1314" s="2" t="s">
-        <v>2350</v>
+        <v>2345</v>
       </c>
       <c r="H1314" t="s">
-        <v>2396</v>
+        <v>2391</v>
       </c>
       <c r="I1314" t="s">
-        <v>2397</v>
+        <v>2392</v>
       </c>
     </row>
     <row r="1315" spans="1:9" x14ac:dyDescent="0.45">
@@ -39000,25 +38993,25 @@
         <v>4</v>
       </c>
       <c r="C1315" t="s">
-        <v>2347</v>
+        <v>2342</v>
       </c>
       <c r="D1315" s="2" t="s">
-        <v>2398</v>
+        <v>2393</v>
       </c>
       <c r="E1315" s="2">
         <v>13</v>
       </c>
       <c r="F1315" s="2" t="s">
-        <v>2399</v>
+        <v>2394</v>
       </c>
       <c r="G1315" s="2" t="s">
-        <v>2350</v>
+        <v>2345</v>
       </c>
       <c r="H1315" t="s">
-        <v>2400</v>
+        <v>2395</v>
       </c>
       <c r="I1315" t="s">
-        <v>2401</v>
+        <v>2396</v>
       </c>
     </row>
     <row r="1316" spans="1:9" x14ac:dyDescent="0.45">
@@ -39029,25 +39022,25 @@
         <v>4</v>
       </c>
       <c r="C1316" t="s">
-        <v>2347</v>
+        <v>2342</v>
       </c>
       <c r="D1316" s="2" t="s">
-        <v>2402</v>
+        <v>2397</v>
       </c>
       <c r="E1316" s="2">
         <v>14</v>
       </c>
       <c r="F1316" s="2" t="s">
-        <v>2403</v>
+        <v>2398</v>
       </c>
       <c r="G1316" s="2" t="s">
-        <v>2350</v>
+        <v>2345</v>
       </c>
       <c r="H1316" t="s">
-        <v>2404</v>
+        <v>2399</v>
       </c>
       <c r="I1316" t="s">
-        <v>2405</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="1317" spans="1:9" x14ac:dyDescent="0.45">
@@ -39058,25 +39051,25 @@
         <v>4</v>
       </c>
       <c r="C1317" t="s">
-        <v>2347</v>
+        <v>2342</v>
       </c>
       <c r="D1317" s="2" t="s">
-        <v>2406</v>
+        <v>2401</v>
       </c>
       <c r="E1317" s="2">
         <v>15</v>
       </c>
       <c r="F1317" s="2" t="s">
-        <v>2407</v>
+        <v>2402</v>
       </c>
       <c r="G1317" s="2" t="s">
-        <v>2350</v>
+        <v>2345</v>
       </c>
       <c r="H1317" t="s">
-        <v>2408</v>
+        <v>2403</v>
       </c>
       <c r="I1317" t="s">
-        <v>2409</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="1318" spans="1:9" x14ac:dyDescent="0.45">
@@ -39087,25 +39080,25 @@
         <v>4</v>
       </c>
       <c r="C1318" t="s">
-        <v>2347</v>
+        <v>2342</v>
       </c>
       <c r="D1318" s="2" t="s">
-        <v>2410</v>
+        <v>2405</v>
       </c>
       <c r="E1318" s="2">
         <v>16</v>
       </c>
       <c r="F1318" s="2" t="s">
-        <v>2411</v>
+        <v>2406</v>
       </c>
       <c r="G1318" s="2" t="s">
-        <v>2350</v>
+        <v>2345</v>
       </c>
       <c r="H1318" t="s">
-        <v>2412</v>
+        <v>2407</v>
       </c>
       <c r="I1318" t="s">
-        <v>2413</v>
+        <v>2408</v>
       </c>
     </row>
     <row r="1319" spans="1:9" x14ac:dyDescent="0.45">
@@ -39116,25 +39109,25 @@
         <v>4</v>
       </c>
       <c r="C1319" t="s">
-        <v>2347</v>
+        <v>2342</v>
       </c>
       <c r="D1319" s="2" t="s">
-        <v>2414</v>
+        <v>2409</v>
       </c>
       <c r="E1319" s="2">
         <v>17</v>
       </c>
       <c r="F1319" s="2" t="s">
-        <v>2415</v>
+        <v>2410</v>
       </c>
       <c r="G1319" s="2" t="s">
-        <v>2350</v>
+        <v>2345</v>
       </c>
       <c r="H1319" t="s">
-        <v>2416</v>
+        <v>2411</v>
       </c>
       <c r="I1319" t="s">
-        <v>2417</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="1320" spans="1:9" x14ac:dyDescent="0.45">
@@ -39145,25 +39138,25 @@
         <v>4</v>
       </c>
       <c r="C1320" t="s">
-        <v>2347</v>
+        <v>2342</v>
       </c>
       <c r="D1320" s="2" t="s">
-        <v>2418</v>
+        <v>2413</v>
       </c>
       <c r="E1320" s="2">
         <v>18</v>
       </c>
       <c r="F1320" s="2" t="s">
-        <v>2419</v>
+        <v>2414</v>
       </c>
       <c r="G1320" s="2" t="s">
-        <v>2350</v>
+        <v>2345</v>
       </c>
       <c r="H1320" t="s">
-        <v>2420</v>
+        <v>2415</v>
       </c>
       <c r="I1320" t="s">
-        <v>2421</v>
+        <v>2416</v>
       </c>
     </row>
     <row r="1321" spans="1:9" x14ac:dyDescent="0.45">
@@ -39174,25 +39167,25 @@
         <v>4</v>
       </c>
       <c r="C1321" t="s">
-        <v>2347</v>
+        <v>2342</v>
       </c>
       <c r="D1321" s="2" t="s">
-        <v>2422</v>
+        <v>2417</v>
       </c>
       <c r="E1321" s="2">
         <v>19</v>
       </c>
       <c r="F1321" s="2" t="s">
-        <v>2423</v>
+        <v>2418</v>
       </c>
       <c r="G1321" s="2" t="s">
-        <v>2350</v>
+        <v>2345</v>
       </c>
       <c r="H1321" t="s">
-        <v>2424</v>
+        <v>2419</v>
       </c>
       <c r="I1321" t="s">
-        <v>2425</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="1322" spans="1:9" x14ac:dyDescent="0.45">
@@ -39203,25 +39196,25 @@
         <v>4</v>
       </c>
       <c r="C1322" t="s">
-        <v>2347</v>
+        <v>2342</v>
       </c>
       <c r="D1322" s="2" t="s">
-        <v>2426</v>
+        <v>2421</v>
       </c>
       <c r="E1322" s="2">
         <v>20</v>
       </c>
       <c r="F1322" s="2" t="s">
-        <v>2427</v>
+        <v>2422</v>
       </c>
       <c r="G1322" s="2" t="s">
-        <v>2350</v>
+        <v>2345</v>
       </c>
       <c r="H1322" t="s">
-        <v>2428</v>
+        <v>2423</v>
       </c>
       <c r="I1322" t="s">
-        <v>2429</v>
+        <v>2424</v>
       </c>
     </row>
     <row r="1323" spans="1:9" x14ac:dyDescent="0.45">
@@ -39232,25 +39225,25 @@
         <v>4</v>
       </c>
       <c r="C1323" t="s">
-        <v>2347</v>
+        <v>2342</v>
       </c>
       <c r="D1323" s="2" t="s">
-        <v>2430</v>
+        <v>2425</v>
       </c>
       <c r="E1323" s="2">
         <v>21</v>
       </c>
       <c r="F1323" s="2" t="s">
-        <v>2431</v>
+        <v>2426</v>
       </c>
       <c r="G1323" s="2" t="s">
-        <v>2432</v>
+        <v>2427</v>
       </c>
       <c r="H1323" t="s">
-        <v>2433</v>
+        <v>2428</v>
       </c>
       <c r="I1323" t="s">
-        <v>2434</v>
+        <v>2429</v>
       </c>
     </row>
     <row r="1324" spans="1:9" x14ac:dyDescent="0.45">
@@ -39261,25 +39254,25 @@
         <v>4</v>
       </c>
       <c r="C1324" t="s">
-        <v>2347</v>
+        <v>2342</v>
       </c>
       <c r="D1324" s="2" t="s">
-        <v>2435</v>
+        <v>2430</v>
       </c>
       <c r="E1324" s="2">
         <v>22</v>
       </c>
       <c r="F1324" s="2" t="s">
-        <v>2436</v>
+        <v>2431</v>
       </c>
       <c r="G1324" s="2" t="s">
-        <v>2350</v>
+        <v>2345</v>
       </c>
       <c r="H1324" t="s">
-        <v>2437</v>
+        <v>2432</v>
       </c>
       <c r="I1324" t="s">
-        <v>2438</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="1325" spans="1:9" x14ac:dyDescent="0.45">
@@ -39290,25 +39283,25 @@
         <v>4</v>
       </c>
       <c r="C1325" t="s">
-        <v>2347</v>
+        <v>2342</v>
       </c>
       <c r="D1325" s="2" t="s">
-        <v>2439</v>
+        <v>2434</v>
       </c>
       <c r="E1325" s="2">
         <v>23</v>
       </c>
       <c r="F1325" s="2" t="s">
-        <v>2440</v>
+        <v>2435</v>
       </c>
       <c r="G1325" s="2" t="s">
-        <v>2350</v>
+        <v>2345</v>
       </c>
       <c r="H1325" t="s">
-        <v>2441</v>
+        <v>2436</v>
       </c>
       <c r="I1325" t="s">
-        <v>2442</v>
+        <v>2437</v>
       </c>
     </row>
     <row r="1326" spans="1:9" x14ac:dyDescent="0.45">
@@ -39319,25 +39312,25 @@
         <v>4</v>
       </c>
       <c r="C1326" t="s">
-        <v>2347</v>
+        <v>2342</v>
       </c>
       <c r="D1326" s="2" t="s">
-        <v>2443</v>
+        <v>2438</v>
       </c>
       <c r="E1326" s="2">
         <v>24</v>
       </c>
       <c r="F1326" s="2" t="s">
-        <v>2444</v>
+        <v>2439</v>
       </c>
       <c r="G1326" s="2" t="s">
-        <v>2350</v>
+        <v>2345</v>
       </c>
       <c r="H1326" t="s">
-        <v>2445</v>
+        <v>2440</v>
       </c>
       <c r="I1326" t="s">
-        <v>2446</v>
+        <v>2441</v>
       </c>
     </row>
     <row r="1327" spans="1:9" x14ac:dyDescent="0.45">
@@ -39348,25 +39341,25 @@
         <v>4</v>
       </c>
       <c r="C1327" t="s">
-        <v>2347</v>
+        <v>2342</v>
       </c>
       <c r="D1327" s="2" t="s">
-        <v>2447</v>
+        <v>2442</v>
       </c>
       <c r="E1327" s="2">
         <v>25</v>
       </c>
       <c r="F1327" s="2" t="s">
-        <v>2448</v>
+        <v>2443</v>
       </c>
       <c r="G1327" s="2" t="s">
-        <v>2350</v>
+        <v>2345</v>
       </c>
       <c r="H1327" t="s">
-        <v>2449</v>
+        <v>2444</v>
       </c>
       <c r="I1327" t="s">
-        <v>2450</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="1328" spans="1:9" x14ac:dyDescent="0.45">
@@ -39377,25 +39370,25 @@
         <v>4</v>
       </c>
       <c r="C1328" t="s">
-        <v>2347</v>
+        <v>2342</v>
       </c>
       <c r="D1328" s="2" t="s">
-        <v>2451</v>
+        <v>2446</v>
       </c>
       <c r="E1328" s="2">
         <v>26</v>
       </c>
       <c r="F1328" s="2" t="s">
-        <v>2452</v>
+        <v>2447</v>
       </c>
       <c r="G1328" s="2" t="s">
-        <v>2350</v>
+        <v>2345</v>
       </c>
       <c r="H1328" t="s">
-        <v>2453</v>
+        <v>2448</v>
       </c>
       <c r="I1328" t="s">
-        <v>2454</v>
+        <v>2449</v>
       </c>
     </row>
     <row r="1329" spans="1:9" x14ac:dyDescent="0.45">
@@ -39406,25 +39399,25 @@
         <v>4</v>
       </c>
       <c r="C1329" t="s">
-        <v>2347</v>
+        <v>2342</v>
       </c>
       <c r="D1329" s="2" t="s">
-        <v>2455</v>
+        <v>2450</v>
       </c>
       <c r="E1329" s="2">
         <v>27</v>
       </c>
       <c r="F1329" s="2" t="s">
-        <v>2456</v>
+        <v>2451</v>
       </c>
       <c r="G1329" s="2" t="s">
-        <v>2350</v>
+        <v>2345</v>
       </c>
       <c r="H1329" t="s">
-        <v>2457</v>
+        <v>2452</v>
       </c>
       <c r="I1329" t="s">
-        <v>2458</v>
+        <v>2453</v>
       </c>
     </row>
     <row r="1330" spans="1:9" x14ac:dyDescent="0.45">
@@ -39435,25 +39428,25 @@
         <v>4</v>
       </c>
       <c r="C1330" t="s">
-        <v>2347</v>
+        <v>2342</v>
       </c>
       <c r="D1330" s="2" t="s">
-        <v>2459</v>
+        <v>2454</v>
       </c>
       <c r="E1330" s="2">
         <v>28</v>
       </c>
       <c r="F1330" s="2" t="s">
-        <v>2460</v>
+        <v>2455</v>
       </c>
       <c r="G1330" s="2" t="s">
-        <v>2350</v>
+        <v>2345</v>
       </c>
       <c r="H1330" t="s">
-        <v>2461</v>
+        <v>2456</v>
       </c>
       <c r="I1330" t="s">
-        <v>2462</v>
+        <v>2457</v>
       </c>
     </row>
     <row r="1331" spans="1:9" x14ac:dyDescent="0.45">
@@ -39464,25 +39457,25 @@
         <v>4</v>
       </c>
       <c r="C1331" t="s">
-        <v>2347</v>
+        <v>2342</v>
       </c>
       <c r="D1331" s="2" t="s">
-        <v>2463</v>
+        <v>2458</v>
       </c>
       <c r="E1331" s="2">
         <v>29</v>
       </c>
       <c r="F1331" s="2" t="s">
-        <v>2464</v>
+        <v>2459</v>
       </c>
       <c r="G1331" s="2" t="s">
-        <v>2350</v>
+        <v>2345</v>
       </c>
       <c r="H1331" t="s">
-        <v>2465</v>
+        <v>2460</v>
       </c>
       <c r="I1331" t="s">
-        <v>2466</v>
+        <v>2461</v>
       </c>
     </row>
     <row r="1332" spans="1:9" x14ac:dyDescent="0.45">
@@ -39493,25 +39486,25 @@
         <v>4</v>
       </c>
       <c r="C1332" t="s">
-        <v>2347</v>
+        <v>2342</v>
       </c>
       <c r="D1332" s="2" t="s">
-        <v>2467</v>
+        <v>2462</v>
       </c>
       <c r="E1332" s="2">
         <v>30</v>
       </c>
       <c r="F1332" s="2" t="s">
-        <v>2468</v>
+        <v>2463</v>
       </c>
       <c r="G1332" s="2" t="s">
-        <v>2350</v>
+        <v>2345</v>
       </c>
       <c r="H1332" t="s">
-        <v>2469</v>
+        <v>2464</v>
       </c>
       <c r="I1332" t="s">
-        <v>2470</v>
+        <v>2465</v>
       </c>
     </row>
     <row r="1333" spans="1:9" x14ac:dyDescent="0.45">
@@ -39522,25 +39515,25 @@
         <v>4</v>
       </c>
       <c r="C1333" t="s">
-        <v>2347</v>
+        <v>2342</v>
       </c>
       <c r="D1333" s="2" t="s">
-        <v>2471</v>
+        <v>2466</v>
       </c>
       <c r="E1333" s="2">
         <v>31</v>
       </c>
       <c r="F1333" s="2" t="s">
-        <v>2472</v>
+        <v>2467</v>
       </c>
       <c r="G1333" s="2" t="s">
-        <v>2471</v>
+        <v>2466</v>
       </c>
       <c r="H1333" t="s">
-        <v>2473</v>
+        <v>2468</v>
       </c>
       <c r="I1333" t="s">
-        <v>2474</v>
+        <v>2469</v>
       </c>
     </row>
     <row r="1334" spans="1:9" x14ac:dyDescent="0.45">
@@ -39551,25 +39544,25 @@
         <v>4</v>
       </c>
       <c r="C1334" t="s">
-        <v>2347</v>
+        <v>2342</v>
       </c>
       <c r="D1334" s="2" t="s">
-        <v>2475</v>
+        <v>2470</v>
       </c>
       <c r="E1334" s="2">
         <v>32</v>
       </c>
       <c r="F1334" s="2" t="s">
-        <v>2476</v>
+        <v>2471</v>
       </c>
       <c r="G1334" s="2" t="s">
-        <v>2350</v>
+        <v>2345</v>
       </c>
       <c r="H1334" t="s">
-        <v>2477</v>
+        <v>2472</v>
       </c>
       <c r="I1334" t="s">
-        <v>2478</v>
+        <v>2473</v>
       </c>
     </row>
     <row r="1335" spans="1:9" x14ac:dyDescent="0.45">
@@ -39580,25 +39573,25 @@
         <v>4</v>
       </c>
       <c r="C1335" t="s">
-        <v>2347</v>
+        <v>2342</v>
       </c>
       <c r="D1335" s="2" t="s">
-        <v>2479</v>
+        <v>2474</v>
       </c>
       <c r="E1335" s="2">
         <v>33</v>
       </c>
       <c r="F1335" s="2" t="s">
-        <v>2480</v>
+        <v>2475</v>
       </c>
       <c r="G1335" s="2" t="s">
-        <v>2350</v>
+        <v>2345</v>
       </c>
       <c r="H1335" t="s">
-        <v>2481</v>
+        <v>2476</v>
       </c>
       <c r="I1335" t="s">
-        <v>2482</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="1336" spans="1:9" x14ac:dyDescent="0.45">
@@ -39609,25 +39602,25 @@
         <v>4</v>
       </c>
       <c r="C1336" t="s">
-        <v>2347</v>
+        <v>2342</v>
       </c>
       <c r="D1336" s="2" t="s">
-        <v>2483</v>
+        <v>2478</v>
       </c>
       <c r="E1336" s="2">
         <v>34</v>
       </c>
       <c r="F1336" s="2" t="s">
-        <v>2484</v>
+        <v>2479</v>
       </c>
       <c r="G1336" s="2" t="s">
-        <v>2350</v>
+        <v>2345</v>
       </c>
       <c r="H1336" t="s">
-        <v>2485</v>
+        <v>2480</v>
       </c>
       <c r="I1336" t="s">
-        <v>2486</v>
+        <v>2481</v>
       </c>
     </row>
     <row r="1337" spans="1:9" x14ac:dyDescent="0.45">
@@ -39638,25 +39631,25 @@
         <v>4</v>
       </c>
       <c r="C1337" t="s">
-        <v>2347</v>
+        <v>2342</v>
       </c>
       <c r="D1337" s="2" t="s">
-        <v>2487</v>
+        <v>2482</v>
       </c>
       <c r="E1337" s="2">
         <v>35</v>
       </c>
       <c r="F1337" s="2" t="s">
-        <v>2488</v>
+        <v>2483</v>
       </c>
       <c r="G1337" s="2" t="s">
-        <v>2350</v>
+        <v>2345</v>
       </c>
       <c r="H1337" t="s">
-        <v>2489</v>
+        <v>2484</v>
       </c>
       <c r="I1337" t="s">
-        <v>2490</v>
+        <v>2485</v>
       </c>
     </row>
     <row r="1338" spans="1:9" x14ac:dyDescent="0.45">
@@ -39667,25 +39660,25 @@
         <v>4</v>
       </c>
       <c r="C1338" t="s">
-        <v>2347</v>
+        <v>2342</v>
       </c>
       <c r="D1338" s="2" t="s">
-        <v>2491</v>
+        <v>2486</v>
       </c>
       <c r="E1338" s="2">
         <v>36</v>
       </c>
       <c r="F1338" s="2" t="s">
-        <v>2492</v>
+        <v>2487</v>
       </c>
       <c r="G1338" s="2" t="s">
-        <v>2350</v>
+        <v>2345</v>
       </c>
       <c r="H1338" t="s">
-        <v>2493</v>
+        <v>2488</v>
       </c>
       <c r="I1338" t="s">
-        <v>2494</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="1339" spans="1:9" x14ac:dyDescent="0.45">
@@ -39696,25 +39689,25 @@
         <v>4</v>
       </c>
       <c r="C1339" t="s">
-        <v>2347</v>
+        <v>2342</v>
       </c>
       <c r="D1339" s="2" t="s">
-        <v>2495</v>
+        <v>2490</v>
       </c>
       <c r="E1339" s="2">
         <v>37</v>
       </c>
       <c r="F1339" s="2" t="s">
-        <v>2496</v>
+        <v>2491</v>
       </c>
       <c r="G1339" s="2" t="s">
-        <v>2350</v>
+        <v>2345</v>
       </c>
       <c r="H1339" t="s">
-        <v>2497</v>
+        <v>2492</v>
       </c>
       <c r="I1339" t="s">
-        <v>2498</v>
+        <v>2493</v>
       </c>
     </row>
     <row r="1340" spans="1:9" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -39725,25 +39718,25 @@
         <v>4</v>
       </c>
       <c r="C1340" t="s">
-        <v>2347</v>
+        <v>2342</v>
       </c>
       <c r="D1340" s="2" t="s">
-        <v>2499</v>
+        <v>2494</v>
       </c>
       <c r="E1340" s="2">
         <v>38</v>
       </c>
       <c r="F1340" s="2" t="s">
-        <v>2500</v>
+        <v>2495</v>
       </c>
       <c r="G1340" s="2" t="s">
-        <v>2350</v>
+        <v>2345</v>
       </c>
       <c r="H1340" t="s">
-        <v>2501</v>
+        <v>2496</v>
       </c>
       <c r="I1340" t="s">
-        <v>2502</v>
+        <v>2497</v>
       </c>
     </row>
     <row r="1341" spans="1:9" x14ac:dyDescent="0.45">
@@ -39754,25 +39747,25 @@
         <v>4</v>
       </c>
       <c r="C1341" t="s">
-        <v>2347</v>
+        <v>2342</v>
       </c>
       <c r="D1341" s="2" t="s">
-        <v>2503</v>
+        <v>2498</v>
       </c>
       <c r="E1341" s="2">
         <v>39</v>
       </c>
       <c r="F1341" s="2" t="s">
-        <v>2504</v>
+        <v>2499</v>
       </c>
       <c r="G1341" s="2" t="s">
-        <v>2350</v>
+        <v>2345</v>
       </c>
       <c r="H1341" t="s">
-        <v>2505</v>
+        <v>2500</v>
       </c>
       <c r="I1341" t="s">
-        <v>2506</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="1342" spans="1:9" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -39783,25 +39776,25 @@
         <v>4</v>
       </c>
       <c r="C1342" t="s">
-        <v>2347</v>
+        <v>2342</v>
       </c>
       <c r="D1342" s="2" t="s">
-        <v>2507</v>
+        <v>2502</v>
       </c>
       <c r="E1342" s="2">
         <v>40</v>
       </c>
       <c r="F1342" s="2" t="s">
-        <v>2508</v>
+        <v>2503</v>
       </c>
       <c r="G1342" s="2" t="s">
-        <v>2350</v>
+        <v>2345</v>
       </c>
       <c r="H1342" t="s">
-        <v>2509</v>
+        <v>2504</v>
       </c>
       <c r="I1342" t="s">
-        <v>2510</v>
+        <v>2505</v>
       </c>
     </row>
     <row r="1343" spans="1:9" x14ac:dyDescent="0.45">
@@ -39812,19 +39805,19 @@
         <v>5</v>
       </c>
       <c r="C1343" t="s">
-        <v>2511</v>
+        <v>2506</v>
       </c>
       <c r="D1343" s="2" t="s">
-        <v>2512</v>
+        <v>2507</v>
       </c>
       <c r="E1343" s="2">
         <v>1</v>
       </c>
       <c r="F1343" s="2" t="s">
-        <v>2513</v>
+        <v>2508</v>
       </c>
       <c r="G1343" s="2" t="s">
-        <v>2514</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="1344" spans="1:9" x14ac:dyDescent="0.45">
@@ -39835,19 +39828,19 @@
         <v>5</v>
       </c>
       <c r="C1344" t="s">
-        <v>2511</v>
+        <v>2506</v>
       </c>
       <c r="D1344" s="2" t="s">
-        <v>2515</v>
+        <v>2510</v>
       </c>
       <c r="E1344" s="2">
         <v>2</v>
       </c>
       <c r="F1344" s="2" t="s">
-        <v>2513</v>
+        <v>2508</v>
       </c>
       <c r="G1344" s="2" t="s">
-        <v>2514</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="1345" spans="1:7" x14ac:dyDescent="0.45">
@@ -39858,19 +39851,19 @@
         <v>5</v>
       </c>
       <c r="C1345" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D1345" s="2" t="s">
         <v>2511</v>
-      </c>
-      <c r="D1345" s="2" t="s">
-        <v>2516</v>
       </c>
       <c r="E1345" s="2">
         <v>3</v>
       </c>
       <c r="F1345" s="2" t="s">
-        <v>2513</v>
+        <v>2508</v>
       </c>
       <c r="G1345" s="2" t="s">
-        <v>2514</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="1346" spans="1:7" x14ac:dyDescent="0.45">
@@ -39881,19 +39874,19 @@
         <v>5</v>
       </c>
       <c r="C1346" t="s">
-        <v>2511</v>
+        <v>2506</v>
       </c>
       <c r="D1346" s="2" t="s">
-        <v>2517</v>
+        <v>2512</v>
       </c>
       <c r="E1346" s="2">
         <v>4</v>
       </c>
       <c r="F1346" s="2" t="s">
-        <v>2518</v>
+        <v>2513</v>
       </c>
       <c r="G1346" s="2" t="s">
-        <v>2514</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="1347" spans="1:7" x14ac:dyDescent="0.45">
@@ -39904,19 +39897,19 @@
         <v>5</v>
       </c>
       <c r="C1347" t="s">
-        <v>2511</v>
+        <v>2506</v>
       </c>
       <c r="D1347" s="2" t="s">
-        <v>2519</v>
+        <v>2514</v>
       </c>
       <c r="E1347" s="2">
         <v>5</v>
       </c>
       <c r="F1347" s="2" t="s">
-        <v>2518</v>
+        <v>2513</v>
       </c>
       <c r="G1347" s="2" t="s">
-        <v>2514</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="1348" spans="1:7" x14ac:dyDescent="0.45">
@@ -39927,19 +39920,19 @@
         <v>5</v>
       </c>
       <c r="C1348" t="s">
-        <v>2511</v>
+        <v>2506</v>
       </c>
       <c r="D1348" s="2" t="s">
-        <v>2520</v>
+        <v>2515</v>
       </c>
       <c r="E1348" s="2">
         <v>6</v>
       </c>
       <c r="F1348" s="2" t="s">
-        <v>2518</v>
+        <v>2513</v>
       </c>
       <c r="G1348" s="2" t="s">
-        <v>2514</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="1349" spans="1:7" x14ac:dyDescent="0.45">
@@ -39950,19 +39943,19 @@
         <v>5</v>
       </c>
       <c r="C1349" t="s">
-        <v>2511</v>
+        <v>2506</v>
       </c>
       <c r="D1349" s="2" t="s">
-        <v>2521</v>
+        <v>2516</v>
       </c>
       <c r="E1349" s="2">
         <v>7</v>
       </c>
       <c r="F1349" s="2" t="s">
-        <v>2522</v>
+        <v>2517</v>
       </c>
       <c r="G1349" s="2" t="s">
-        <v>2514</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="1350" spans="1:7" x14ac:dyDescent="0.45">
@@ -39973,19 +39966,19 @@
         <v>5</v>
       </c>
       <c r="C1350" t="s">
-        <v>2511</v>
+        <v>2506</v>
       </c>
       <c r="D1350" s="2" t="s">
-        <v>2523</v>
+        <v>2518</v>
       </c>
       <c r="E1350" s="2">
         <v>8</v>
       </c>
       <c r="F1350" s="2" t="s">
-        <v>2522</v>
+        <v>2517</v>
       </c>
       <c r="G1350" s="2" t="s">
-        <v>2514</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="1351" spans="1:7" x14ac:dyDescent="0.45">
@@ -39996,19 +39989,19 @@
         <v>5</v>
       </c>
       <c r="C1351" t="s">
-        <v>2511</v>
+        <v>2506</v>
       </c>
       <c r="D1351" s="2" t="s">
-        <v>2524</v>
+        <v>2519</v>
       </c>
       <c r="E1351" s="2">
         <v>9</v>
       </c>
       <c r="F1351" s="2" t="s">
-        <v>2522</v>
+        <v>2517</v>
       </c>
       <c r="G1351" s="2" t="s">
-        <v>2514</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="1352" spans="1:7" x14ac:dyDescent="0.45">
@@ -40019,19 +40012,19 @@
         <v>5</v>
       </c>
       <c r="C1352" t="s">
-        <v>2511</v>
+        <v>2506</v>
       </c>
       <c r="D1352" s="2" t="s">
-        <v>2525</v>
+        <v>2520</v>
       </c>
       <c r="E1352" s="2">
         <v>10</v>
       </c>
       <c r="F1352" s="2" t="s">
-        <v>2522</v>
+        <v>2517</v>
       </c>
       <c r="G1352" s="2" t="s">
-        <v>2514</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="1353" spans="1:7" x14ac:dyDescent="0.45">
@@ -40042,19 +40035,19 @@
         <v>5</v>
       </c>
       <c r="C1353" t="s">
-        <v>2511</v>
+        <v>2506</v>
       </c>
       <c r="D1353" s="2" t="s">
-        <v>2526</v>
+        <v>2521</v>
       </c>
       <c r="E1353" s="2">
         <v>11</v>
       </c>
       <c r="F1353" s="2" t="s">
-        <v>2513</v>
+        <v>2508</v>
       </c>
       <c r="G1353" s="2" t="s">
-        <v>2513</v>
+        <v>2508</v>
       </c>
     </row>
     <row r="1354" spans="1:7" x14ac:dyDescent="0.45">
@@ -40065,19 +40058,19 @@
         <v>5</v>
       </c>
       <c r="C1354" t="s">
-        <v>2511</v>
+        <v>2506</v>
       </c>
       <c r="D1354" s="2" t="s">
-        <v>2527</v>
+        <v>2522</v>
       </c>
       <c r="E1354" s="2">
         <v>12</v>
       </c>
       <c r="F1354" s="2" t="s">
-        <v>2518</v>
+        <v>2513</v>
       </c>
       <c r="G1354" s="2" t="s">
-        <v>2514</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="1355" spans="1:7" x14ac:dyDescent="0.45">
@@ -40088,19 +40081,19 @@
         <v>5</v>
       </c>
       <c r="C1355" t="s">
-        <v>2511</v>
+        <v>2506</v>
       </c>
       <c r="D1355" s="2" t="s">
-        <v>2528</v>
+        <v>2523</v>
       </c>
       <c r="E1355" s="2">
         <v>13</v>
       </c>
       <c r="F1355" s="2" t="s">
-        <v>2522</v>
+        <v>2517</v>
       </c>
       <c r="G1355" s="2" t="s">
-        <v>2514</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="1356" spans="1:7" x14ac:dyDescent="0.45">
@@ -40111,19 +40104,19 @@
         <v>5</v>
       </c>
       <c r="C1356" t="s">
-        <v>2511</v>
+        <v>2506</v>
       </c>
       <c r="D1356" s="2" t="s">
-        <v>2529</v>
+        <v>2524</v>
       </c>
       <c r="E1356" s="2">
         <v>14</v>
       </c>
       <c r="F1356" s="2" t="s">
-        <v>2513</v>
+        <v>2508</v>
       </c>
       <c r="G1356" s="2" t="s">
-        <v>2514</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="1357" spans="1:7" x14ac:dyDescent="0.45">
@@ -40134,19 +40127,19 @@
         <v>5</v>
       </c>
       <c r="C1357" t="s">
-        <v>2511</v>
+        <v>2506</v>
       </c>
       <c r="D1357" s="2" t="s">
-        <v>2530</v>
+        <v>2525</v>
       </c>
       <c r="E1357" s="2">
         <v>15</v>
       </c>
       <c r="F1357" s="2" t="s">
-        <v>2518</v>
+        <v>2513</v>
       </c>
       <c r="G1357" s="2" t="s">
-        <v>2514</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="1358" spans="1:7" x14ac:dyDescent="0.45">
@@ -40157,19 +40150,19 @@
         <v>5</v>
       </c>
       <c r="C1358" t="s">
-        <v>2511</v>
+        <v>2506</v>
       </c>
       <c r="D1358" s="2" t="s">
-        <v>2531</v>
+        <v>2526</v>
       </c>
       <c r="E1358" s="2">
         <v>16</v>
       </c>
       <c r="F1358" s="2" t="s">
-        <v>2522</v>
+        <v>2517</v>
       </c>
       <c r="G1358" s="2" t="s">
-        <v>2514</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="1359" spans="1:7" x14ac:dyDescent="0.45">
@@ -40180,19 +40173,19 @@
         <v>5</v>
       </c>
       <c r="C1359" t="s">
-        <v>2511</v>
+        <v>2506</v>
       </c>
       <c r="D1359" s="2" t="s">
-        <v>2532</v>
+        <v>2527</v>
       </c>
       <c r="E1359" s="2">
         <v>17</v>
       </c>
       <c r="F1359" s="2" t="s">
-        <v>2513</v>
+        <v>2508</v>
       </c>
       <c r="G1359" s="2" t="s">
-        <v>2514</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="1360" spans="1:7" x14ac:dyDescent="0.45">
@@ -40203,19 +40196,19 @@
         <v>5</v>
       </c>
       <c r="C1360" t="s">
-        <v>2511</v>
+        <v>2506</v>
       </c>
       <c r="D1360" s="2" t="s">
-        <v>2533</v>
+        <v>2528</v>
       </c>
       <c r="E1360" s="2">
         <v>18</v>
       </c>
       <c r="F1360" s="2" t="s">
-        <v>2522</v>
+        <v>2517</v>
       </c>
       <c r="G1360" s="2" t="s">
-        <v>2514</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="1361" spans="1:7" x14ac:dyDescent="0.45">
@@ -40226,19 +40219,19 @@
         <v>5</v>
       </c>
       <c r="C1361" t="s">
-        <v>2511</v>
+        <v>2506</v>
       </c>
       <c r="D1361" s="2" t="s">
-        <v>2534</v>
+        <v>2529</v>
       </c>
       <c r="E1361" s="2">
         <v>19</v>
       </c>
       <c r="F1361" s="2" t="s">
-        <v>2518</v>
+        <v>2513</v>
       </c>
       <c r="G1361" s="2" t="s">
-        <v>2514</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="1362" spans="1:7" x14ac:dyDescent="0.45">
@@ -40249,19 +40242,19 @@
         <v>5</v>
       </c>
       <c r="C1362" t="s">
-        <v>2511</v>
+        <v>2506</v>
       </c>
       <c r="D1362" s="2" t="s">
-        <v>2535</v>
+        <v>2530</v>
       </c>
       <c r="E1362" s="2">
         <v>20</v>
       </c>
       <c r="F1362" s="2" t="s">
-        <v>2522</v>
+        <v>2517</v>
       </c>
       <c r="G1362" s="2" t="s">
-        <v>2514</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="1363" spans="1:7" x14ac:dyDescent="0.45">
@@ -40272,19 +40265,19 @@
         <v>6</v>
       </c>
       <c r="C1363" t="s">
-        <v>2536</v>
+        <v>2531</v>
       </c>
       <c r="D1363" s="2" t="s">
-        <v>2537</v>
+        <v>2532</v>
       </c>
       <c r="E1363" s="2">
         <v>1</v>
       </c>
       <c r="F1363" s="2" t="s">
-        <v>2538</v>
+        <v>2533</v>
       </c>
       <c r="G1363" s="2" t="s">
-        <v>2539</v>
+        <v>2534</v>
       </c>
     </row>
     <row r="1364" spans="1:7" x14ac:dyDescent="0.45">
@@ -40295,10 +40288,10 @@
         <v>6</v>
       </c>
       <c r="C1364" t="s">
-        <v>2536</v>
+        <v>2531</v>
       </c>
       <c r="D1364" s="2" t="s">
-        <v>2540</v>
+        <v>2535</v>
       </c>
       <c r="E1364" s="2">
         <v>2</v>
@@ -40307,7 +40300,7 @@
         <v>1853</v>
       </c>
       <c r="G1364" s="2" t="s">
-        <v>2541</v>
+        <v>2536</v>
       </c>
     </row>
     <row r="1365" spans="1:7" x14ac:dyDescent="0.45">
@@ -40318,19 +40311,19 @@
         <v>6</v>
       </c>
       <c r="C1365" t="s">
-        <v>2536</v>
+        <v>2531</v>
       </c>
       <c r="D1365" s="2" t="s">
-        <v>2542</v>
+        <v>2537</v>
       </c>
       <c r="E1365" s="2">
         <v>3</v>
       </c>
       <c r="F1365" s="2" t="s">
-        <v>2543</v>
+        <v>2538</v>
       </c>
       <c r="G1365" s="2" t="s">
-        <v>2544</v>
+        <v>2539</v>
       </c>
     </row>
     <row r="1366" spans="1:7" x14ac:dyDescent="0.45">
@@ -40341,19 +40334,19 @@
         <v>6</v>
       </c>
       <c r="C1366" t="s">
-        <v>2536</v>
+        <v>2531</v>
       </c>
       <c r="D1366" s="2" t="s">
-        <v>2545</v>
+        <v>2540</v>
       </c>
       <c r="E1366" s="2">
         <v>4</v>
       </c>
       <c r="F1366" s="2" t="s">
-        <v>2546</v>
+        <v>2541</v>
       </c>
       <c r="G1366" s="2" t="s">
-        <v>2544</v>
+        <v>2539</v>
       </c>
     </row>
     <row r="1367" spans="1:7" x14ac:dyDescent="0.45">
@@ -40364,19 +40357,19 @@
         <v>6</v>
       </c>
       <c r="C1367" t="s">
-        <v>2536</v>
+        <v>2531</v>
       </c>
       <c r="D1367" s="2" t="s">
-        <v>2547</v>
+        <v>2542</v>
       </c>
       <c r="E1367" s="2">
         <v>5</v>
       </c>
       <c r="F1367" s="2" t="s">
-        <v>2548</v>
+        <v>2543</v>
       </c>
       <c r="G1367" s="2" t="s">
-        <v>2549</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="1368" spans="1:7" x14ac:dyDescent="0.45">
@@ -40387,19 +40380,19 @@
         <v>6</v>
       </c>
       <c r="C1368" t="s">
-        <v>2536</v>
+        <v>2531</v>
       </c>
       <c r="D1368" s="2" t="s">
-        <v>2550</v>
+        <v>2545</v>
       </c>
       <c r="E1368" s="2">
         <v>6</v>
       </c>
       <c r="F1368" s="2" t="s">
-        <v>2543</v>
+        <v>2538</v>
       </c>
       <c r="G1368" s="2" t="s">
-        <v>2549</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="1369" spans="1:7" x14ac:dyDescent="0.45">
@@ -40410,19 +40403,19 @@
         <v>6</v>
       </c>
       <c r="C1369" t="s">
-        <v>2536</v>
+        <v>2531</v>
       </c>
       <c r="D1369" s="2" t="s">
-        <v>2551</v>
+        <v>2546</v>
       </c>
       <c r="E1369" s="2">
         <v>7</v>
       </c>
       <c r="F1369" s="2" t="s">
-        <v>2552</v>
+        <v>2547</v>
       </c>
       <c r="G1369" s="2" t="s">
-        <v>2553</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="1370" spans="1:7" x14ac:dyDescent="0.45">
@@ -40433,19 +40426,19 @@
         <v>6</v>
       </c>
       <c r="C1370" t="s">
-        <v>2536</v>
+        <v>2531</v>
       </c>
       <c r="D1370" s="2" t="s">
-        <v>2554</v>
+        <v>2549</v>
       </c>
       <c r="E1370" s="2">
         <v>8</v>
       </c>
       <c r="F1370" s="2" t="s">
-        <v>2555</v>
+        <v>2550</v>
       </c>
       <c r="G1370" s="2" t="s">
-        <v>2556</v>
+        <v>2551</v>
       </c>
     </row>
     <row r="1371" spans="1:7" x14ac:dyDescent="0.45">
@@ -40456,19 +40449,19 @@
         <v>6</v>
       </c>
       <c r="C1371" t="s">
-        <v>2536</v>
+        <v>2531</v>
       </c>
       <c r="D1371" s="2" t="s">
-        <v>2557</v>
+        <v>2552</v>
       </c>
       <c r="E1371" s="2">
         <v>9</v>
       </c>
       <c r="F1371" s="2" t="s">
-        <v>2558</v>
+        <v>2553</v>
       </c>
       <c r="G1371" s="2" t="s">
-        <v>2559</v>
+        <v>2554</v>
       </c>
     </row>
     <row r="1372" spans="1:7" x14ac:dyDescent="0.45">
@@ -40479,19 +40472,19 @@
         <v>6</v>
       </c>
       <c r="C1372" t="s">
-        <v>2536</v>
+        <v>2531</v>
       </c>
       <c r="D1372" s="2" t="s">
-        <v>2560</v>
+        <v>2555</v>
       </c>
       <c r="E1372" s="2">
         <v>10</v>
       </c>
       <c r="F1372" s="2" t="s">
-        <v>2561</v>
+        <v>2556</v>
       </c>
       <c r="G1372" s="2" t="s">
-        <v>2539</v>
+        <v>2534</v>
       </c>
     </row>
     <row r="1373" spans="1:7" x14ac:dyDescent="0.45">
@@ -40502,19 +40495,19 @@
         <v>6</v>
       </c>
       <c r="C1373" t="s">
-        <v>2536</v>
+        <v>2531</v>
       </c>
       <c r="D1373" s="2" t="s">
-        <v>2562</v>
+        <v>2557</v>
       </c>
       <c r="E1373" s="2">
         <v>11</v>
       </c>
       <c r="F1373" s="2" t="s">
-        <v>2563</v>
+        <v>2558</v>
       </c>
       <c r="G1373" s="2" t="s">
-        <v>2563</v>
+        <v>2558</v>
       </c>
     </row>
     <row r="1374" spans="1:7" x14ac:dyDescent="0.45">
@@ -40525,19 +40518,19 @@
         <v>6</v>
       </c>
       <c r="C1374" t="s">
-        <v>2536</v>
+        <v>2531</v>
       </c>
       <c r="D1374" s="2" t="s">
-        <v>2564</v>
+        <v>2559</v>
       </c>
       <c r="E1374" s="2">
         <v>12</v>
       </c>
       <c r="F1374" s="2" t="s">
-        <v>2565</v>
+        <v>2560</v>
       </c>
       <c r="G1374" s="2" t="s">
-        <v>2566</v>
+        <v>2561</v>
       </c>
     </row>
     <row r="1375" spans="1:7" x14ac:dyDescent="0.45">
@@ -40548,10 +40541,10 @@
         <v>6</v>
       </c>
       <c r="C1375" t="s">
-        <v>2536</v>
+        <v>2531</v>
       </c>
       <c r="D1375" s="2" t="s">
-        <v>2567</v>
+        <v>2562</v>
       </c>
       <c r="E1375" s="2">
         <v>13</v>
@@ -40560,7 +40553,7 @@
         <v>1418</v>
       </c>
       <c r="G1375" s="2" t="s">
-        <v>2568</v>
+        <v>2563</v>
       </c>
     </row>
     <row r="1376" spans="1:7" x14ac:dyDescent="0.45">
@@ -40571,19 +40564,19 @@
         <v>6</v>
       </c>
       <c r="C1376" t="s">
-        <v>2536</v>
+        <v>2531</v>
       </c>
       <c r="D1376" s="2" t="s">
-        <v>2569</v>
+        <v>2564</v>
       </c>
       <c r="E1376" s="2">
         <v>14</v>
       </c>
       <c r="F1376" s="2" t="s">
-        <v>2552</v>
+        <v>2547</v>
       </c>
       <c r="G1376" s="2" t="s">
-        <v>2570</v>
+        <v>2565</v>
       </c>
     </row>
     <row r="1377" spans="1:7" x14ac:dyDescent="0.45">
@@ -40594,10 +40587,10 @@
         <v>6</v>
       </c>
       <c r="C1377" t="s">
-        <v>2536</v>
+        <v>2531</v>
       </c>
       <c r="D1377" s="2" t="s">
-        <v>2571</v>
+        <v>2566</v>
       </c>
       <c r="E1377" s="2">
         <v>15</v>
@@ -40606,7 +40599,7 @@
         <v>1418</v>
       </c>
       <c r="G1377" s="2" t="s">
-        <v>2572</v>
+        <v>2567</v>
       </c>
     </row>
     <row r="1378" spans="1:7" x14ac:dyDescent="0.45">
@@ -40617,19 +40610,19 @@
         <v>6</v>
       </c>
       <c r="C1378" t="s">
-        <v>2536</v>
+        <v>2531</v>
       </c>
       <c r="D1378" s="2" t="s">
-        <v>2573</v>
+        <v>2568</v>
       </c>
       <c r="E1378" s="2">
         <v>16</v>
       </c>
       <c r="F1378" s="2" t="s">
-        <v>2552</v>
+        <v>2547</v>
       </c>
       <c r="G1378" s="2" t="s">
-        <v>2574</v>
+        <v>2569</v>
       </c>
     </row>
     <row r="1379" spans="1:7" x14ac:dyDescent="0.45">
@@ -40640,19 +40633,19 @@
         <v>6</v>
       </c>
       <c r="C1379" t="s">
-        <v>2536</v>
+        <v>2531</v>
       </c>
       <c r="D1379" s="2" t="s">
-        <v>2575</v>
+        <v>2570</v>
       </c>
       <c r="E1379" s="2">
         <v>17</v>
       </c>
       <c r="F1379" s="2" t="s">
-        <v>2576</v>
+        <v>2571</v>
       </c>
       <c r="G1379" s="2" t="s">
-        <v>2539</v>
+        <v>2534</v>
       </c>
     </row>
     <row r="1380" spans="1:7" x14ac:dyDescent="0.45">
@@ -40663,19 +40656,19 @@
         <v>6</v>
       </c>
       <c r="C1380" t="s">
-        <v>2536</v>
+        <v>2531</v>
       </c>
       <c r="D1380" s="2" t="s">
-        <v>2577</v>
+        <v>2572</v>
       </c>
       <c r="E1380" s="2">
         <v>18</v>
       </c>
       <c r="F1380" s="2" t="s">
-        <v>2578</v>
+        <v>2573</v>
       </c>
       <c r="G1380" s="2" t="s">
-        <v>2539</v>
+        <v>2534</v>
       </c>
     </row>
     <row r="1381" spans="1:7" x14ac:dyDescent="0.45">
@@ -40686,19 +40679,19 @@
         <v>6</v>
       </c>
       <c r="C1381" t="s">
-        <v>2536</v>
+        <v>2531</v>
       </c>
       <c r="D1381" s="2" t="s">
-        <v>2579</v>
+        <v>2574</v>
       </c>
       <c r="E1381" s="2">
         <v>19</v>
       </c>
       <c r="F1381" s="2" t="s">
-        <v>2552</v>
+        <v>2547</v>
       </c>
       <c r="G1381" s="2" t="s">
-        <v>2539</v>
+        <v>2534</v>
       </c>
     </row>
     <row r="1382" spans="1:7" x14ac:dyDescent="0.45">
@@ -40709,19 +40702,19 @@
         <v>6</v>
       </c>
       <c r="C1382" t="s">
-        <v>2536</v>
+        <v>2531</v>
       </c>
       <c r="D1382" s="2" t="s">
-        <v>2580</v>
+        <v>2575</v>
       </c>
       <c r="E1382" s="2">
         <v>20</v>
       </c>
       <c r="F1382" s="2" t="s">
-        <v>2581</v>
+        <v>2576</v>
       </c>
       <c r="G1382" s="2" t="s">
-        <v>2549</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="1383" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -40732,19 +40725,19 @@
         <v>7</v>
       </c>
       <c r="C1383" t="s">
-        <v>2582</v>
+        <v>2577</v>
       </c>
       <c r="D1383" t="s">
-        <v>2583</v>
+        <v>2578</v>
       </c>
       <c r="E1383" s="2">
         <v>1</v>
       </c>
       <c r="F1383" s="2" t="s">
-        <v>2584</v>
+        <v>2579</v>
       </c>
       <c r="G1383" s="2" t="s">
-        <v>2585</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="1384" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -40755,10 +40748,10 @@
         <v>7</v>
       </c>
       <c r="C1384" t="s">
-        <v>2582</v>
+        <v>2577</v>
       </c>
       <c r="D1384" t="s">
-        <v>2586</v>
+        <v>2581</v>
       </c>
       <c r="E1384" s="2">
         <v>2</v>
@@ -40767,7 +40760,7 @@
         <v>449</v>
       </c>
       <c r="G1384" s="2" t="s">
-        <v>2585</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="1385" spans="1:7" x14ac:dyDescent="0.45">
@@ -40778,10 +40771,10 @@
         <v>7</v>
       </c>
       <c r="C1385" t="s">
+        <v>2577</v>
+      </c>
+      <c r="D1385" t="s">
         <v>2582</v>
-      </c>
-      <c r="D1385" t="s">
-        <v>2587</v>
       </c>
       <c r="E1385" s="2">
         <v>3</v>
@@ -40790,7 +40783,7 @@
         <v>434</v>
       </c>
       <c r="G1385" s="2" t="s">
-        <v>2588</v>
+        <v>2583</v>
       </c>
     </row>
     <row r="1386" spans="1:7" x14ac:dyDescent="0.45">
@@ -40801,19 +40794,19 @@
         <v>7</v>
       </c>
       <c r="C1386" t="s">
-        <v>2582</v>
+        <v>2577</v>
       </c>
       <c r="D1386" t="s">
-        <v>2589</v>
+        <v>2584</v>
       </c>
       <c r="E1386" s="2">
         <v>4</v>
       </c>
       <c r="F1386" s="2" t="s">
-        <v>2590</v>
+        <v>2585</v>
       </c>
       <c r="G1386" s="2" t="s">
-        <v>2591</v>
+        <v>2586</v>
       </c>
     </row>
     <row r="1387" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -40824,10 +40817,10 @@
         <v>7</v>
       </c>
       <c r="C1387" t="s">
-        <v>2582</v>
+        <v>2577</v>
       </c>
       <c r="D1387" t="s">
-        <v>2592</v>
+        <v>2587</v>
       </c>
       <c r="E1387" s="2">
         <v>5</v>
@@ -40836,7 +40829,7 @@
         <v>26</v>
       </c>
       <c r="G1387" s="2" t="s">
-        <v>2593</v>
+        <v>2588</v>
       </c>
     </row>
     <row r="1388" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -40847,19 +40840,19 @@
         <v>7</v>
       </c>
       <c r="C1388" t="s">
-        <v>2582</v>
+        <v>2577</v>
       </c>
       <c r="D1388" t="s">
-        <v>2594</v>
+        <v>2589</v>
       </c>
       <c r="E1388" s="2">
         <v>6</v>
       </c>
       <c r="F1388" s="2" t="s">
-        <v>2595</v>
+        <v>2590</v>
       </c>
       <c r="G1388" s="2" t="s">
-        <v>2596</v>
+        <v>2591</v>
       </c>
     </row>
     <row r="1389" spans="1:7" x14ac:dyDescent="0.45">
@@ -40870,19 +40863,19 @@
         <v>7</v>
       </c>
       <c r="C1389" t="s">
-        <v>2582</v>
+        <v>2577</v>
       </c>
       <c r="D1389" t="s">
-        <v>2597</v>
+        <v>2592</v>
       </c>
       <c r="E1389" s="2">
         <v>7</v>
       </c>
       <c r="F1389" s="2" t="s">
-        <v>2598</v>
+        <v>2593</v>
       </c>
       <c r="G1389" s="2" t="s">
-        <v>2599</v>
+        <v>2594</v>
       </c>
     </row>
     <row r="1390" spans="1:7" x14ac:dyDescent="0.45">
@@ -40893,19 +40886,19 @@
         <v>7</v>
       </c>
       <c r="C1390" t="s">
-        <v>2582</v>
+        <v>2577</v>
       </c>
       <c r="D1390" t="s">
-        <v>2600</v>
+        <v>2595</v>
       </c>
       <c r="E1390" s="2">
         <v>8</v>
       </c>
       <c r="F1390" s="2" t="s">
-        <v>2601</v>
+        <v>2596</v>
       </c>
       <c r="G1390" s="2" t="s">
-        <v>2602</v>
+        <v>2597</v>
       </c>
     </row>
     <row r="1391" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -40916,19 +40909,19 @@
         <v>7</v>
       </c>
       <c r="C1391" t="s">
-        <v>2582</v>
+        <v>2577</v>
       </c>
       <c r="D1391" t="s">
-        <v>2603</v>
+        <v>2598</v>
       </c>
       <c r="E1391" s="2">
         <v>9</v>
       </c>
       <c r="F1391" s="2" t="s">
-        <v>2604</v>
+        <v>2599</v>
       </c>
       <c r="G1391" s="2" t="s">
-        <v>2605</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="1392" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -40939,19 +40932,19 @@
         <v>7</v>
       </c>
       <c r="C1392" t="s">
-        <v>2582</v>
+        <v>2577</v>
       </c>
       <c r="D1392" t="s">
-        <v>2606</v>
+        <v>2601</v>
       </c>
       <c r="E1392" s="2">
         <v>10</v>
       </c>
       <c r="F1392" s="2" t="s">
-        <v>2607</v>
+        <v>2602</v>
       </c>
       <c r="G1392" s="2" t="s">
-        <v>2608</v>
+        <v>2603</v>
       </c>
     </row>
     <row r="1393" spans="1:7" x14ac:dyDescent="0.45">
@@ -40962,19 +40955,19 @@
         <v>7</v>
       </c>
       <c r="C1393" t="s">
-        <v>2582</v>
+        <v>2577</v>
       </c>
       <c r="D1393" t="s">
-        <v>2609</v>
+        <v>2604</v>
       </c>
       <c r="E1393" s="2">
         <v>11</v>
       </c>
       <c r="F1393" s="2" t="s">
-        <v>2610</v>
+        <v>2605</v>
       </c>
       <c r="G1393" s="2" t="s">
-        <v>2610</v>
+        <v>2605</v>
       </c>
     </row>
     <row r="1394" spans="1:7" x14ac:dyDescent="0.45">
@@ -40985,10 +40978,10 @@
         <v>7</v>
       </c>
       <c r="C1394" t="s">
-        <v>2582</v>
+        <v>2577</v>
       </c>
       <c r="D1394" t="s">
-        <v>2611</v>
+        <v>2606</v>
       </c>
       <c r="E1394" s="2">
         <v>12</v>
@@ -40997,7 +40990,7 @@
         <v>384</v>
       </c>
       <c r="G1394" s="2" t="s">
-        <v>2612</v>
+        <v>2607</v>
       </c>
     </row>
     <row r="1395" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -41008,19 +41001,19 @@
         <v>7</v>
       </c>
       <c r="C1395" t="s">
-        <v>2582</v>
+        <v>2577</v>
       </c>
       <c r="D1395" t="s">
-        <v>2613</v>
+        <v>2608</v>
       </c>
       <c r="E1395" s="2">
         <v>13</v>
       </c>
       <c r="F1395" s="2" t="s">
-        <v>2614</v>
+        <v>2609</v>
       </c>
       <c r="G1395" s="2" t="s">
-        <v>2615</v>
+        <v>2610</v>
       </c>
     </row>
     <row r="1396" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -41031,19 +41024,19 @@
         <v>7</v>
       </c>
       <c r="C1396" t="s">
-        <v>2582</v>
+        <v>2577</v>
       </c>
       <c r="D1396" t="s">
-        <v>2616</v>
+        <v>2611</v>
       </c>
       <c r="E1396" s="2">
         <v>14</v>
       </c>
       <c r="F1396" s="2" t="s">
-        <v>2617</v>
+        <v>2612</v>
       </c>
       <c r="G1396" s="2" t="s">
-        <v>2618</v>
+        <v>2613</v>
       </c>
     </row>
     <row r="1397" spans="1:7" x14ac:dyDescent="0.45">
@@ -41054,19 +41047,19 @@
         <v>7</v>
       </c>
       <c r="C1397" t="s">
-        <v>2582</v>
+        <v>2577</v>
       </c>
       <c r="D1397" t="s">
-        <v>2619</v>
+        <v>2614</v>
       </c>
       <c r="E1397" s="2">
         <v>15</v>
       </c>
       <c r="F1397" s="2" t="s">
-        <v>2620</v>
+        <v>2615</v>
       </c>
       <c r="G1397" s="2" t="s">
-        <v>2621</v>
+        <v>2616</v>
       </c>
     </row>
     <row r="1398" spans="1:7" x14ac:dyDescent="0.45">
@@ -41077,10 +41070,10 @@
         <v>7</v>
       </c>
       <c r="C1398" t="s">
-        <v>2582</v>
+        <v>2577</v>
       </c>
       <c r="D1398" t="s">
-        <v>2622</v>
+        <v>2617</v>
       </c>
       <c r="E1398" s="2">
         <v>16</v>
@@ -41089,7 +41082,7 @@
         <v>449</v>
       </c>
       <c r="G1398" s="2" t="s">
-        <v>2623</v>
+        <v>2618</v>
       </c>
     </row>
     <row r="1399" spans="1:7" x14ac:dyDescent="0.45">
@@ -41100,19 +41093,19 @@
         <v>7</v>
       </c>
       <c r="C1399" t="s">
-        <v>2582</v>
+        <v>2577</v>
       </c>
       <c r="D1399" t="s">
-        <v>2624</v>
+        <v>2619</v>
       </c>
       <c r="E1399" s="2">
         <v>17</v>
       </c>
       <c r="F1399" s="2" t="s">
-        <v>2625</v>
+        <v>2620</v>
       </c>
       <c r="G1399" s="2" t="s">
-        <v>2626</v>
+        <v>2621</v>
       </c>
     </row>
     <row r="1400" spans="1:7" x14ac:dyDescent="0.45">
@@ -41123,19 +41116,19 @@
         <v>7</v>
       </c>
       <c r="C1400" t="s">
-        <v>2582</v>
+        <v>2577</v>
       </c>
       <c r="D1400" t="s">
-        <v>2627</v>
+        <v>2622</v>
       </c>
       <c r="E1400" s="2">
         <v>18</v>
       </c>
       <c r="F1400" s="2" t="s">
-        <v>2628</v>
+        <v>2623</v>
       </c>
       <c r="G1400" s="2" t="s">
-        <v>2629</v>
+        <v>2624</v>
       </c>
     </row>
     <row r="1401" spans="1:7" x14ac:dyDescent="0.45">
@@ -41146,19 +41139,19 @@
         <v>7</v>
       </c>
       <c r="C1401" t="s">
-        <v>2582</v>
+        <v>2577</v>
       </c>
       <c r="D1401" t="s">
-        <v>2630</v>
+        <v>2625</v>
       </c>
       <c r="E1401" s="2">
         <v>19</v>
       </c>
       <c r="F1401" s="2" t="s">
-        <v>2631</v>
+        <v>2626</v>
       </c>
       <c r="G1401" s="2" t="s">
-        <v>2632</v>
+        <v>2627</v>
       </c>
     </row>
     <row r="1402" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
@@ -41169,19 +41162,19 @@
         <v>7</v>
       </c>
       <c r="C1402" t="s">
-        <v>2582</v>
+        <v>2577</v>
       </c>
       <c r="D1402" t="s">
-        <v>2633</v>
+        <v>2628</v>
       </c>
       <c r="E1402" s="2">
         <v>20</v>
       </c>
       <c r="F1402" s="2" t="s">
-        <v>2634</v>
+        <v>2629</v>
       </c>
       <c r="G1402" s="2" t="s">
-        <v>2635</v>
+        <v>2630</v>
       </c>
     </row>
     <row r="1403" spans="1:7" x14ac:dyDescent="0.45">
@@ -41192,19 +41185,19 @@
         <v>1</v>
       </c>
       <c r="C1403" t="s">
-        <v>2636</v>
+        <v>2631</v>
       </c>
       <c r="D1403" s="2" t="s">
-        <v>2637</v>
+        <v>2632</v>
       </c>
       <c r="E1403" s="2">
         <v>1</v>
       </c>
       <c r="F1403" s="2" t="s">
-        <v>2638</v>
+        <v>2633</v>
       </c>
       <c r="G1403" s="2" t="s">
-        <v>2639</v>
+        <v>2634</v>
       </c>
     </row>
     <row r="1404" spans="1:7" x14ac:dyDescent="0.45">
@@ -41215,19 +41208,19 @@
         <v>1</v>
       </c>
       <c r="C1404" t="s">
-        <v>2636</v>
+        <v>2631</v>
       </c>
       <c r="D1404" s="2" t="s">
-        <v>2640</v>
+        <v>2635</v>
       </c>
       <c r="E1404" s="2">
         <v>2</v>
       </c>
       <c r="F1404" s="2" t="s">
-        <v>2638</v>
+        <v>2633</v>
       </c>
       <c r="G1404" s="2" t="s">
-        <v>2641</v>
+        <v>2636</v>
       </c>
     </row>
     <row r="1405" spans="1:7" x14ac:dyDescent="0.45">
@@ -41238,19 +41231,19 @@
         <v>1</v>
       </c>
       <c r="C1405" t="s">
-        <v>2636</v>
+        <v>2631</v>
       </c>
       <c r="D1405" s="2" t="s">
-        <v>2642</v>
+        <v>2637</v>
       </c>
       <c r="E1405" s="2">
         <v>3</v>
       </c>
       <c r="F1405" s="2" t="s">
-        <v>2643</v>
+        <v>2638</v>
       </c>
       <c r="G1405" s="2" t="s">
-        <v>2644</v>
+        <v>2639</v>
       </c>
     </row>
     <row r="1406" spans="1:7" x14ac:dyDescent="0.45">
@@ -41261,19 +41254,19 @@
         <v>1</v>
       </c>
       <c r="C1406" t="s">
-        <v>2636</v>
+        <v>2631</v>
       </c>
       <c r="D1406" s="2" t="s">
-        <v>2645</v>
+        <v>2640</v>
       </c>
       <c r="E1406" s="2">
         <v>4</v>
       </c>
       <c r="F1406" s="2" t="s">
-        <v>2638</v>
+        <v>2633</v>
       </c>
       <c r="G1406" s="2" t="s">
-        <v>2644</v>
+        <v>2639</v>
       </c>
     </row>
     <row r="1407" spans="1:7" x14ac:dyDescent="0.45">
@@ -41284,19 +41277,19 @@
         <v>1</v>
       </c>
       <c r="C1407" t="s">
-        <v>2636</v>
+        <v>2631</v>
       </c>
       <c r="D1407" s="2" t="s">
-        <v>2646</v>
+        <v>2641</v>
       </c>
       <c r="E1407" s="2">
         <v>5</v>
       </c>
       <c r="F1407" s="2" t="s">
-        <v>2647</v>
+        <v>2642</v>
       </c>
       <c r="G1407" s="2" t="s">
-        <v>2639</v>
+        <v>2634</v>
       </c>
     </row>
     <row r="1408" spans="1:7" x14ac:dyDescent="0.45">
@@ -41307,19 +41300,19 @@
         <v>1</v>
       </c>
       <c r="C1408" t="s">
-        <v>2636</v>
+        <v>2631</v>
       </c>
       <c r="D1408" s="2" t="s">
-        <v>2648</v>
+        <v>2643</v>
       </c>
       <c r="E1408" s="2">
         <v>6</v>
       </c>
       <c r="F1408" s="2" t="s">
-        <v>2649</v>
+        <v>2644</v>
       </c>
       <c r="G1408" s="2" t="s">
-        <v>2639</v>
+        <v>2634</v>
       </c>
     </row>
     <row r="1409" spans="1:7" x14ac:dyDescent="0.45">
@@ -41330,19 +41323,19 @@
         <v>1</v>
       </c>
       <c r="C1409" t="s">
-        <v>2636</v>
+        <v>2631</v>
       </c>
       <c r="D1409" s="2" t="s">
-        <v>2650</v>
+        <v>2645</v>
       </c>
       <c r="E1409" s="2">
         <v>7</v>
       </c>
       <c r="F1409" s="2" t="s">
-        <v>2651</v>
+        <v>2646</v>
       </c>
       <c r="G1409" s="2" t="s">
-        <v>2652</v>
+        <v>2647</v>
       </c>
     </row>
     <row r="1410" spans="1:7" x14ac:dyDescent="0.45">
@@ -41353,19 +41346,19 @@
         <v>1</v>
       </c>
       <c r="C1410" t="s">
-        <v>2636</v>
+        <v>2631</v>
       </c>
       <c r="D1410" s="2" t="s">
-        <v>2653</v>
+        <v>2648</v>
       </c>
       <c r="E1410" s="2">
         <v>8</v>
       </c>
       <c r="F1410" s="2" t="s">
-        <v>2654</v>
+        <v>2649</v>
       </c>
       <c r="G1410" s="2" t="s">
-        <v>2655</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="1411" spans="1:7" x14ac:dyDescent="0.45">
@@ -41376,19 +41369,19 @@
         <v>1</v>
       </c>
       <c r="C1411" t="s">
-        <v>2636</v>
+        <v>2631</v>
       </c>
       <c r="D1411" s="2" t="s">
-        <v>2656</v>
+        <v>2651</v>
       </c>
       <c r="E1411" s="2">
         <v>9</v>
       </c>
       <c r="F1411" s="2" t="s">
-        <v>2657</v>
+        <v>2652</v>
       </c>
       <c r="G1411" s="2" t="s">
-        <v>2639</v>
+        <v>2634</v>
       </c>
     </row>
     <row r="1412" spans="1:7" x14ac:dyDescent="0.45">
@@ -41399,19 +41392,19 @@
         <v>1</v>
       </c>
       <c r="C1412" t="s">
-        <v>2636</v>
+        <v>2631</v>
       </c>
       <c r="D1412" s="2" t="s">
-        <v>2658</v>
+        <v>2653</v>
       </c>
       <c r="E1412" s="2">
         <v>10</v>
       </c>
       <c r="F1412" s="2" t="s">
-        <v>2659</v>
+        <v>2654</v>
       </c>
       <c r="G1412" s="2" t="s">
-        <v>2639</v>
+        <v>2634</v>
       </c>
     </row>
     <row r="1413" spans="1:7" x14ac:dyDescent="0.45">
@@ -41422,19 +41415,19 @@
         <v>1</v>
       </c>
       <c r="C1413" t="s">
-        <v>2636</v>
+        <v>2631</v>
       </c>
       <c r="D1413" s="2" t="s">
-        <v>2660</v>
+        <v>2655</v>
       </c>
       <c r="E1413" s="2">
         <v>11</v>
       </c>
       <c r="F1413" s="2" t="s">
-        <v>2661</v>
+        <v>2656</v>
       </c>
       <c r="G1413" s="2" t="s">
-        <v>2661</v>
+        <v>2656</v>
       </c>
     </row>
     <row r="1414" spans="1:7" x14ac:dyDescent="0.45">
@@ -41445,19 +41438,19 @@
         <v>1</v>
       </c>
       <c r="C1414" t="s">
-        <v>2636</v>
+        <v>2631</v>
       </c>
       <c r="D1414" s="2" t="s">
-        <v>2662</v>
+        <v>2657</v>
       </c>
       <c r="E1414" s="2">
         <v>12</v>
       </c>
       <c r="F1414" s="2" t="s">
-        <v>2663</v>
+        <v>2658</v>
       </c>
       <c r="G1414" s="2" t="s">
-        <v>2664</v>
+        <v>2659</v>
       </c>
     </row>
     <row r="1415" spans="1:7" x14ac:dyDescent="0.45">
@@ -41468,10 +41461,10 @@
         <v>1</v>
       </c>
       <c r="C1415" t="s">
-        <v>2636</v>
+        <v>2631</v>
       </c>
       <c r="D1415" s="2" t="s">
-        <v>2665</v>
+        <v>2660</v>
       </c>
       <c r="E1415" s="2">
         <v>13</v>
@@ -41480,7 +41473,7 @@
         <v>1483</v>
       </c>
       <c r="G1415" s="2" t="s">
-        <v>2666</v>
+        <v>2661</v>
       </c>
     </row>
     <row r="1416" spans="1:7" x14ac:dyDescent="0.45">
@@ -41491,19 +41484,19 @@
         <v>1</v>
       </c>
       <c r="C1416" t="s">
-        <v>2636</v>
+        <v>2631</v>
       </c>
       <c r="D1416" s="2" t="s">
-        <v>2667</v>
+        <v>2662</v>
       </c>
       <c r="E1416" s="2">
         <v>14</v>
       </c>
       <c r="F1416" s="2" t="s">
-        <v>2668</v>
+        <v>2663</v>
       </c>
       <c r="G1416" s="2" t="s">
-        <v>2669</v>
+        <v>2664</v>
       </c>
     </row>
     <row r="1417" spans="1:7" x14ac:dyDescent="0.45">
@@ -41514,19 +41507,19 @@
         <v>1</v>
       </c>
       <c r="C1417" t="s">
-        <v>2636</v>
+        <v>2631</v>
       </c>
       <c r="D1417" s="2" t="s">
-        <v>2670</v>
+        <v>2665</v>
       </c>
       <c r="E1417" s="2">
         <v>15</v>
       </c>
       <c r="F1417" s="2" t="s">
-        <v>2671</v>
+        <v>2666</v>
       </c>
       <c r="G1417" s="2" t="s">
-        <v>2672</v>
+        <v>2667</v>
       </c>
     </row>
     <row r="1418" spans="1:7" x14ac:dyDescent="0.45">
@@ -41537,19 +41530,19 @@
         <v>1</v>
       </c>
       <c r="C1418" t="s">
-        <v>2636</v>
+        <v>2631</v>
       </c>
       <c r="D1418" s="2" t="s">
-        <v>2673</v>
+        <v>2668</v>
       </c>
       <c r="E1418" s="2">
         <v>16</v>
       </c>
       <c r="F1418" s="2" t="s">
-        <v>2674</v>
+        <v>2669</v>
       </c>
       <c r="G1418" s="2" t="s">
-        <v>2675</v>
+        <v>2670</v>
       </c>
     </row>
     <row r="1419" spans="1:7" x14ac:dyDescent="0.45">
@@ -41560,19 +41553,19 @@
         <v>1</v>
       </c>
       <c r="C1419" t="s">
-        <v>2636</v>
+        <v>2631</v>
       </c>
       <c r="D1419" s="2" t="s">
-        <v>2676</v>
+        <v>2671</v>
       </c>
       <c r="E1419" s="2">
         <v>17</v>
       </c>
       <c r="F1419" s="2" t="s">
-        <v>2668</v>
+        <v>2663</v>
       </c>
       <c r="G1419" s="2" t="s">
-        <v>2669</v>
+        <v>2664</v>
       </c>
     </row>
     <row r="1420" spans="1:7" x14ac:dyDescent="0.45">
@@ -41583,19 +41576,19 @@
         <v>1</v>
       </c>
       <c r="C1420" t="s">
-        <v>2636</v>
+        <v>2631</v>
       </c>
       <c r="D1420" s="2" t="s">
-        <v>2677</v>
+        <v>2672</v>
       </c>
       <c r="E1420" s="2">
         <v>18</v>
       </c>
       <c r="F1420" s="2" t="s">
-        <v>2661</v>
+        <v>2656</v>
       </c>
       <c r="G1420" s="2" t="s">
-        <v>2669</v>
+        <v>2664</v>
       </c>
     </row>
     <row r="1421" spans="1:7" x14ac:dyDescent="0.45">
@@ -41606,10 +41599,10 @@
         <v>1</v>
       </c>
       <c r="C1421" t="s">
-        <v>2636</v>
+        <v>2631</v>
       </c>
       <c r="D1421" s="2" t="s">
-        <v>2678</v>
+        <v>2673</v>
       </c>
       <c r="E1421" s="2">
         <v>19</v>
@@ -41618,7 +41611,7 @@
         <v>1483</v>
       </c>
       <c r="G1421" s="2" t="s">
-        <v>2679</v>
+        <v>2674</v>
       </c>
     </row>
     <row r="1422" spans="1:7" x14ac:dyDescent="0.45">
@@ -41629,19 +41622,19 @@
         <v>1</v>
       </c>
       <c r="C1422" t="s">
-        <v>2636</v>
+        <v>2631</v>
       </c>
       <c r="D1422" s="2" t="s">
-        <v>2680</v>
+        <v>2675</v>
       </c>
       <c r="E1422" s="2">
         <v>20</v>
       </c>
       <c r="F1422" s="2" t="s">
-        <v>2681</v>
+        <v>2676</v>
       </c>
       <c r="G1422" s="2" t="s">
-        <v>2669</v>
+        <v>2664</v>
       </c>
     </row>
     <row r="1423" spans="1:7" x14ac:dyDescent="0.45">
@@ -41652,19 +41645,19 @@
         <v>1</v>
       </c>
       <c r="C1423" t="s">
-        <v>2636</v>
+        <v>2631</v>
       </c>
       <c r="D1423" s="2" t="s">
-        <v>2682</v>
+        <v>2677</v>
       </c>
       <c r="E1423" s="2">
         <v>21</v>
       </c>
       <c r="F1423" s="2" t="s">
-        <v>2683</v>
+        <v>2678</v>
       </c>
       <c r="G1423" s="2" t="s">
-        <v>2683</v>
+        <v>2678</v>
       </c>
     </row>
     <row r="1424" spans="1:7" x14ac:dyDescent="0.45">
@@ -41675,19 +41668,19 @@
         <v>1</v>
       </c>
       <c r="C1424" t="s">
-        <v>2636</v>
+        <v>2631</v>
       </c>
       <c r="D1424" s="2" t="s">
-        <v>2684</v>
+        <v>2679</v>
       </c>
       <c r="E1424" s="2">
         <v>22</v>
       </c>
       <c r="F1424" s="2" t="s">
-        <v>2638</v>
+        <v>2633</v>
       </c>
       <c r="G1424" s="2" t="s">
-        <v>2644</v>
+        <v>2639</v>
       </c>
     </row>
     <row r="1425" spans="1:7" x14ac:dyDescent="0.45">
@@ -41698,19 +41691,19 @@
         <v>1</v>
       </c>
       <c r="C1425" t="s">
-        <v>2636</v>
+        <v>2631</v>
       </c>
       <c r="D1425" s="2" t="s">
-        <v>2685</v>
+        <v>2680</v>
       </c>
       <c r="E1425" s="2">
         <v>23</v>
       </c>
       <c r="F1425" s="2" t="s">
-        <v>2643</v>
+        <v>2638</v>
       </c>
       <c r="G1425" s="2" t="s">
-        <v>2686</v>
+        <v>2681</v>
       </c>
     </row>
     <row r="1426" spans="1:7" x14ac:dyDescent="0.45">
@@ -41721,19 +41714,19 @@
         <v>1</v>
       </c>
       <c r="C1426" t="s">
-        <v>2636</v>
+        <v>2631</v>
       </c>
       <c r="D1426" s="2" t="s">
-        <v>2687</v>
+        <v>2682</v>
       </c>
       <c r="E1426" s="2">
         <v>24</v>
       </c>
       <c r="F1426" s="2" t="s">
-        <v>2649</v>
+        <v>2644</v>
       </c>
       <c r="G1426" s="2" t="s">
-        <v>2639</v>
+        <v>2634</v>
       </c>
     </row>
     <row r="1427" spans="1:7" x14ac:dyDescent="0.45">
@@ -41744,19 +41737,19 @@
         <v>1</v>
       </c>
       <c r="C1427" t="s">
-        <v>2636</v>
+        <v>2631</v>
       </c>
       <c r="D1427" s="2" t="s">
-        <v>2688</v>
+        <v>2683</v>
       </c>
       <c r="E1427" s="2">
         <v>25</v>
       </c>
       <c r="F1427" s="2" t="s">
-        <v>2647</v>
+        <v>2642</v>
       </c>
       <c r="G1427" s="2" t="s">
-        <v>2639</v>
+        <v>2634</v>
       </c>
     </row>
     <row r="1428" spans="1:7" x14ac:dyDescent="0.45">
@@ -41767,19 +41760,19 @@
         <v>1</v>
       </c>
       <c r="C1428" t="s">
-        <v>2636</v>
+        <v>2631</v>
       </c>
       <c r="D1428" s="2" t="s">
-        <v>2689</v>
+        <v>2684</v>
       </c>
       <c r="E1428" s="2">
         <v>26</v>
       </c>
       <c r="F1428" s="2" t="s">
-        <v>2681</v>
+        <v>2676</v>
       </c>
       <c r="G1428" s="2" t="s">
-        <v>2669</v>
+        <v>2664</v>
       </c>
     </row>
     <row r="1429" spans="1:7" x14ac:dyDescent="0.45">
@@ -41790,19 +41783,19 @@
         <v>1</v>
       </c>
       <c r="C1429" t="s">
-        <v>2636</v>
+        <v>2631</v>
       </c>
       <c r="D1429" s="2" t="s">
-        <v>2690</v>
+        <v>2685</v>
       </c>
       <c r="E1429" s="2">
         <v>27</v>
       </c>
       <c r="F1429" s="2" t="s">
-        <v>2671</v>
+        <v>2666</v>
       </c>
       <c r="G1429" s="2" t="s">
-        <v>2691</v>
+        <v>2686</v>
       </c>
     </row>
     <row r="1430" spans="1:7" x14ac:dyDescent="0.45">
@@ -41813,19 +41806,19 @@
         <v>1</v>
       </c>
       <c r="C1430" t="s">
-        <v>2636</v>
+        <v>2631</v>
       </c>
       <c r="D1430" s="2" t="s">
-        <v>2692</v>
+        <v>2687</v>
       </c>
       <c r="E1430" s="2">
         <v>28</v>
       </c>
       <c r="F1430" s="2" t="s">
-        <v>2674</v>
+        <v>2669</v>
       </c>
       <c r="G1430" s="2" t="s">
-        <v>2675</v>
+        <v>2670</v>
       </c>
     </row>
     <row r="1431" spans="1:7" x14ac:dyDescent="0.45">
@@ -41836,19 +41829,19 @@
         <v>1</v>
       </c>
       <c r="C1431" t="s">
-        <v>2636</v>
+        <v>2631</v>
       </c>
       <c r="D1431" s="2" t="s">
-        <v>2693</v>
+        <v>2688</v>
       </c>
       <c r="E1431" s="2">
         <v>29</v>
       </c>
       <c r="F1431" s="2" t="s">
-        <v>2647</v>
+        <v>2642</v>
       </c>
       <c r="G1431" s="2" t="s">
-        <v>2639</v>
+        <v>2634</v>
       </c>
     </row>
     <row r="1432" spans="1:7" x14ac:dyDescent="0.45">
@@ -41859,19 +41852,19 @@
         <v>1</v>
       </c>
       <c r="C1432" t="s">
-        <v>2636</v>
+        <v>2631</v>
       </c>
       <c r="D1432" s="2" t="s">
-        <v>2694</v>
+        <v>2689</v>
       </c>
       <c r="E1432" s="2">
         <v>30</v>
       </c>
       <c r="F1432" s="2" t="s">
-        <v>2668</v>
+        <v>2663</v>
       </c>
       <c r="G1432" s="2" t="s">
-        <v>2669</v>
+        <v>2664</v>
       </c>
     </row>
     <row r="1433" spans="1:7" x14ac:dyDescent="0.45">
@@ -41885,13 +41878,13 @@
         <v>1530</v>
       </c>
       <c r="D1433" t="s">
-        <v>2695</v>
+        <v>2690</v>
       </c>
       <c r="E1433">
         <v>41</v>
       </c>
       <c r="F1433" t="s">
-        <v>2696</v>
+        <v>2691</v>
       </c>
       <c r="G1433" t="s">
         <v>1533</v>
@@ -41908,13 +41901,13 @@
         <v>1530</v>
       </c>
       <c r="D1434" t="s">
-        <v>2697</v>
+        <v>2692</v>
       </c>
       <c r="E1434">
         <v>42</v>
       </c>
       <c r="F1434" t="s">
-        <v>2698</v>
+        <v>2693</v>
       </c>
       <c r="G1434" t="s">
         <v>1533</v>
@@ -41931,13 +41924,13 @@
         <v>1530</v>
       </c>
       <c r="D1435" t="s">
-        <v>2699</v>
+        <v>2694</v>
       </c>
       <c r="E1435">
         <v>43</v>
       </c>
       <c r="F1435" t="s">
-        <v>2700</v>
+        <v>2695</v>
       </c>
       <c r="G1435" t="s">
         <v>1533</v>
@@ -41954,13 +41947,13 @@
         <v>1530</v>
       </c>
       <c r="D1436" t="s">
-        <v>2701</v>
+        <v>2696</v>
       </c>
       <c r="E1436">
         <v>44</v>
       </c>
       <c r="F1436" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="G1436" t="s">
         <v>1533</v>
@@ -41977,13 +41970,13 @@
         <v>1530</v>
       </c>
       <c r="D1437" t="s">
-        <v>2703</v>
+        <v>2698</v>
       </c>
       <c r="E1437">
         <v>45</v>
       </c>
       <c r="F1437" t="s">
-        <v>2702</v>
+        <v>2697</v>
       </c>
       <c r="G1437" t="s">
         <v>1533</v>
@@ -42000,13 +41993,13 @@
         <v>1530</v>
       </c>
       <c r="D1438" t="s">
-        <v>2704</v>
+        <v>2699</v>
       </c>
       <c r="E1438">
         <v>46</v>
       </c>
       <c r="F1438" t="s">
-        <v>2705</v>
+        <v>2700</v>
       </c>
       <c r="G1438" t="s">
         <v>1533</v>
@@ -42023,13 +42016,13 @@
         <v>1530</v>
       </c>
       <c r="D1439" t="s">
-        <v>2706</v>
+        <v>2701</v>
       </c>
       <c r="E1439">
         <v>47</v>
       </c>
       <c r="F1439" t="s">
-        <v>2707</v>
+        <v>2702</v>
       </c>
       <c r="G1439" t="s">
         <v>1533</v>
@@ -42046,13 +42039,13 @@
         <v>1530</v>
       </c>
       <c r="D1440" t="s">
-        <v>2708</v>
+        <v>2703</v>
       </c>
       <c r="E1440">
         <v>48</v>
       </c>
       <c r="F1440" t="s">
-        <v>2709</v>
+        <v>2704</v>
       </c>
       <c r="G1440" t="s">
         <v>1533</v>
@@ -42069,13 +42062,13 @@
         <v>1530</v>
       </c>
       <c r="D1441" t="s">
-        <v>2710</v>
+        <v>2705</v>
       </c>
       <c r="E1441">
         <v>49</v>
       </c>
       <c r="F1441" t="s">
-        <v>2711</v>
+        <v>2706</v>
       </c>
       <c r="G1441" t="s">
         <v>1533</v>
@@ -42092,13 +42085,13 @@
         <v>1530</v>
       </c>
       <c r="D1442" t="s">
-        <v>2712</v>
+        <v>2707</v>
       </c>
       <c r="E1442">
         <v>50</v>
       </c>
       <c r="F1442" t="s">
-        <v>2713</v>
+        <v>2708</v>
       </c>
       <c r="G1442" t="s">
         <v>1533</v>
@@ -42115,13 +42108,13 @@
         <v>1530</v>
       </c>
       <c r="D1443" t="s">
-        <v>2714</v>
+        <v>2709</v>
       </c>
       <c r="E1443">
         <v>51</v>
       </c>
       <c r="F1443" t="s">
-        <v>2713</v>
+        <v>2708</v>
       </c>
       <c r="G1443" t="s">
         <v>1533</v>
@@ -42138,13 +42131,13 @@
         <v>1530</v>
       </c>
       <c r="D1444" t="s">
-        <v>2715</v>
+        <v>2710</v>
       </c>
       <c r="E1444">
         <v>52</v>
       </c>
       <c r="F1444" t="s">
-        <v>2716</v>
+        <v>2711</v>
       </c>
       <c r="G1444" t="s">
         <v>1533</v>
@@ -42161,13 +42154,13 @@
         <v>1530</v>
       </c>
       <c r="D1445" t="s">
-        <v>2717</v>
+        <v>2712</v>
       </c>
       <c r="E1445">
         <v>53</v>
       </c>
       <c r="F1445" t="s">
-        <v>2718</v>
+        <v>2713</v>
       </c>
       <c r="G1445" t="s">
         <v>1533</v>
@@ -42184,13 +42177,13 @@
         <v>1530</v>
       </c>
       <c r="D1446" t="s">
-        <v>2719</v>
+        <v>2714</v>
       </c>
       <c r="E1446">
         <v>54</v>
       </c>
       <c r="F1446" t="s">
-        <v>2718</v>
+        <v>2713</v>
       </c>
       <c r="G1446" t="s">
         <v>1533</v>
@@ -42207,7 +42200,7 @@
         <v>1530</v>
       </c>
       <c r="D1447" t="s">
-        <v>2720</v>
+        <v>2715</v>
       </c>
       <c r="E1447">
         <v>55</v>
@@ -42230,13 +42223,13 @@
         <v>1530</v>
       </c>
       <c r="D1448" t="s">
-        <v>2721</v>
+        <v>2716</v>
       </c>
       <c r="E1448">
         <v>56</v>
       </c>
       <c r="F1448" t="s">
-        <v>2722</v>
+        <v>2717</v>
       </c>
       <c r="G1448" t="s">
         <v>1533</v>
@@ -42253,7 +42246,7 @@
         <v>1530</v>
       </c>
       <c r="D1449" t="s">
-        <v>2723</v>
+        <v>2718</v>
       </c>
       <c r="E1449">
         <v>57</v>
@@ -42276,13 +42269,13 @@
         <v>1530</v>
       </c>
       <c r="D1450" t="s">
-        <v>2724</v>
+        <v>2719</v>
       </c>
       <c r="E1450">
         <v>58</v>
       </c>
       <c r="F1450" t="s">
-        <v>2725</v>
+        <v>2720</v>
       </c>
       <c r="G1450" t="s">
         <v>1533</v>
@@ -42299,13 +42292,13 @@
         <v>1530</v>
       </c>
       <c r="D1451" t="s">
-        <v>2726</v>
+        <v>2721</v>
       </c>
       <c r="E1451">
         <v>59</v>
       </c>
       <c r="F1451" t="s">
-        <v>2727</v>
+        <v>2722</v>
       </c>
       <c r="G1451" t="s">
         <v>1533</v>
@@ -42322,13 +42315,13 @@
         <v>1530</v>
       </c>
       <c r="D1452" t="s">
-        <v>2728</v>
+        <v>2723</v>
       </c>
       <c r="E1452">
         <v>60</v>
       </c>
       <c r="F1452" t="s">
-        <v>2727</v>
+        <v>2722</v>
       </c>
       <c r="G1452" t="s">
         <v>1533</v>

--- a/aisth/LTRYI-grammar-lesson-questions.xlsx
+++ b/aisth/LTRYI-grammar-lesson-questions.xlsx
@@ -32788,8 +32788,10 @@
       <c r="E1048" s="2">
         <v>6</v>
       </c>
-      <c r="F1048" s="2" t="s">
-        <v>1873</v>
+      <c r="F1048" s="2" t="inlineStr">
+        <is>
+          <t>I - made - **a** cake -</t>
+        </is>
       </c>
       <c r="G1048" s="2" t="s">
         <v>1865</v>
@@ -32811,8 +32813,10 @@
       <c r="E1049" s="2">
         <v>7</v>
       </c>
-      <c r="F1049" s="2" t="s">
-        <v>1875</v>
+      <c r="F1049" s="2" t="inlineStr">
+        <is>
+          <t>She - found - **the** keys - **in the** drawer</t>
+        </is>
       </c>
       <c r="G1049" s="2" t="s">
         <v>1865</v>
@@ -32857,8 +32861,10 @@
       <c r="E1051" s="2">
         <v>9</v>
       </c>
-      <c r="F1051" s="2" t="s">
-        <v>1879</v>
+      <c r="F1051" s="2" t="inlineStr">
+        <is>
+          <t>He - opened - **the** window -</t>
+        </is>
       </c>
       <c r="G1051" s="2" t="s">
         <v>1865</v>
@@ -32880,8 +32886,10 @@
       <c r="E1052" s="2">
         <v>10</v>
       </c>
-      <c r="F1052" s="2" t="s">
-        <v>1881</v>
+      <c r="F1052" s="2" t="inlineStr">
+        <is>
+          <t>I - bought - **a** new phone -</t>
+        </is>
       </c>
       <c r="G1052" s="2" t="s">
         <v>1865</v>
@@ -32903,8 +32911,10 @@
       <c r="E1053" s="2">
         <v>11</v>
       </c>
-      <c r="F1053" s="2" t="s">
-        <v>1883</v>
+      <c r="F1053" s="2" t="inlineStr">
+        <is>
+          <t>She - gave - me - **a** book</t>
+        </is>
       </c>
       <c r="G1053" s="2" t="s">
         <v>1865</v>
@@ -32926,8 +32936,10 @@
       <c r="E1054" s="2">
         <v>12</v>
       </c>
-      <c r="F1054" s="2" t="s">
-        <v>1885</v>
+      <c r="F1054" s="2" t="inlineStr">
+        <is>
+          <t>He - sent - **a** friend - **a** postcard</t>
+        </is>
       </c>
       <c r="G1054" s="2" t="s">
         <v>1865</v>
@@ -32943,14 +32955,18 @@
       <c r="C1055" t="s">
         <v>1862</v>
       </c>
-      <c r="D1055" s="2" t="s">
-        <v>1886</v>
+      <c r="D1055" s="2" t="inlineStr">
+        <is>
+          <t>그들은 (S) / 보여주었다 (V) / 우리에게 (T) / 사진을 (D)</t>
+        </is>
       </c>
       <c r="E1055" s="2">
         <v>13</v>
       </c>
-      <c r="F1055" s="2" t="s">
-        <v>1887</v>
+      <c r="F1055" s="2" t="inlineStr">
+        <is>
+          <t>They - showed - us - pictures</t>
+        </is>
       </c>
       <c r="G1055" s="2" t="s">
         <v>1865</v>
@@ -32972,8 +32988,10 @@
       <c r="E1056" s="2">
         <v>14</v>
       </c>
-      <c r="F1056" s="2" t="s">
-        <v>1889</v>
+      <c r="F1056" s="2" t="inlineStr">
+        <is>
+          <t>I - wrote - her - **a** letter</t>
+        </is>
       </c>
       <c r="G1056" s="2" t="s">
         <v>1865</v>
@@ -32995,8 +33013,10 @@
       <c r="E1057" s="2">
         <v>15</v>
       </c>
-      <c r="F1057" s="2" t="s">
-        <v>1891</v>
+      <c r="F1057" s="2" t="inlineStr">
+        <is>
+          <t>We - built - them - **a** house</t>
+        </is>
       </c>
       <c r="G1057" s="2" t="s">
         <v>1865</v>
@@ -33018,8 +33038,10 @@
       <c r="E1058" s="2">
         <v>16</v>
       </c>
-      <c r="F1058" s="2" t="s">
-        <v>1893</v>
+      <c r="F1058" s="2" t="inlineStr">
+        <is>
+          <t>She - told - me - **a** story</t>
+        </is>
       </c>
       <c r="G1058" s="2" t="s">
         <v>1865</v>
@@ -33041,8 +33063,10 @@
       <c r="E1059" s="2">
         <v>17</v>
       </c>
-      <c r="F1059" s="2" t="s">
-        <v>1895</v>
+      <c r="F1059" s="2" t="inlineStr">
+        <is>
+          <t>He - handed - **the** teacher - **his** homework</t>
+        </is>
       </c>
       <c r="G1059" s="2" t="s">
         <v>1865</v>
@@ -33064,8 +33088,10 @@
       <c r="E1060" s="2">
         <v>18</v>
       </c>
-      <c r="F1060" s="2" t="s">
-        <v>1897</v>
+      <c r="F1060" s="2" t="inlineStr">
+        <is>
+          <t>I - brought - **my** brother - snacks</t>
+        </is>
       </c>
       <c r="G1060" s="2" t="s">
         <v>1865</v>
@@ -33156,8 +33182,10 @@
       <c r="E1064" s="2">
         <v>22</v>
       </c>
-      <c r="F1064" s="2" t="s">
-        <v>1905</v>
+      <c r="F1064" s="2" t="inlineStr">
+        <is>
+          <t>**The** teacher - called - me - smart</t>
+        </is>
       </c>
       <c r="G1064" s="2" t="s">
         <v>1865</v>
@@ -33202,8 +33230,10 @@
       <c r="E1066" s="2">
         <v>24</v>
       </c>
-      <c r="F1066" s="2" t="s">
-        <v>1909</v>
+      <c r="F1066" s="2" t="inlineStr">
+        <is>
+          <t>I - painted - **the** wall - blue</t>
+        </is>
       </c>
       <c r="G1066" s="2" t="s">
         <v>1865</v>
@@ -33225,8 +33255,10 @@
       <c r="E1067" s="2">
         <v>25</v>
       </c>
-      <c r="F1067" s="2" t="s">
-        <v>1911</v>
+      <c r="F1067" s="2" t="inlineStr">
+        <is>
+          <t>She - found - **the** movie - boring</t>
+        </is>
       </c>
       <c r="G1067" s="2" t="s">
         <v>1865</v>
@@ -33248,8 +33280,10 @@
       <c r="E1068" s="2">
         <v>26</v>
       </c>
-      <c r="F1068" s="2" t="s">
-        <v>1913</v>
+      <c r="F1068" s="2" t="inlineStr">
+        <is>
+          <t>**The** news - made - him - sad</t>
+        </is>
       </c>
       <c r="G1068" s="2" t="s">
         <v>1865</v>
@@ -33271,8 +33305,10 @@
       <c r="E1069" s="2">
         <v>27</v>
       </c>
-      <c r="F1069" s="2" t="s">
-        <v>1915</v>
+      <c r="F1069" s="2" t="inlineStr">
+        <is>
+          <t>We - named - **the** puppy - Max</t>
+        </is>
       </c>
       <c r="G1069" s="2" t="s">
         <v>1865</v>
@@ -33294,8 +33330,10 @@
       <c r="E1070" s="2">
         <v>28</v>
       </c>
-      <c r="F1070" s="2" t="s">
-        <v>1917</v>
+      <c r="F1070" s="2" t="inlineStr">
+        <is>
+          <t>**The** game - kept - us - excited</t>
+        </is>
       </c>
       <c r="G1070" s="2" t="s">
         <v>1865</v>
@@ -33478,8 +33516,10 @@
       <c r="E1078" s="2">
         <v>36</v>
       </c>
-      <c r="F1078" s="2" t="s">
-        <v>1933</v>
+      <c r="F1078" s="2" t="inlineStr">
+        <is>
+          <t>She - spoke **to** - **the** audience -</t>
+        </is>
       </c>
       <c r="G1078" s="2" t="s">
         <v>1865</v>
@@ -33547,8 +33587,10 @@
       <c r="E1081" s="2">
         <v>39</v>
       </c>
-      <c r="F1081" s="2" t="s">
-        <v>1939</v>
+      <c r="F1081" s="2" t="inlineStr">
+        <is>
+          <t>I - waited **for** - **the** bus -</t>
+        </is>
       </c>
       <c r="G1081" s="2" t="s">
         <v>1865</v>
@@ -33570,8 +33612,10 @@
       <c r="E1082" s="2">
         <v>40</v>
       </c>
-      <c r="F1082" s="2" t="s">
-        <v>1941</v>
+      <c r="F1082" s="2" t="inlineStr">
+        <is>
+          <t>We - stood **by** -  - **the** door</t>
+        </is>
       </c>
       <c r="G1082" s="2" t="s">
         <v>1865</v>

--- a/aisth/LTRYI-grammar-lesson-questions.xlsx
+++ b/aisth/LTRYI-grammar-lesson-questions.xlsx
@@ -8695,7 +8695,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1452"/>
+  <dimension ref="A1:J1452"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="3" max="3" width="31.08203125" customWidth="1"/>
@@ -8703,9 +8703,10 @@
     <col min="5" max="5" width="8.1640625" customWidth="1"/>
     <col min="6" max="6" width="34.75" customWidth="1"/>
     <col min="7" max="7" width="35.33203125" customWidth="1"/>
+    <col min="10" max="10" width="62" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8733,8 +8734,13 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>RevisionNote</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>0</v>
       </c>
@@ -8757,7 +8763,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>0</v>
       </c>
@@ -8780,7 +8786,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>0</v>
       </c>
@@ -8803,7 +8809,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>0</v>
       </c>
@@ -8826,7 +8832,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>0</v>
       </c>
@@ -8849,7 +8855,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>0</v>
       </c>
@@ -8872,7 +8878,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>0</v>
       </c>
@@ -8895,7 +8901,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>0</v>
       </c>
@@ -8918,7 +8924,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>0</v>
       </c>
@@ -8941,7 +8947,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>0</v>
       </c>
@@ -8964,7 +8970,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>0</v>
       </c>
@@ -8987,7 +8993,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>0</v>
       </c>
@@ -9010,7 +9016,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>0</v>
       </c>
@@ -9033,7 +9039,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>0</v>
       </c>
@@ -9056,7 +9062,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>0</v>
       </c>
@@ -34333,6 +34339,11 @@
       <c r="G1113" s="2" t="s">
         <v>2009</v>
       </c>
+      <c r="J1113" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1114" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1114">
@@ -34356,6 +34367,11 @@
       <c r="G1114" s="2" t="s">
         <v>2009</v>
       </c>
+      <c r="J1114" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1115" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1115">
@@ -34379,6 +34395,11 @@
       <c r="G1115" s="2" t="s">
         <v>2009</v>
       </c>
+      <c r="J1115" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1116" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1116">
@@ -34402,6 +34423,11 @@
       <c r="G1116" s="2" t="s">
         <v>2009</v>
       </c>
+      <c r="J1116" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1117" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1117">
@@ -34425,6 +34451,11 @@
       <c r="G1117" s="2" t="s">
         <v>2009</v>
       </c>
+      <c r="J1117" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1118" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1118">
@@ -34448,6 +34479,11 @@
       <c r="G1118" s="2" t="s">
         <v>2009</v>
       </c>
+      <c r="J1118" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1119" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1119">
@@ -34471,6 +34507,11 @@
       <c r="G1119" s="2" t="s">
         <v>2009</v>
       </c>
+      <c r="J1119" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1120" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1120">
@@ -34494,6 +34535,11 @@
       <c r="G1120" s="2" t="s">
         <v>2009</v>
       </c>
+      <c r="J1120" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1121" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1121">
@@ -34517,6 +34563,11 @@
       <c r="G1121" s="2" t="s">
         <v>2009</v>
       </c>
+      <c r="J1121" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1122" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1122">
@@ -34540,6 +34591,11 @@
       <c r="G1122" s="2" t="s">
         <v>2009</v>
       </c>
+      <c r="J1122" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1123" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1123">
@@ -34563,6 +34619,11 @@
       <c r="G1123" s="2" t="s">
         <v>2012</v>
       </c>
+      <c r="J1123" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1124" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1124">
@@ -34586,6 +34647,11 @@
       <c r="G1124" s="2" t="s">
         <v>2009</v>
       </c>
+      <c r="J1124" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1125" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1125">
@@ -34609,6 +34675,11 @@
       <c r="G1125" s="2" t="s">
         <v>2009</v>
       </c>
+      <c r="J1125" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1126" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1126">
@@ -34632,6 +34703,11 @@
       <c r="G1126" s="2" t="s">
         <v>2009</v>
       </c>
+      <c r="J1126" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1127" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1127">
@@ -34655,6 +34731,11 @@
       <c r="G1127" s="2" t="s">
         <v>2009</v>
       </c>
+      <c r="J1127" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1128" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1128">
@@ -34678,6 +34759,11 @@
       <c r="G1128" s="2" t="s">
         <v>2009</v>
       </c>
+      <c r="J1128" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1129" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1129">
@@ -34701,6 +34787,11 @@
       <c r="G1129" s="2" t="s">
         <v>2009</v>
       </c>
+      <c r="J1129" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1130" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1130">
@@ -34724,6 +34815,11 @@
       <c r="G1130" s="2" t="s">
         <v>2009</v>
       </c>
+      <c r="J1130" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1131" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1131">
@@ -34747,6 +34843,11 @@
       <c r="G1131" s="2" t="s">
         <v>2009</v>
       </c>
+      <c r="J1131" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1132" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1132">
@@ -34770,6 +34871,11 @@
       <c r="G1132" s="2" t="s">
         <v>2009</v>
       </c>
+      <c r="J1132" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1133" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1133">
@@ -34793,6 +34899,11 @@
       <c r="G1133" s="2" t="s">
         <v>2033</v>
       </c>
+      <c r="J1133" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1134" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1134">
@@ -34816,6 +34927,11 @@
       <c r="G1134" s="2" t="s">
         <v>2036</v>
       </c>
+      <c r="J1134" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1135" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1135">
@@ -34839,6 +34955,11 @@
       <c r="G1135" s="2" t="s">
         <v>2036</v>
       </c>
+      <c r="J1135" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1136" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1136">
@@ -34862,6 +34983,11 @@
       <c r="G1136" s="2" t="s">
         <v>2036</v>
       </c>
+      <c r="J1136" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1137" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1137">
@@ -34885,6 +35011,11 @@
       <c r="G1137" s="2" t="s">
         <v>2036</v>
       </c>
+      <c r="J1137" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1138" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1138">
@@ -34908,6 +35039,11 @@
       <c r="G1138" s="2" t="s">
         <v>2036</v>
       </c>
+      <c r="J1138" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1139" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1139">
@@ -34931,6 +35067,11 @@
       <c r="G1139" s="2" t="s">
         <v>2036</v>
       </c>
+      <c r="J1139" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1140" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1140">
@@ -34954,6 +35095,11 @@
       <c r="G1140" s="2" t="s">
         <v>2036</v>
       </c>
+      <c r="J1140" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1141" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1141">
@@ -34977,6 +35123,11 @@
       <c r="G1141" s="2" t="s">
         <v>2036</v>
       </c>
+      <c r="J1141" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1142" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1142">
@@ -35000,6 +35151,11 @@
       <c r="G1142" s="2" t="s">
         <v>2036</v>
       </c>
+      <c r="J1142" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1143" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1143">
@@ -35023,6 +35179,11 @@
       <c r="G1143" s="2" t="s">
         <v>2036</v>
       </c>
+      <c r="J1143" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1144" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1144">
@@ -35046,6 +35207,11 @@
       <c r="G1144" s="2" t="s">
         <v>2036</v>
       </c>
+      <c r="J1144" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1145" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1145">
@@ -35069,6 +35235,11 @@
       <c r="G1145" s="2" t="s">
         <v>2036</v>
       </c>
+      <c r="J1145" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1146" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1146">
@@ -35092,6 +35263,11 @@
       <c r="G1146" s="2" t="s">
         <v>2036</v>
       </c>
+      <c r="J1146" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1147" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1147">
@@ -35115,6 +35291,11 @@
       <c r="G1147" s="2" t="s">
         <v>2036</v>
       </c>
+      <c r="J1147" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1148" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1148">
@@ -35138,6 +35319,11 @@
       <c r="G1148" s="2" t="s">
         <v>2036</v>
       </c>
+      <c r="J1148" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1149" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1149">
@@ -35161,6 +35347,11 @@
       <c r="G1149" s="2" t="s">
         <v>2036</v>
       </c>
+      <c r="J1149" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1150" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1150">
@@ -35184,6 +35375,11 @@
       <c r="G1150" s="2" t="s">
         <v>2036</v>
       </c>
+      <c r="J1150" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1151" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1151">
@@ -35207,6 +35403,11 @@
       <c r="G1151" s="2" t="s">
         <v>2036</v>
       </c>
+      <c r="J1151" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1152" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1152">
@@ -35230,6 +35431,11 @@
       <c r="G1152" s="2" t="s">
         <v>2036</v>
       </c>
+      <c r="J1152" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1153" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1153">
@@ -35253,6 +35459,11 @@
       <c r="G1153" s="2" t="s">
         <v>2074</v>
       </c>
+      <c r="J1153" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1154" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1154">
@@ -35276,6 +35487,11 @@
       <c r="G1154" s="2" t="s">
         <v>2036</v>
       </c>
+      <c r="J1154" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1155" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1155">
@@ -35299,6 +35515,11 @@
       <c r="G1155" s="2" t="s">
         <v>2036</v>
       </c>
+      <c r="J1155" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1156" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1156">
@@ -35322,6 +35543,11 @@
       <c r="G1156" s="2" t="s">
         <v>2036</v>
       </c>
+      <c r="J1156" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1157" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1157">
@@ -35345,6 +35571,11 @@
       <c r="G1157" s="2" t="s">
         <v>2036</v>
       </c>
+      <c r="J1157" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1158" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1158">
@@ -35368,6 +35599,11 @@
       <c r="G1158" s="2" t="s">
         <v>2036</v>
       </c>
+      <c r="J1158" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1159" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1159">
@@ -35391,6 +35627,11 @@
       <c r="G1159" s="2" t="s">
         <v>2036</v>
       </c>
+      <c r="J1159" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1160" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1160">
@@ -35414,6 +35655,11 @@
       <c r="G1160" s="2" t="s">
         <v>2036</v>
       </c>
+      <c r="J1160" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1161" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1161">
@@ -35437,6 +35683,11 @@
       <c r="G1161" s="2" t="s">
         <v>2036</v>
       </c>
+      <c r="J1161" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1162" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1162">
@@ -35460,6 +35711,11 @@
       <c r="G1162" s="2" t="s">
         <v>2036</v>
       </c>
+      <c r="J1162" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1163" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1163">
@@ -35483,6 +35739,11 @@
       <c r="G1163" s="2" t="s">
         <v>2094</v>
       </c>
+      <c r="J1163" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1164" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1164">
@@ -35506,6 +35767,11 @@
       <c r="G1164" s="2" t="s">
         <v>2036</v>
       </c>
+      <c r="J1164" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1165" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1165">
@@ -35529,6 +35795,11 @@
       <c r="G1165" s="2" t="s">
         <v>2036</v>
       </c>
+      <c r="J1165" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1166" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1166">
@@ -35552,6 +35823,11 @@
       <c r="G1166" s="2" t="s">
         <v>2036</v>
       </c>
+      <c r="J1166" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1167" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1167">
@@ -35575,6 +35851,11 @@
       <c r="G1167" s="2" t="s">
         <v>2036</v>
       </c>
+      <c r="J1167" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1168" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1168">
@@ -35598,6 +35879,11 @@
       <c r="G1168" s="2" t="s">
         <v>2036</v>
       </c>
+      <c r="J1168" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1169" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1169">
@@ -35621,6 +35907,11 @@
       <c r="G1169" s="2" t="s">
         <v>2036</v>
       </c>
+      <c r="J1169" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1170" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1170">
@@ -35644,6 +35935,11 @@
       <c r="G1170" s="2" t="s">
         <v>2036</v>
       </c>
+      <c r="J1170" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1171" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1171">
@@ -35667,6 +35963,11 @@
       <c r="G1171" s="2" t="s">
         <v>2036</v>
       </c>
+      <c r="J1171" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1172" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1172">
@@ -35690,6 +35991,11 @@
       <c r="G1172" s="2" t="s">
         <v>2036</v>
       </c>
+      <c r="J1172" t="inlineStr">
+        <is>
+          <t>관계사는 Aisth가 아니라 Herma에서 다룰 내용. Aisth 7-4/7-5는 삭제하고 의문사 소개로 재편 필요.</t>
+        </is>
+      </c>
     </row>
     <row r="1173" spans="1:7" ht="34" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1173">
@@ -38543,7 +38849,7 @@
         <v>2306</v>
       </c>
     </row>
-    <row r="1297" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1297" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1297">
         <v>8</v>
       </c>
@@ -38566,7 +38872,7 @@
         <v>2306</v>
       </c>
     </row>
-    <row r="1298" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1298" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1298">
         <v>8</v>
       </c>
@@ -38589,7 +38895,7 @@
         <v>2306</v>
       </c>
     </row>
-    <row r="1299" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1299" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1299">
         <v>8</v>
       </c>
@@ -38612,7 +38918,7 @@
         <v>2306</v>
       </c>
     </row>
-    <row r="1300" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1300" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1300">
         <v>8</v>
       </c>
@@ -38635,7 +38941,7 @@
         <v>2306</v>
       </c>
     </row>
-    <row r="1301" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1301" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1301">
         <v>8</v>
       </c>
@@ -38658,7 +38964,7 @@
         <v>2306</v>
       </c>
     </row>
-    <row r="1302" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1302" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1302">
         <v>8</v>
       </c>
@@ -38681,7 +38987,7 @@
         <v>2306</v>
       </c>
     </row>
-    <row r="1303" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1303" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1303">
         <v>8</v>
       </c>
@@ -38710,7 +39016,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="1304" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1304" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1304">
         <v>8</v>
       </c>
@@ -38739,7 +39045,7 @@
         <v>2351</v>
       </c>
     </row>
-    <row r="1305" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1305" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1305">
         <v>8</v>
       </c>
@@ -38768,7 +39074,7 @@
         <v>2355</v>
       </c>
     </row>
-    <row r="1306" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1306" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1306">
         <v>8</v>
       </c>
@@ -38797,7 +39103,7 @@
         <v>2359</v>
       </c>
     </row>
-    <row r="1307" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1307" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1307">
         <v>8</v>
       </c>
@@ -38826,7 +39132,7 @@
         <v>2363</v>
       </c>
     </row>
-    <row r="1308" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1308" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1308">
         <v>8</v>
       </c>
@@ -38855,7 +39161,7 @@
         <v>2367</v>
       </c>
     </row>
-    <row r="1309" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1309" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1309">
         <v>8</v>
       </c>
@@ -38884,7 +39190,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="1310" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1310" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1310">
         <v>8</v>
       </c>
@@ -38913,7 +39219,7 @@
         <v>2375</v>
       </c>
     </row>
-    <row r="1311" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1311" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1311">
         <v>8</v>
       </c>
@@ -38942,7 +39248,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="1312" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1312" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1312">
         <v>8</v>
       </c>
@@ -38971,7 +39277,7 @@
         <v>2383</v>
       </c>
     </row>
-    <row r="1313" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1313" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1313">
         <v>8</v>
       </c>
@@ -39000,7 +39306,7 @@
         <v>2388</v>
       </c>
     </row>
-    <row r="1314" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1314" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1314">
         <v>8</v>
       </c>
@@ -39029,7 +39335,7 @@
         <v>2392</v>
       </c>
     </row>
-    <row r="1315" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1315" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1315">
         <v>8</v>
       </c>
@@ -39058,7 +39364,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="1316" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1316" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1316">
         <v>8</v>
       </c>
@@ -39087,7 +39393,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="1317" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1317" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1317">
         <v>8</v>
       </c>
@@ -39116,7 +39422,7 @@
         <v>2404</v>
       </c>
     </row>
-    <row r="1318" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1318" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1318">
         <v>8</v>
       </c>
@@ -39145,7 +39451,7 @@
         <v>2408</v>
       </c>
     </row>
-    <row r="1319" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1319" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1319">
         <v>8</v>
       </c>
@@ -39174,7 +39480,7 @@
         <v>2412</v>
       </c>
     </row>
-    <row r="1320" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1320" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1320">
         <v>8</v>
       </c>
@@ -39203,7 +39509,7 @@
         <v>2416</v>
       </c>
     </row>
-    <row r="1321" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1321" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1321">
         <v>8</v>
       </c>
@@ -39232,7 +39538,7 @@
         <v>2420</v>
       </c>
     </row>
-    <row r="1322" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1322" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1322">
         <v>8</v>
       </c>
@@ -39261,7 +39567,7 @@
         <v>2424</v>
       </c>
     </row>
-    <row r="1323" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1323" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1323">
         <v>8</v>
       </c>
@@ -39290,7 +39596,7 @@
         <v>2429</v>
       </c>
     </row>
-    <row r="1324" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1324" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1324">
         <v>8</v>
       </c>
@@ -39319,7 +39625,7 @@
         <v>2433</v>
       </c>
     </row>
-    <row r="1325" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1325" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1325">
         <v>8</v>
       </c>
@@ -39348,7 +39654,7 @@
         <v>2437</v>
       </c>
     </row>
-    <row r="1326" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1326" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1326">
         <v>8</v>
       </c>
@@ -39377,7 +39683,7 @@
         <v>2441</v>
       </c>
     </row>
-    <row r="1327" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1327" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1327">
         <v>8</v>
       </c>
@@ -39406,7 +39712,7 @@
         <v>2445</v>
       </c>
     </row>
-    <row r="1328" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1328" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1328">
         <v>8</v>
       </c>
@@ -39435,7 +39741,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="1329" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1329" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1329">
         <v>8</v>
       </c>
@@ -39464,7 +39770,7 @@
         <v>2453</v>
       </c>
     </row>
-    <row r="1330" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1330" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1330">
         <v>8</v>
       </c>
@@ -39493,7 +39799,7 @@
         <v>2457</v>
       </c>
     </row>
-    <row r="1331" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1331" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1331">
         <v>8</v>
       </c>
@@ -39522,7 +39828,7 @@
         <v>2461</v>
       </c>
     </row>
-    <row r="1332" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1332" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1332">
         <v>8</v>
       </c>
@@ -39551,7 +39857,7 @@
         <v>2465</v>
       </c>
     </row>
-    <row r="1333" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1333" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1333">
         <v>8</v>
       </c>
@@ -39580,7 +39886,7 @@
         <v>2469</v>
       </c>
     </row>
-    <row r="1334" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1334" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1334">
         <v>8</v>
       </c>
@@ -39609,7 +39915,7 @@
         <v>2473</v>
       </c>
     </row>
-    <row r="1335" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1335" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1335">
         <v>8</v>
       </c>
@@ -39638,7 +39944,7 @@
         <v>2477</v>
       </c>
     </row>
-    <row r="1336" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1336" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1336">
         <v>8</v>
       </c>
@@ -39667,7 +39973,7 @@
         <v>2481</v>
       </c>
     </row>
-    <row r="1337" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1337" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1337">
         <v>8</v>
       </c>
@@ -39696,7 +40002,7 @@
         <v>2485</v>
       </c>
     </row>
-    <row r="1338" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1338" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1338">
         <v>8</v>
       </c>
@@ -39725,7 +40031,7 @@
         <v>2489</v>
       </c>
     </row>
-    <row r="1339" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1339" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1339">
         <v>8</v>
       </c>
@@ -39754,7 +40060,7 @@
         <v>2493</v>
       </c>
     </row>
-    <row r="1340" spans="1:9" ht="34" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1340" spans="1:10" ht="34" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1340">
         <v>8</v>
       </c>
@@ -39783,7 +40089,7 @@
         <v>2497</v>
       </c>
     </row>
-    <row r="1341" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1341" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1341">
         <v>8</v>
       </c>
@@ -39812,7 +40118,7 @@
         <v>2501</v>
       </c>
     </row>
-    <row r="1342" spans="1:9" ht="34" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1342" spans="1:10" ht="34" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1342">
         <v>8</v>
       </c>
@@ -39841,7 +40147,7 @@
         <v>2505</v>
       </c>
     </row>
-    <row r="1343" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1343" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1343">
         <v>8</v>
       </c>
@@ -39864,7 +40170,7 @@
         <v>2509</v>
       </c>
     </row>
-    <row r="1344" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1344" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1344">
         <v>8</v>
       </c>
